--- a/experiments/E5-attn-vs-hope/sheet/Attn-vs-HOPE.xlsx
+++ b/experiments/E5-attn-vs-hope/sheet/Attn-vs-HOPE.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Guide" sheetId="1" r:id="Rfe8ed7ee462b4649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Inputs" sheetId="2" r:id="R0c6ea534b2684789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_HW" sheetId="3" r:id="R745462732f3a4b37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_AttnMoE_Prefill" sheetId="4" r:id="Rac8bb67d6fb841b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AttnMoE_Decode" sheetId="5" r:id="R311f02261cb042bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_HOPE_Prefill" sheetId="6" r:id="R8f3352fd192a48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_HOPE_Decode" sheetId="7" r:id="Rbbeb6cc8e55f4211"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Compare" sheetId="8" r:id="R03264386cd2e4654"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_Sweeps" sheetId="9" r:id="R102c8b23765b41c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_QA" sheetId="10" r:id="R3f1bc3f204534b26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Sources" sheetId="11" r:id="Rc6f373ea40b8437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Guide" sheetId="1" r:id="R68f0ce3d643e480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Inputs" sheetId="2" r:id="Re5e5b06f084542aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_HW" sheetId="3" r:id="R2db0d770ef3a4035"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_AttnMoE_Prefill" sheetId="4" r:id="Rb58597bfa6e04ec1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AttnMoE_Decode" sheetId="5" r:id="Rb7b939057e01491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_HOPE_Prefill" sheetId="6" r:id="R5c1749cb27984c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_HOPE_Decode" sheetId="7" r:id="Rb0cb7e7f288e4623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Compare" sheetId="8" r:id="R13f86e3c70ee425a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_Sweeps" sheetId="9" r:id="Rac22ec74457245bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_QA" sheetId="10" r:id="Rf3801330178946f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Sources" sheetId="11" r:id="Raad7c2dfa94d4b7c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,8 +30,8 @@
     <x:numFmt numFmtId="203" formatCode="0.000"/>
     <x:numFmt numFmtId="204" formatCode="0.000000"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.00"/>
-    <x:numFmt numFmtId="206" formatCode="0.00E+00"/>
-    <x:numFmt numFmtId="207" formatCode="#,##0"/>
+    <x:numFmt numFmtId="206" formatCode="#,##0"/>
+    <x:numFmt numFmtId="207" formatCode="0.00E+00"/>
     <x:numFmt numFmtId="208" formatCode="0.0000000000E+00"/>
   </x:numFmts>
   <x:fonts count="6">
@@ -353,6 +353,15 @@
     <x:xf numFmtId="206" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
+    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
     <x:xf numFmtId="203" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
@@ -360,15 +369,6 @@
       <x:alignment vertical="top"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="207" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
     <x:xf numFmtId="208" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -555,14 +555,17 @@
             <c:v>Effective TFLOP/s</c:v>
           </c:tx>
           <c:xVal>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="0"/>
-            </c:numLit>
+            <c:numRef>
+              <c:f>'30_Compare'!$P$6:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'30_Compare'!$M$6:$M$9</c:f>
+              <c:f>'30_Compare'!$Q$6:$Q$9</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -835,13 +838,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -857,7 +860,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd69c2ee42f1b4ac4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8b0a612a981440a6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -865,13 +868,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -887,7 +890,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R765359823efe47d6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb9908089caf341bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -922,7 +925,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R189eda71ad2849ea"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9643110e5fdc46de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1306,22 +1309,22 @@
         <x:v>Attention prefill FLOPs</x:v>
       </x:c>
       <x:c r="B6" s="85" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'10_AttnMoE_Prefill'!$A$3</x:f>
         <x:v>90324254851072</x:v>
       </x:c>
       <x:c r="C6" s="85" t="n">
         <x:v>90324254851072</x:v>
       </x:c>
       <x:c r="D6" s="85" t="n">
-        <x:f>B6-C6+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B6-C6</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="85" t="n">
-        <x:f>0+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
-        <x:f>IF(ABS(D6)&lt;=E6,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D6)&lt;=E6,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G6" s="20" t="str">
@@ -1333,22 +1336,22 @@
         <x:v>Attention prefill effective HBM B</x:v>
       </x:c>
       <x:c r="B7" s="86" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$D$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'10_AttnMoE_Prefill'!$D$3</x:f>
         <x:v>67916267520</x:v>
       </x:c>
       <x:c r="C7" s="86" t="n">
         <x:v>67916267520</x:v>
       </x:c>
       <x:c r="D7" s="86" t="n">
-        <x:f>B7-C7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B7-C7</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="86" t="n">
-        <x:f>0.01+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:f>IF(ABS(D7)&lt;=E7,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D7)&lt;=E7,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
@@ -1360,22 +1363,22 @@
         <x:v>Attention prefill stagewise ms</x:v>
       </x:c>
       <x:c r="B8" s="86" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
         <x:v>93.38632175616647</x:v>
       </x:c>
       <x:c r="C8" s="86" t="n">
         <x:v>93.38632175616648</x:v>
       </x:c>
       <x:c r="D8" s="86" t="n">
-        <x:f>B8-C8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B8-C8</x:f>
         <x:v>-1.4210854715202004e-14</x:v>
       </x:c>
       <x:c r="E8" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:f>IF(ABS(D8)&lt;=E8,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D8)&lt;=E8,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
@@ -1387,22 +1390,22 @@
         <x:v>Attention decode FLOPs</x:v>
       </x:c>
       <x:c r="B9" s="86" t="n">
-        <x:f>'11_AttnMoE_Decode'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'11_AttnMoE_Decode'!$A$3</x:f>
         <x:v>181800013824</x:v>
       </x:c>
       <x:c r="C9" s="86" t="n">
         <x:v>181800013824</x:v>
       </x:c>
       <x:c r="D9" s="86" t="n">
-        <x:f>B9-C9+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="86" t="n">
-        <x:f>0+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:f>IF(ABS(D9)&lt;=E9,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D9)&lt;=E9,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
@@ -1414,22 +1417,22 @@
         <x:v>Attention decode effective HBM B</x:v>
       </x:c>
       <x:c r="B10" s="86" t="n">
-        <x:f>'11_AttnMoE_Decode'!$D$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'11_AttnMoE_Decode'!$D$3</x:f>
         <x:v>80571472801.34651</x:v>
       </x:c>
       <x:c r="C10" s="86" t="n">
         <x:v>80571472801.34651</x:v>
       </x:c>
       <x:c r="D10" s="86" t="n">
-        <x:f>B10-C10+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="86" t="n">
-        <x:f>0.01+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:f>IF(ABS(D10)&lt;=E10,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D10)&lt;=E10,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
@@ -1441,22 +1444,22 @@
         <x:v>Attention decode stagewise ms</x:v>
       </x:c>
       <x:c r="B11" s="86" t="n">
-        <x:f>'11_AttnMoE_Decode'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="C11" s="86" t="n">
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="D11" s="86" t="n">
-        <x:f>B11-C11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B11-C11</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:f>IF(ABS(D11)&lt;=E11,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D11)&lt;=E11,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
@@ -1468,22 +1471,22 @@
         <x:v>HOPE prefill FLOPs</x:v>
       </x:c>
       <x:c r="B12" s="86" t="n">
-        <x:f>'20_HOPE_Prefill'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'20_HOPE_Prefill'!$A$3</x:f>
         <x:v>422284943294464</x:v>
       </x:c>
       <x:c r="C12" s="86" t="n">
         <x:v>422284943294464</x:v>
       </x:c>
       <x:c r="D12" s="86" t="n">
-        <x:f>B12-C12+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E12" s="86" t="n">
-        <x:f>0.01+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F12" s="21" t="str">
-        <x:f>IF(ABS(D12)&lt;=E12,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D12)&lt;=E12,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G12" s="21" t="str">
@@ -1495,22 +1498,22 @@
         <x:v>HOPE prefill effective HBM B</x:v>
       </x:c>
       <x:c r="B13" s="86" t="n">
-        <x:f>'20_HOPE_Prefill'!$D$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'20_HOPE_Prefill'!$D$3</x:f>
         <x:v>348506292224</x:v>
       </x:c>
       <x:c r="C13" s="86" t="n">
         <x:v>348506292224</x:v>
       </x:c>
       <x:c r="D13" s="86" t="n">
-        <x:f>B13-C13+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E13" s="86" t="n">
-        <x:f>0.01+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
-        <x:f>IF(ABS(D13)&lt;=E13,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D13)&lt;=E13,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G13" s="21" t="str">
@@ -1522,22 +1525,22 @@
         <x:v>HOPE prefill stagewise ms</x:v>
       </x:c>
       <x:c r="B14" s="86" t="n">
-        <x:f>'20_HOPE_Prefill'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'20_HOPE_Prefill'!$J$3</x:f>
         <x:v>451.376552017883</x:v>
       </x:c>
       <x:c r="C14" s="86" t="n">
         <x:v>451.3765520178831</x:v>
       </x:c>
       <x:c r="D14" s="86" t="n">
-        <x:f>B14-C14+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B14-C14</x:f>
         <x:v>-1.1368683772161603e-13</x:v>
       </x:c>
       <x:c r="E14" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F14" s="21" t="str">
-        <x:f>IF(ABS(D14)&lt;=E14,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D14)&lt;=E14,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G14" s="21" t="str">
@@ -1549,22 +1552,22 @@
         <x:v>HOPE normal decode ms</x:v>
       </x:c>
       <x:c r="B15" s="86" t="n">
-        <x:f>'21_HOPE_Decode'!$B$6+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
         <x:v>76.34359890613672</x:v>
       </x:c>
       <x:c r="C15" s="86" t="n">
         <x:v>76.3435989061367</x:v>
       </x:c>
       <x:c r="D15" s="86" t="n">
-        <x:f>B15-C15+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B15-C15</x:f>
         <x:v>1.4210854715202004e-14</x:v>
       </x:c>
       <x:c r="E15" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F15" s="21" t="str">
-        <x:f>IF(ABS(D15)&lt;=E15,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D15)&lt;=E15,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G15" s="21" t="str">
@@ -1576,22 +1579,22 @@
         <x:v>HOPE boundary decode ms</x:v>
       </x:c>
       <x:c r="B16" s="86" t="n">
-        <x:f>'21_HOPE_Decode'!$B$7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$7</x:f>
         <x:v>96.85750155927104</x:v>
       </x:c>
       <x:c r="C16" s="86" t="n">
         <x:v>96.85750155927103</x:v>
       </x:c>
       <x:c r="D16" s="86" t="n">
-        <x:f>B16-C16+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B16-C16</x:f>
         <x:v>1.4210854715202004e-14</x:v>
       </x:c>
       <x:c r="E16" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F16" s="21" t="str">
-        <x:f>IF(ABS(D16)&lt;=E16,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D16)&lt;=E16,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
@@ -1603,22 +1606,22 @@
         <x:v>HOPE amortized decode ms</x:v>
       </x:c>
       <x:c r="B17" s="86" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="C17" s="86" t="n">
         <x:v>76.35361546016655</x:v>
       </x:c>
       <x:c r="D17" s="86" t="n">
-        <x:f>B17-C17+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B17-C17</x:f>
         <x:v>1.4210854715202004e-14</x:v>
       </x:c>
       <x:c r="E17" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
-        <x:f>IF(ABS(D17)&lt;=E17,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D17)&lt;=E17,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G17" s="21" t="str">
@@ -1630,22 +1633,22 @@
         <x:v>Context sweep 1K Attention decode ms</x:v>
       </x:c>
       <x:c r="B18" s="86" t="n">
-        <x:f>'40_Sweeps'!$B$6+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'40_Sweeps'!$B$6</x:f>
         <x:v>3.657791245775076</x:v>
       </x:c>
       <x:c r="C18" s="86" t="n">
         <x:v>3.6577912457750763</x:v>
       </x:c>
       <x:c r="D18" s="86" t="n">
-        <x:f>B18-C18+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B18-C18</x:f>
         <x:v>-4.440892098500626e-16</x:v>
       </x:c>
       <x:c r="E18" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F18" s="21" t="str">
-        <x:f>IF(ABS(D18)&lt;=E18,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D18)&lt;=E18,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G18" s="21" t="str">
@@ -1657,22 +1660,22 @@
         <x:v>Context sweep 256K Attention decode ms</x:v>
       </x:c>
       <x:c r="B19" s="86" t="n">
-        <x:f>'40_Sweeps'!$B$11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'40_Sweeps'!$B$11</x:f>
         <x:v>44.60484054965567</x:v>
       </x:c>
       <x:c r="C19" s="86" t="n">
         <x:v>44.60484054965568</x:v>
       </x:c>
       <x:c r="D19" s="86" t="n">
-        <x:f>B19-C19+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B19-C19</x:f>
         <x:v>-7.105427357601002e-15</x:v>
       </x:c>
       <x:c r="E19" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F19" s="21" t="str">
-        <x:f>IF(ABS(D19)&lt;=E19,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D19)&lt;=E19,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G19" s="21" t="str">
@@ -1684,22 +1687,22 @@
         <x:v>Batch sweep B=1 HOPE decode ms</x:v>
       </x:c>
       <x:c r="B20" s="86" t="n">
-        <x:f>'40_Sweeps'!$C$17+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'40_Sweeps'!$C$17</x:f>
         <x:v>2.405456964324235</x:v>
       </x:c>
       <x:c r="C20" s="86" t="n">
         <x:v>2.4054569643242347</x:v>
       </x:c>
       <x:c r="D20" s="86" t="n">
-        <x:f>B20-C20+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B20-C20</x:f>
         <x:v>4.440892098500626e-16</x:v>
       </x:c>
       <x:c r="E20" s="86" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F20" s="21" t="str">
-        <x:f>IF(ABS(D20)&lt;=E20,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D20)&lt;=E20,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
@@ -1711,22 +1714,22 @@
         <x:v>Batch sweep B=32 HOPE decode ms</x:v>
       </x:c>
       <x:c r="B21" s="87" t="n">
-        <x:f>'40_Sweeps'!$C$22+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'40_Sweeps'!$C$22</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="C21" s="87" t="n">
         <x:v>76.35361546016655</x:v>
       </x:c>
       <x:c r="D21" s="87" t="n">
-        <x:f>B21-C21+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B21-C21</x:f>
         <x:v>1.4210854715202004e-14</x:v>
       </x:c>
       <x:c r="E21" s="87" t="n">
-        <x:f>1e-8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
       <x:c r="F21" s="22" t="str">
-        <x:f>IF(ABS(D21)&lt;=E21,"PASS","REVIEW")&amp;IF('02_HW'!$C$8&gt;0,"","")</x:f>
+        <x:f>IF(ABS(D21)&lt;=E21,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G21" s="22" t="str">
@@ -2854,7 +2857,7 @@
         <x:v>hope_scenarios.shipped_credible_momentum.inputs.prefill.position</x:v>
       </x:c>
       <x:c r="F40" s="21" t="str">
-        <x:v>Boundary-count origin</x:v>
+        <x:v>Imported boundary-count origin</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2874,7 +2877,7 @@
         <x:v>hope_scenarios.shipped_credible_momentum.inputs.decode.position</x:v>
       </x:c>
       <x:c r="F41" s="21" t="str">
-        <x:v>Timing sheet uses explicit modes</x:v>
+        <x:v>Imported timing origin; timing modes remain explicit</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3587,59 +3590,59 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="63" t="n">
-        <x:f>SUM(G6:G17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(G6:G17)</x:f>
         <x:v>90324254851072</x:v>
       </x:c>
       <x:c r="B3" s="63" t="n">
-        <x:f>SUM(K6:K17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:K17)</x:f>
         <x:v>60399550464</x:v>
       </x:c>
       <x:c r="C3" s="63" t="n">
-        <x:f>SUM(L6:L17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(L6:L17)</x:f>
         <x:v>7516717056</x:v>
       </x:c>
       <x:c r="D3" s="63" t="n">
-        <x:f>SUM(K6:L17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:L17)</x:f>
         <x:v>67916267520</x:v>
       </x:c>
       <x:c r="E3" s="63" t="n">
-        <x:f>SUM(M6:M17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M6:M17)</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="F3" s="64" t="n">
-        <x:f>IF(SUM(K6:L17)=0,"",SUM(G6:G17)/SUM(K6:L17)+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(SUM(K6:L17)=0,"",SUM(G6:G17)/SUM(K6:L17))</x:f>
         <x:v>1329.9354948278524</x:v>
       </x:c>
       <x:c r="G3" s="64" t="n">
-        <x:f>SUM(O6:O17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(O6:O17)</x:f>
         <x:v>91.28530655852009</x:v>
       </x:c>
       <x:c r="H3" s="64" t="n">
-        <x:f>SUM(P6:P17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(P6:P17)</x:f>
         <x:v>20.273512692537313</x:v>
       </x:c>
       <x:c r="I3" s="64" t="n">
-        <x:f>MAX(SUM(O6:O17),SUM(P6:P17))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>MAX(SUM(O6:O17),SUM(P6:P17))</x:f>
         <x:v>91.28530655852009</x:v>
       </x:c>
       <x:c r="J3" s="64" t="n">
-        <x:f>SUM(Q6:Q17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q6:Q17)</x:f>
         <x:v>93.38632175616647</x:v>
       </x:c>
       <x:c r="K3" s="62" t="str">
-        <x:f>IF(SUM(O6:O17)&gt;SUM(P6:P17),"compute",IF(SUM(P6:P17)&gt;SUM(O6:O17),"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(O6:O17)&gt;SUM(P6:P17),"compute",IF(SUM(P6:P17)&gt;SUM(O6:O17),"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="L3" s="62" t="str">
-        <x:f>IF(SUM(M6:M17)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M6:M17)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>FIT</x:v>
       </x:c>
       <x:c r="M3" s="64" t="n">
-        <x:f>'02_HW'!$C$6/'02_HW'!$C$7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'02_HW'!$C$6/'02_HW'!$C$7</x:f>
         <x:v>295.36477611940296</x:v>
       </x:c>
       <x:c r="N3" s="62" t="str">
-        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")</x:f>
         <x:v>compute-side</x:v>
       </x:c>
       <x:c r="O3" s="72"/>
@@ -3709,7 +3712,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="20" t="str">
@@ -3725,7 +3728,7 @@
         <x:v>2ND(Dq+2Dkv)</x:v>
       </x:c>
       <x:c r="F6" s="65" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="68" t="n">
@@ -3737,7 +3740,7 @@
         <x:v>738197504</x:v>
       </x:c>
       <x:c r="I6" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="68" t="n">
@@ -3745,35 +3748,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))</x:f>
         <x:v>738197504</x:v>
       </x:c>
       <x:c r="L6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M6" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N6" s="65" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>20695.57894736842</x:v>
       </x:c>
       <x:c r="O6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="P6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.38061743761194033</x:v>
       </x:c>
       <x:c r="Q6" s="65" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="R6" s="20" t="str">
-        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S6" s="23" t="str">
@@ -3782,7 +3785,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="21" t="str">
@@ -3798,15 +3801,15 @@
         <x:v>2BQDkv bkv</x:v>
       </x:c>
       <x:c r="F7" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="69" t="n">
@@ -3814,15 +3817,15 @@
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="J7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="M7" s="69" t="n">
@@ -3830,23 +3833,23 @@
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="N7" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0)))=0,"",((1)*(0))/(((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="Q7" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="R7" s="21" t="str">
-        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S7" s="24" t="str">
@@ -3855,7 +3858,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="21" t="str">
@@ -3871,11 +3874,11 @@
         <x:v>NDq ba</x:v>
       </x:c>
       <x:c r="F8" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="69" t="n">
@@ -3883,43 +3886,43 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+(0))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N8" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0)))=0,"",((1)*(0))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.16025997373134326</x:v>
       </x:c>
       <x:c r="Q8" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.16025997373134326</x:v>
       </x:c>
       <x:c r="R8" s="21" t="str">
-        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S8" s="24" t="str">
@@ -3928,7 +3931,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="21" t="str">
@@ -3944,7 +3947,7 @@
         <x:v>4Πdh + csoftmaxΠ</x:v>
       </x:c>
       <x:c r="F9" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="69" t="n">
@@ -3960,39 +3963,39 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="J9" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="L9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M9" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2)))))/((((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)))=0,"",((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2)))))/(((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)))))</x:f>
         <x:v>1379.33984375</x:v>
       </x:c>
       <x:c r="O9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>2.245219995731057</x:v>
       </x:c>
       <x:c r="P9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.48077992119402985</x:v>
       </x:c>
       <x:c r="Q9" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$6)*(('01_Inputs'!$C$6)+1)/2))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.245219995731057</x:v>
       </x:c>
       <x:c r="R9" s="21" t="str">
-        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S9" s="24" t="str">
@@ -4001,7 +4004,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="21" t="str">
@@ -4017,7 +4020,7 @@
         <x:v>2NDqD</x:v>
       </x:c>
       <x:c r="F10" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="69" t="n">
@@ -4029,7 +4032,7 @@
         <x:v>603979776</x:v>
       </x:c>
       <x:c r="I10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="69" t="n">
@@ -4037,35 +4040,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K10" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))</x:f>
         <x:v>603979776</x:v>
       </x:c>
       <x:c r="L10" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>7710.117647058823</x:v>
       </x:c>
       <x:c r="O10" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="P10" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.34055244417910446</x:v>
       </x:c>
       <x:c r="Q10" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="R10" s="21" t="str">
-        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S10" s="24" t="str">
@@ -4074,7 +4077,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="21" t="str">
@@ -4090,7 +4093,7 @@
         <x:v>2NDE + crouterNE</x:v>
       </x:c>
       <x:c r="F11" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="69" t="n">
@@ -4102,7 +4105,7 @@
         <x:v>537919488</x:v>
       </x:c>
       <x:c r="I11" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="69" t="n">
@@ -4110,35 +4113,35 @@
         <x:v>524288</x:v>
       </x:c>
       <x:c r="K11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))</x:f>
         <x:v>537919488</x:v>
       </x:c>
       <x:c r="L11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))</x:f>
         <x:v>524288</x:v>
       </x:c>
       <x:c r="M11" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N11" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))))</x:f>
         <x:v>255.26777020447906</x:v>
       </x:c>
       <x:c r="O11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.13890978428899453</x:v>
       </x:c>
       <x:c r="P11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.1607294853731343</x:v>
       </x:c>
       <x:c r="Q11" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.1607294853731343</x:v>
       </x:c>
       <x:c r="R11" s="21" t="str">
-        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S11" s="24" t="str">
@@ -4147,7 +4150,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="21" t="str">
@@ -4163,11 +4166,11 @@
         <x:v>materialize top-k routes</x:v>
       </x:c>
       <x:c r="F12" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="69" t="n">
@@ -4175,7 +4178,7 @@
         <x:v>537395200</x:v>
       </x:c>
       <x:c r="I12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="69" t="n">
@@ -4183,35 +4186,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))</x:f>
         <x:v>537395200</x:v>
       </x:c>
       <x:c r="L12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*(0))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3206764513432836</x:v>
       </x:c>
       <x:c r="Q12" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3206764513432836</x:v>
       </x:c>
       <x:c r="R12" s="21" t="str">
-        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S12" s="24" t="str">
@@ -4220,7 +4223,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
@@ -4236,7 +4239,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F13" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="69" t="n">
@@ -4248,7 +4251,7 @@
         <x:v>17716740096</x:v>
       </x:c>
       <x:c r="I13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" s="69" t="n">
@@ -4256,35 +4259,35 @@
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="K13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))</x:f>
         <x:v>17716740096</x:v>
       </x:c>
       <x:c r="L13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="M13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>936.2285714285714</x:v>
       </x:c>
       <x:c r="O13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="P13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q13" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="R13" s="21" t="str">
-        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S13" s="24" t="str">
@@ -4293,7 +4296,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
@@ -4309,7 +4312,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F14" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="69" t="n">
@@ -4321,7 +4324,7 @@
         <x:v>17716740096</x:v>
       </x:c>
       <x:c r="I14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="69" t="n">
@@ -4329,35 +4332,35 @@
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="K14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>17716740096</x:v>
       </x:c>
       <x:c r="L14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="M14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>936.2285714285714</x:v>
       </x:c>
       <x:c r="O14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="P14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q14" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="R14" s="21" t="str">
-        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S14" s="24" t="str">
@@ -4366,7 +4369,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
@@ -4382,7 +4385,7 @@
         <x:v>NrF cactivation</x:v>
       </x:c>
       <x:c r="F15" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="69" t="n">
@@ -4394,7 +4397,7 @@
         <x:v>2147483648</x:v>
       </x:c>
       <x:c r="I15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="69" t="n">
@@ -4402,35 +4405,35 @@
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="K15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2147483648</x:v>
       </x:c>
       <x:c r="L15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1073741824</x:v>
       </x:c>
       <x:c r="M15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33))))/((((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33))))/(((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>1.3333333333333333</x:v>
       </x:c>
       <x:c r="O15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004340665825814171</x:v>
       </x:c>
       <x:c r="P15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.9615598423880597</x:v>
       </x:c>
       <x:c r="Q15" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.9615598423880597</x:v>
       </x:c>
       <x:c r="R15" s="21" t="str">
-        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S15" s="24" t="str">
@@ -4439,7 +4442,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
@@ -4455,7 +4458,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F16" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="69" t="n">
@@ -4467,7 +4470,7 @@
         <x:v>18253611008</x:v>
       </x:c>
       <x:c r="I16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="69" t="n">
@@ -4475,35 +4478,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>18253611008</x:v>
       </x:c>
       <x:c r="L16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>936.2285714285714</x:v>
       </x:c>
       <x:c r="O16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="P16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q16" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="R16" s="21" t="str">
-        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S16" s="24" t="str">
@@ -4512,7 +4515,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="22" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="22" t="str">
@@ -4528,11 +4531,11 @@
         <x:v>combine top-k outputs</x:v>
       </x:c>
       <x:c r="F17" s="67" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="70" t="n">
@@ -4544,39 +4547,39 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="J17" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L17" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M17" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="67" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0)))=0,"",((1)*(0))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O17" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P17" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="Q17" s="67" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="R17" s="22" t="str">
-        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S17" s="25" t="str">
@@ -4690,59 +4693,59 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="63" t="n">
-        <x:f>SUM(G6:G18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(G6:G18)</x:f>
         <x:v>181800013824</x:v>
       </x:c>
       <x:c r="B3" s="63" t="n">
-        <x:f>SUM(K6:K18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:K18)</x:f>
         <x:v>80500169377.34651</x:v>
       </x:c>
       <x:c r="C3" s="63" t="n">
-        <x:f>SUM(L6:L18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(L6:L18)</x:f>
         <x:v>71303424</x:v>
       </x:c>
       <x:c r="D3" s="63" t="n">
-        <x:f>SUM(K6:L18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:L18)</x:f>
         <x:v>80571472801.34651</x:v>
       </x:c>
       <x:c r="E3" s="63" t="n">
-        <x:f>SUM(M6:M18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M6:M18)</x:f>
         <x:v>68719476736</x:v>
       </x:c>
       <x:c r="F3" s="64" t="n">
-        <x:f>IF(SUM(K6:L18)=0,"",SUM(G6:G18)/SUM(K6:L18)+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(SUM(K6:L18)=0,"",SUM(G6:G18)/SUM(K6:L18))</x:f>
         <x:v>2.2563819116505184</x:v>
       </x:c>
       <x:c r="G3" s="64" t="n">
-        <x:f>SUM(O6:O18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(O6:O18)</x:f>
         <x:v>0.18373436926360726</x:v>
       </x:c>
       <x:c r="H3" s="64" t="n">
-        <x:f>SUM(P6:P18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(P6:P18)</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="I3" s="64" t="n">
-        <x:f>MAX(SUM(O6:O18),SUM(P6:P18))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>MAX(SUM(O6:O18),SUM(P6:P18))</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="J3" s="64" t="n">
-        <x:f>SUM(Q6:Q18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q6:Q18)</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="K3" s="62" t="str">
-        <x:f>IF(SUM(O6:O18)&gt;SUM(P6:P18),"compute",IF(SUM(P6:P18)&gt;SUM(O6:O18),"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(O6:O18)&gt;SUM(P6:P18),"compute",IF(SUM(P6:P18)&gt;SUM(O6:O18),"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="L3" s="62" t="str">
-        <x:f>IF(SUM(M6:M18)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M6:M18)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>FIT</x:v>
       </x:c>
       <x:c r="M3" s="64" t="n">
-        <x:f>'02_HW'!$C$6/'02_HW'!$C$7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'02_HW'!$C$6/'02_HW'!$C$7</x:f>
         <x:v>295.36477611940296</x:v>
       </x:c>
       <x:c r="N3" s="62" t="str">
-        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")</x:f>
         <x:v>memory-side</x:v>
       </x:c>
       <x:c r="O3" s="72"/>
@@ -4812,7 +4815,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="20" t="str">
@@ -4828,7 +4831,7 @@
         <x:v>2ND(Dq+2Dkv)</x:v>
       </x:c>
       <x:c r="F6" s="65" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="68" t="n">
@@ -4840,7 +4843,7 @@
         <x:v>201588736</x:v>
       </x:c>
       <x:c r="I6" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="68" t="n">
@@ -4848,35 +4851,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))</x:f>
         <x:v>201588736</x:v>
       </x:c>
       <x:c r="L6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M6" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N6" s="65" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>63.833766233766234</x:v>
       </x:c>
       <x:c r="O6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.013021997477442515</x:v>
       </x:c>
       <x:c r="P6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="Q6" s="65" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="R6" s="20" t="str">
-        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S6" s="23" t="str">
@@ -4885,7 +4888,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="21" t="str">
@@ -4901,15 +4904,15 @@
         <x:v>2BQDkv bkv</x:v>
       </x:c>
       <x:c r="F7" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" s="69" t="n">
@@ -4917,15 +4920,15 @@
         <x:v>524288</x:v>
       </x:c>
       <x:c r="J7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(0)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))</x:f>
         <x:v>524288</x:v>
       </x:c>
       <x:c r="M7" s="69" t="n">
@@ -4933,23 +4936,23 @@
         <x:v>68719476736</x:v>
       </x:c>
       <x:c r="N7" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0)))=0,"",((1)*(0))/(((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="Q7" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="R7" s="21" t="str">
-        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S7" s="24" t="str">
@@ -4958,7 +4961,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="21" t="str">
@@ -4974,11 +4977,11 @@
         <x:v>NDq ba</x:v>
       </x:c>
       <x:c r="F8" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="69" t="n">
@@ -4986,43 +4989,43 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+(0))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N8" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0)))=0,"",((1)*(0))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="Q8" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="R8" s="21" t="str">
-        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S8" s="24" t="str">
@@ -5031,7 +5034,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="21" t="str">
@@ -5047,7 +5050,7 @@
         <x:v>4BHqQKdh + csoftmaxBHqQK</x:v>
       </x:c>
       <x:c r="F9" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="69" t="n">
@@ -5067,35 +5070,35 @@
         <x:v>67633152</x:v>
       </x:c>
       <x:c r="K9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))</x:f>
         <x:v>68719476736</x:v>
       </x:c>
       <x:c r="L9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))</x:f>
         <x:v>67633152</x:v>
       </x:c>
       <x:c r="M9" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9))))))/((((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))))=0,"",((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9))))))/(((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))))))</x:f>
         <x:v>2.017545597975625</x:v>
       </x:c>
       <x:c r="O9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.14025776449662042</x:v>
       </x:c>
       <x:c r="P9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>20.533465638208956</x:v>
       </x:c>
       <x:c r="Q9" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>20.533465638208956</x:v>
       </x:c>
       <x:c r="R9" s="21" t="str">
-        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S9" s="24" t="str">
@@ -5104,7 +5107,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="21" t="str">
@@ -5120,11 +5123,11 @@
         <x:v>read partials; write O</x:v>
       </x:c>
       <x:c r="F10" s="66" t="n">
-        <x:f>(IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(IF(('01_Inputs'!$C$19)&gt;1,1,0))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="69" t="n">
@@ -5136,39 +5139,39 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="J10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K10" s="69" t="n">
-        <x:f>((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))</x:f>
         <x:v>67633152</x:v>
       </x:c>
       <x:c r="L10" s="69" t="n">
-        <x:f>((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="66" t="n">
-        <x:f>IF((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))))=0,"",(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)))=0,"",(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0))/((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="66" t="n">
-        <x:f>(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P10" s="66" t="n">
-        <x:f>(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.020267252537313433</x:v>
       </x:c>
       <x:c r="Q10" s="66" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020267252537313433</x:v>
       </x:c>
       <x:c r="R10" s="21" t="str">
-        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S10" s="24" t="str">
@@ -5177,7 +5180,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="21" t="str">
@@ -5193,7 +5196,7 @@
         <x:v>2NDqD</x:v>
       </x:c>
       <x:c r="F11" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="69" t="n">
@@ -5205,7 +5208,7 @@
         <x:v>67371008</x:v>
       </x:c>
       <x:c r="I11" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="69" t="n">
@@ -5213,35 +5216,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))</x:f>
         <x:v>67371008</x:v>
       </x:c>
       <x:c r="L11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M11" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N11" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>63.50387596899225</x:v>
       </x:c>
       <x:c r="O11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004340665825814171</x:v>
       </x:c>
       <x:c r="P11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="Q11" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="R11" s="21" t="str">
-        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S11" s="24" t="str">
@@ -5250,7 +5253,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="21" t="str">
@@ -5266,7 +5269,7 @@
         <x:v>2NDE + crouterNE</x:v>
       </x:c>
       <x:c r="F12" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="69" t="n">
@@ -5278,7 +5281,7 @@
         <x:v>1310720</x:v>
       </x:c>
       <x:c r="I12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="69" t="n">
@@ -5286,35 +5289,35 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="K12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))</x:f>
         <x:v>1310720</x:v>
       </x:c>
       <x:c r="L12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))</x:f>
         <x:v>256</x:v>
       </x:c>
       <x:c r="M12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))))</x:f>
         <x:v>51.19312634251123</x:v>
       </x:c>
       <x:c r="O12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00006782704310986061</x:v>
       </x:c>
       <x:c r="P12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="Q12" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="R12" s="21" t="str">
-        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S12" s="24" t="str">
@@ -5323,7 +5326,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
@@ -5339,11 +5342,11 @@
         <x:v>materialize top-k routes</x:v>
       </x:c>
       <x:c r="F13" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="69" t="n">
@@ -5351,7 +5354,7 @@
         <x:v>262400</x:v>
       </x:c>
       <x:c r="I13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" s="69" t="n">
@@ -5359,35 +5362,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))</x:f>
         <x:v>262400</x:v>
       </x:c>
       <x:c r="L13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*(0))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="Q13" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="R13" s="21" t="str">
-        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S13" s="24" t="str">
@@ -5396,7 +5399,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
@@ -5412,7 +5415,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F14" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="69" t="n">
@@ -5424,7 +5427,7 @@
         <x:v>3813563872.4488354</x:v>
       </x:c>
       <x:c r="I14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="69" t="n">
@@ -5432,35 +5435,35 @@
         <x:v>524288</x:v>
       </x:c>
       <x:c r="K14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))</x:f>
         <x:v>3813563872.4488354</x:v>
       </x:c>
       <x:c r="L14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>524288</x:v>
       </x:c>
       <x:c r="M14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>2.252159423338854</x:v>
       </x:c>
       <x:c r="O14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.008681331651628342</x:v>
       </x:c>
       <x:c r="P14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q14" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R14" s="21" t="str">
-        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S14" s="24" t="str">
@@ -5469,7 +5472,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
@@ -5485,7 +5488,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F15" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="69" t="n">
@@ -5497,7 +5500,7 @@
         <x:v>3813563872.4488354</x:v>
       </x:c>
       <x:c r="I15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="69" t="n">
@@ -5505,35 +5508,35 @@
         <x:v>524288</x:v>
       </x:c>
       <x:c r="K15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3813563872.4488354</x:v>
       </x:c>
       <x:c r="L15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>524288</x:v>
       </x:c>
       <x:c r="M15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>2.252159423338854</x:v>
       </x:c>
       <x:c r="O15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.008681331651628342</x:v>
       </x:c>
       <x:c r="P15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q15" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R15" s="21" t="str">
-        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S15" s="24" t="str">
@@ -5542,7 +5545,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
@@ -5558,7 +5561,7 @@
         <x:v>NrF cactivation</x:v>
       </x:c>
       <x:c r="F16" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="69" t="n">
@@ -5570,7 +5573,7 @@
         <x:v>1048576</x:v>
       </x:c>
       <x:c r="I16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="69" t="n">
@@ -5578,35 +5581,35 @@
         <x:v>524288</x:v>
       </x:c>
       <x:c r="K16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1048576</x:v>
       </x:c>
       <x:c r="L16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>524288</x:v>
       </x:c>
       <x:c r="M16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",(((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33))))/((((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))=0,"",((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33))))/(((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14))))))))))</x:f>
         <x:v>1.3333333333333333</x:v>
       </x:c>
       <x:c r="O16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0000021194657352608257</x:v>
       </x:c>
       <x:c r="P16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="Q16" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="R16" s="21" t="str">
-        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S16" s="24" t="str">
@@ -5615,7 +5618,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
@@ -5631,7 +5634,7 @@
         <x:v>2NrDF</x:v>
       </x:c>
       <x:c r="F17" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="69" t="n">
@@ -5643,7 +5646,7 @@
         <x:v>3813826016.4488354</x:v>
       </x:c>
       <x:c r="I17" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="69" t="n">
@@ -5651,35 +5654,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3813826016.4488354</x:v>
       </x:c>
       <x:c r="L17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M17" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/((((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25))))/(((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.252159423338854</x:v>
       </x:c>
       <x:c r="O17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.008681331651628342</x:v>
       </x:c>
       <x:c r="P17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q17" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R17" s="21" t="str">
-        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S17" s="24" t="str">
@@ -5688,7 +5691,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="22" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="22" t="str">
@@ -5704,11 +5707,11 @@
         <x:v>combine top-k outputs</x:v>
       </x:c>
       <x:c r="F18" s="67" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="70" t="n">
@@ -5720,39 +5723,39 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="J18" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L18" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M18" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N18" s="67" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))))=0,"",(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0)))=0,"",((1)*(0))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O18" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P18" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="Q18" s="67" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="R18" s="22" t="str">
-        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S18" s="25" t="str">
@@ -5866,59 +5869,59 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="63" t="n">
-        <x:f>SUM(G6:G39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(G6:G39)</x:f>
         <x:v>422284943294464</x:v>
       </x:c>
       <x:c r="B3" s="63" t="n">
-        <x:f>SUM(K6:K39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:K39)</x:f>
         <x:v>169722642432</x:v>
       </x:c>
       <x:c r="C3" s="63" t="n">
-        <x:f>SUM(L6:L39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(L6:L39)</x:f>
         <x:v>178783649792</x:v>
       </x:c>
       <x:c r="D3" s="63" t="n">
-        <x:f>SUM(K6:L39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K6:L39)</x:f>
         <x:v>348506292224</x:v>
       </x:c>
       <x:c r="E3" s="63" t="n">
-        <x:f>SUM(M6:M39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M6:M39)</x:f>
         <x:v>100934352896</x:v>
       </x:c>
       <x:c r="F3" s="64" t="n">
-        <x:f>IF(SUM(K6:L39)=0,"",SUM(G6:G39)/SUM(K6:L39)+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(SUM(K6:L39)=0,"",SUM(G6:G39)/SUM(K6:L39))</x:f>
         <x:v>1211.6996241291486</x:v>
       </x:c>
       <x:c r="G3" s="64" t="n">
-        <x:f>SUM(O6:O39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(O6:O39)</x:f>
         <x:v>426.77806273898</x:v>
       </x:c>
       <x:c r="H3" s="64" t="n">
-        <x:f>SUM(P6:P39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(P6:P39)</x:f>
         <x:v>104.03172902208952</x:v>
       </x:c>
       <x:c r="I3" s="64" t="n">
-        <x:f>MAX(SUM(O6:O39),SUM(P6:P39))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>MAX(SUM(O6:O39),SUM(P6:P39))</x:f>
         <x:v>426.77806273898</x:v>
       </x:c>
       <x:c r="J3" s="64" t="n">
-        <x:f>SUM(Q6:Q39)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q6:Q39)</x:f>
         <x:v>451.376552017883</x:v>
       </x:c>
       <x:c r="K3" s="62" t="str">
-        <x:f>IF(SUM(O6:O39)&gt;SUM(P6:P39),"compute",IF(SUM(P6:P39)&gt;SUM(O6:O39),"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(O6:O39)&gt;SUM(P6:P39),"compute",IF(SUM(P6:P39)&gt;SUM(O6:O39),"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="L3" s="62" t="str">
-        <x:f>IF(SUM(M6:M39)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M6:M39)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
       <x:c r="M3" s="64" t="n">
-        <x:f>'02_HW'!$C$6/'02_HW'!$C$7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'02_HW'!$C$6/'02_HW'!$C$7</x:f>
         <x:v>295.36477611940296</x:v>
       </x:c>
       <x:c r="N3" s="62" t="str">
-        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")</x:f>
         <x:v>compute-side</x:v>
       </x:c>
       <x:c r="O3" s="72"/>
@@ -5988,7 +5991,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="20" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="20" t="str">
@@ -6004,7 +6007,7 @@
         <x:v>2ND²</x:v>
       </x:c>
       <x:c r="F6" s="65" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="68" t="n">
@@ -6016,7 +6019,7 @@
         <x:v>603979776</x:v>
       </x:c>
       <x:c r="I6" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="68" t="n">
@@ -6024,11 +6027,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))</x:f>
         <x:v>603979776</x:v>
       </x:c>
       <x:c r="L6" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M6" s="68" t="n">
@@ -6036,23 +6039,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N6" s="65" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>7710.117647058823</x:v>
       </x:c>
       <x:c r="O6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="P6" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.34055244417910446</x:v>
       </x:c>
       <x:c r="Q6" s="65" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="R6" s="20" t="str">
-        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O6&gt;P6,"compute",IF(P6&gt;O6,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S6" s="23" t="str">
@@ -6061,7 +6064,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="21" t="str">
@@ -6077,7 +6080,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F7" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="69" t="n">
@@ -6089,7 +6092,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I7" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="69" t="n">
@@ -6097,11 +6100,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L7" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M7" s="69" t="n">
@@ -6109,23 +6112,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N7" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P7" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q7" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R7" s="21" t="str">
-        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O7&gt;P7,"compute",IF(P7&gt;O7,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S7" s="24" t="str">
@@ -6134,7 +6137,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="21" t="str">
@@ -6150,7 +6153,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F8" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="69" t="n">
@@ -6162,7 +6165,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I8" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J8" s="69" t="n">
@@ -6170,11 +6173,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L8" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M8" s="69" t="n">
@@ -6182,23 +6185,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N8" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P8" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q8" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R8" s="21" t="str">
-        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O8&gt;P8,"compute",IF(P8&gt;O8,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S8" s="24" t="str">
@@ -6207,7 +6210,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="21" t="str">
@@ -6223,7 +6226,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F9" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="69" t="n">
@@ -6235,7 +6238,7 @@
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="I9" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="69" t="n">
@@ -6243,11 +6246,11 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))</x:f>
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="L9" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M9" s="69" t="n">
@@ -6255,23 +6258,23 @@
         <x:v>10738728960</x:v>
       </x:c>
       <x:c r="N9" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.599926766752</x:v>
       </x:c>
       <x:c r="O9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P9" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.8013976835820895</x:v>
       </x:c>
       <x:c r="Q9" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R9" s="21" t="str">
-        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O9&gt;P9,"compute",IF(P9&gt;O9,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S9" s="24" t="str">
@@ -6280,7 +6283,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="21" t="str">
@@ -6296,7 +6299,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F10" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G10" s="69" t="n">
@@ -6308,7 +6311,7 @@
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="I10" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="69" t="n">
@@ -6316,11 +6319,11 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K10" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))</x:f>
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="L10" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M10" s="69" t="n">
@@ -6328,23 +6331,23 @@
         <x:v>10738728960</x:v>
       </x:c>
       <x:c r="N10" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.599926766752</x:v>
       </x:c>
       <x:c r="O10" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P10" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.8013976835820895</x:v>
       </x:c>
       <x:c r="Q10" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R10" s="21" t="str">
-        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O10&gt;P10,"compute",IF(P10&gt;O10,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S10" s="24" t="str">
@@ -6353,7 +6356,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="21" t="str">
@@ -6369,7 +6372,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F11" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="69" t="n">
@@ -6381,7 +6384,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I11" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J11" s="69" t="n">
@@ -6389,11 +6392,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L11" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M11" s="69" t="n">
@@ -6401,23 +6404,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N11" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P11" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q11" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R11" s="21" t="str">
-        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O11&gt;P11,"compute",IF(P11&gt;O11,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S11" s="24" t="str">
@@ -6426,7 +6429,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="21" t="str">
@@ -6442,7 +6445,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F12" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="69" t="n">
@@ -6454,7 +6457,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="69" t="n">
@@ -6462,35 +6465,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L12" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M12" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P12" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q12" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R12" s="21" t="str">
-        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S12" s="24" t="str">
@@ -6499,7 +6502,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
@@ -6515,7 +6518,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F13" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="69" t="n">
@@ -6527,7 +6530,7 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" s="69" t="n">
@@ -6535,35 +6538,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="Q13" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R13" s="21" t="str">
-        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S13" s="24" t="str">
@@ -6572,7 +6575,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
@@ -6588,7 +6591,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F14" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="69" t="n">
@@ -6600,7 +6603,7 @@
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="I14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="69" t="n">
@@ -6608,35 +6611,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))</x:f>
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="L14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>1404.3428571428572</x:v>
       </x:c>
       <x:c r="O14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="P14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q14" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="R14" s="21" t="str">
-        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S14" s="24" t="str">
@@ -6645,7 +6648,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
@@ -6661,7 +6664,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F15" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="69" t="n">
@@ -6673,7 +6676,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="69" t="n">
@@ -6681,35 +6684,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>256.15625</x:v>
       </x:c>
       <x:c r="O15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.895109443549691</x:v>
       </x:c>
       <x:c r="P15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q15" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R15" s="21" t="str">
-        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S15" s="24" t="str">
@@ -6718,7 +6721,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
@@ -6734,11 +6737,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F16" s="66" t="n">
-        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="69" t="n">
@@ -6750,39 +6753,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K16" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="L16" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="M16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="66" t="n">
-        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(0))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P16" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="Q16" s="66" t="n">
-        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$48))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$48))))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="R16" s="21" t="str">
-        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S16" s="24" t="str">
@@ -6791,7 +6794,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
@@ -6807,7 +6810,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F17" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="69" t="n">
@@ -6819,7 +6822,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I17" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="69" t="n">
@@ -6827,35 +6830,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M17" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q17" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R17" s="21" t="str">
-        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S17" s="24" t="str">
@@ -6864,7 +6867,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="21" t="str">
@@ -6880,7 +6883,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F18" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="69" t="n">
@@ -6892,7 +6895,7 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I18" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="69" t="n">
@@ -6900,35 +6903,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K18" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L18" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M18" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N18" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O18" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P18" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="Q18" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R18" s="21" t="str">
-        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S18" s="24" t="str">
@@ -6937,7 +6940,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="21" t="str">
@@ -6953,7 +6956,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F19" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="69" t="n">
@@ -6965,7 +6968,7 @@
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="I19" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J19" s="69" t="n">
@@ -6973,35 +6976,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K19" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))</x:f>
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="L19" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M19" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N19" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>1404.3428571428572</x:v>
       </x:c>
       <x:c r="O19" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="P19" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q19" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="R19" s="21" t="str">
-        <x:f>IF(O19&gt;P19,"compute",IF(P19&gt;O19,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O19&gt;P19,"compute",IF(P19&gt;O19,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S19" s="24" t="str">
@@ -7010,7 +7013,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="21" t="str">
@@ -7026,7 +7029,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F20" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="69" t="n">
@@ -7038,7 +7041,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I20" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J20" s="69" t="n">
@@ -7046,35 +7049,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K20" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L20" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M20" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N20" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>256.15625</x:v>
       </x:c>
       <x:c r="O20" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.895109443549691</x:v>
       </x:c>
       <x:c r="P20" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q20" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R20" s="21" t="str">
-        <x:f>IF(O20&gt;P20,"compute",IF(P20&gt;O20,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O20&gt;P20,"compute",IF(P20&gt;O20,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S20" s="24" t="str">
@@ -7083,7 +7086,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="21" t="str">
@@ -7099,11 +7102,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F21" s="66" t="n">
-        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="69" t="n">
@@ -7115,39 +7118,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J21" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K21" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="L21" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="M21" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N21" s="66" t="n">
-        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(0))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O21" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P21" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="Q21" s="66" t="n">
-        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$49))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$49))))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="R21" s="21" t="str">
-        <x:f>IF(O21&gt;P21,"compute",IF(P21&gt;O21,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O21&gt;P21,"compute",IF(P21&gt;O21,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S21" s="24" t="str">
@@ -7156,7 +7159,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="21" t="str">
@@ -7172,7 +7175,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F22" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="69" t="n">
@@ -7184,7 +7187,7 @@
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="I22" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="69" t="n">
@@ -7192,35 +7195,35 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K22" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))</x:f>
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="L22" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M22" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N22" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.599926766752</x:v>
       </x:c>
       <x:c r="O22" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P22" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.8013976835820895</x:v>
       </x:c>
       <x:c r="Q22" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R22" s="21" t="str">
-        <x:f>IF(O22&gt;P22,"compute",IF(P22&gt;O22,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O22&gt;P22,"compute",IF(P22&gt;O22,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S22" s="24" t="str">
@@ -7229,7 +7232,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="21" t="str">
@@ -7245,7 +7248,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F23" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="69" t="n">
@@ -7257,7 +7260,7 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I23" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="69" t="n">
@@ -7265,35 +7268,35 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K23" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L23" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M23" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N23" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16387.999633833762</x:v>
       </x:c>
       <x:c r="O23" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P23" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.1602795367164179</x:v>
       </x:c>
       <x:c r="Q23" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R23" s="21" t="str">
-        <x:f>IF(O23&gt;P23,"compute",IF(P23&gt;O23,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O23&gt;P23,"compute",IF(P23&gt;O23,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S23" s="24" t="str">
@@ -7302,7 +7305,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
@@ -7318,7 +7321,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F24" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="69" t="n">
@@ -7330,7 +7333,7 @@
         <x:v>1073807360</x:v>
       </x:c>
       <x:c r="I24" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J24" s="69" t="n">
@@ -7338,35 +7341,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K24" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))</x:f>
         <x:v>1073807360</x:v>
       </x:c>
       <x:c r="L24" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M24" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N24" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>910.3394926528924</x:v>
       </x:c>
       <x:c r="O24" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.891853944180331</x:v>
       </x:c>
       <x:c r="P24" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.885012097910448</x:v>
       </x:c>
       <x:c r="Q24" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.891853944180331</x:v>
       </x:c>
       <x:c r="R24" s="21" t="str">
-        <x:f>IF(O24&gt;P24,"compute",IF(P24&gt;O24,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O24&gt;P24,"compute",IF(P24&gt;O24,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S24" s="24" t="str">
@@ -7375,7 +7378,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="21" t="str">
@@ -7391,7 +7394,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F25" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="69" t="n">
@@ -7403,7 +7406,7 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="I25" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J25" s="69" t="n">
@@ -7411,35 +7414,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K25" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="L25" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M25" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N25" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>512.1874847430734</x:v>
       </x:c>
       <x:c r="O25" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.894024409559847</x:v>
       </x:c>
       <x:c r="P25" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="Q25" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.894024409559847</x:v>
       </x:c>
       <x:c r="R25" s="21" t="str">
-        <x:f>IF(O25&gt;P25,"compute",IF(P25&gt;O25,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O25&gt;P25,"compute",IF(P25&gt;O25,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S25" s="24" t="str">
@@ -7448,7 +7451,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="21" t="str">
@@ -7464,11 +7467,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F26" s="66" t="n">
-        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="69" t="n">
@@ -7480,39 +7483,39 @@
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="J26" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K26" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="L26" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="M26" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N26" s="66" t="n">
-        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(0))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O26" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P26" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.5644725874626864</x:v>
       </x:c>
       <x:c r="Q26" s="66" t="n">
-        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$50))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$50))))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5644725874626864</x:v>
       </x:c>
       <x:c r="R26" s="21" t="str">
-        <x:f>IF(O26&gt;P26,"compute",IF(P26&gt;O26,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O26&gt;P26,"compute",IF(P26&gt;O26,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S26" s="24" t="str">
@@ -7521,7 +7524,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="21" t="str">
@@ -7537,7 +7540,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F27" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G27" s="69" t="n">
@@ -7549,7 +7552,7 @@
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="I27" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="69" t="n">
@@ -7557,35 +7560,35 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K27" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))</x:f>
         <x:v>2684616704</x:v>
       </x:c>
       <x:c r="L27" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M27" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N27" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.599926766752</x:v>
       </x:c>
       <x:c r="O27" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P27" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.8013976835820895</x:v>
       </x:c>
       <x:c r="Q27" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R27" s="21" t="str">
-        <x:f>IF(O27&gt;P27,"compute",IF(P27&gt;O27,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O27&gt;P27,"compute",IF(P27&gt;O27,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S27" s="24" t="str">
@@ -7594,7 +7597,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="21" t="str">
@@ -7610,7 +7613,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F28" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="69" t="n">
@@ -7622,7 +7625,7 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I28" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="69" t="n">
@@ -7630,35 +7633,35 @@
         <x:v>65536</x:v>
       </x:c>
       <x:c r="K28" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L28" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="M28" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N28" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16387.999633833762</x:v>
       </x:c>
       <x:c r="O28" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="P28" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.1602795367164179</x:v>
       </x:c>
       <x:c r="Q28" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.892939176870089</x:v>
       </x:c>
       <x:c r="R28" s="21" t="str">
-        <x:f>IF(O28&gt;P28,"compute",IF(P28&gt;O28,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O28&gt;P28,"compute",IF(P28&gt;O28,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S28" s="24" t="str">
@@ -7667,7 +7670,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="21" t="str">
@@ -7683,7 +7686,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F29" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="69" t="n">
@@ -7695,7 +7698,7 @@
         <x:v>1073807360</x:v>
       </x:c>
       <x:c r="I29" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="69" t="n">
@@ -7703,35 +7706,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K29" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))</x:f>
         <x:v>1073807360</x:v>
       </x:c>
       <x:c r="L29" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M29" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N29" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>910.3394926528924</x:v>
       </x:c>
       <x:c r="O29" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.891853944180331</x:v>
       </x:c>
       <x:c r="P29" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.885012097910448</x:v>
       </x:c>
       <x:c r="Q29" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.891853944180331</x:v>
       </x:c>
       <x:c r="R29" s="21" t="str">
-        <x:f>IF(O29&gt;P29,"compute",IF(P29&gt;O29,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O29&gt;P29,"compute",IF(P29&gt;O29,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S29" s="24" t="str">
@@ -7740,7 +7743,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="21" t="str">
@@ -7756,7 +7759,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F30" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="69" t="n">
@@ -7768,7 +7771,7 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="I30" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="69" t="n">
@@ -7776,35 +7779,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K30" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="L30" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M30" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N30" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>512.1874847430734</x:v>
       </x:c>
       <x:c r="O30" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.894024409559847</x:v>
       </x:c>
       <x:c r="P30" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="Q30" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.894024409559847</x:v>
       </x:c>
       <x:c r="R30" s="21" t="str">
-        <x:f>IF(O30&gt;P30,"compute",IF(P30&gt;O30,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O30&gt;P30,"compute",IF(P30&gt;O30,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S30" s="24" t="str">
@@ -7813,7 +7816,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="21" t="str">
@@ -7829,11 +7832,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F31" s="66" t="n">
-        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="69" t="n">
@@ -7845,39 +7848,39 @@
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="J31" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K31" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="L31" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="M31" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N31" s="66" t="n">
-        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(0))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O31" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P31" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.5644725874626864</x:v>
       </x:c>
       <x:c r="Q31" s="66" t="n">
-        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$51))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$51))))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5644725874626864</x:v>
       </x:c>
       <x:c r="R31" s="21" t="str">
-        <x:f>IF(O31&gt;P31,"compute",IF(P31&gt;O31,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O31&gt;P31,"compute",IF(P31&gt;O31,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S31" s="24" t="str">
@@ -7886,7 +7889,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="21" t="str">
@@ -7902,7 +7905,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F32" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G32" s="69" t="n">
@@ -7914,7 +7917,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I32" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="69" t="n">
@@ -7922,35 +7925,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K32" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L32" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M32" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N32" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3277.3</x:v>
       </x:c>
       <x:c r="O32" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P32" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q32" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R32" s="21" t="str">
-        <x:f>IF(O32&gt;P32,"compute",IF(P32&gt;O32,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O32&gt;P32,"compute",IF(P32&gt;O32,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S32" s="24" t="str">
@@ -7959,7 +7962,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="21" t="str">
@@ -7975,7 +7978,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F33" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="69" t="n">
@@ -7987,7 +7990,7 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="I33" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="69" t="n">
@@ -7995,35 +7998,35 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K33" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="L33" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M33" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N33" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O33" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="P33" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.3205199474626865</x:v>
       </x:c>
       <x:c r="Q33" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.78208013867598</x:v>
       </x:c>
       <x:c r="R33" s="21" t="str">
-        <x:f>IF(O33&gt;P33,"compute",IF(P33&gt;O33,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O33&gt;P33,"compute",IF(P33&gt;O33,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S33" s="24" t="str">
@@ -8032,7 +8035,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="21" t="str">
@@ -8048,7 +8051,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F34" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="69" t="n">
@@ -8060,7 +8063,7 @@
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="I34" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" s="69" t="n">
@@ -8068,35 +8071,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K34" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))</x:f>
         <x:v>1610612736</x:v>
       </x:c>
       <x:c r="L34" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M34" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N34" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>1404.3428571428572</x:v>
       </x:c>
       <x:c r="O34" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="P34" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.609099080597015</x:v>
       </x:c>
       <x:c r="Q34" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>26.66905083380227</x:v>
       </x:c>
       <x:c r="R34" s="21" t="str">
-        <x:f>IF(O34&gt;P34,"compute",IF(P34&gt;O34,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O34&gt;P34,"compute",IF(P34&gt;O34,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S34" s="24" t="str">
@@ -8105,7 +8108,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="21" t="str">
@@ -8121,7 +8124,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F35" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="69" t="n">
@@ -8133,7 +8136,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I35" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="69" t="n">
@@ -8141,35 +8144,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K35" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L35" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M35" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N35" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>256.15625</x:v>
       </x:c>
       <x:c r="O35" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.895109443549691</x:v>
       </x:c>
       <x:c r="P35" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q35" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R35" s="21" t="str">
-        <x:f>IF(O35&gt;P35,"compute",IF(P35&gt;O35,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O35&gt;P35,"compute",IF(P35&gt;O35,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S35" s="24" t="str">
@@ -8178,7 +8181,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="21" t="str">
@@ -8194,11 +8197,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F36" s="66" t="n">
-        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52)))</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G36" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="69" t="n">
@@ -8210,39 +8213,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J36" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K36" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="L36" s="69" t="n">
-        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="M36" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N36" s="66" t="n">
-        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(0))/((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O36" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P36" s="66" t="n">
-        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="Q36" s="66" t="n">
-        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((INT((('01_Inputs'!$C$40)+('01_Inputs'!$C$6))/('01_Inputs'!$E$52))-INT(('01_Inputs'!$C$40)/('01_Inputs'!$E$52))))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.128319159402984</x:v>
       </x:c>
       <x:c r="R36" s="21" t="str">
-        <x:f>IF(O36&gt;P36,"compute",IF(P36&gt;O36,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O36&gt;P36,"compute",IF(P36&gt;O36,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S36" s="24" t="str">
@@ -8251,7 +8254,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="21" t="str">
@@ -8267,7 +8270,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F37" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="69" t="n">
@@ -8279,7 +8282,7 @@
         <x:v>2684354560</x:v>
       </x:c>
       <x:c r="I37" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="69" t="n">
@@ -8287,11 +8290,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K37" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))</x:f>
         <x:v>2684354560</x:v>
       </x:c>
       <x:c r="L37" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M37" s="69" t="n">
@@ -8299,23 +8302,23 @@
         <x:v>2147483648</x:v>
       </x:c>
       <x:c r="N37" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57))))))/(((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2730.6666666666665</x:v>
       </x:c>
       <x:c r="O37" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="P37" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.9615598423880597</x:v>
       </x:c>
       <x:c r="Q37" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>8.889683611267422</x:v>
       </x:c>
       <x:c r="R37" s="21" t="str">
-        <x:f>IF(O37&gt;P37,"compute",IF(P37&gt;O37,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O37&gt;P37,"compute",IF(P37&gt;O37,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S37" s="24" t="str">
@@ -8324,7 +8327,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="21" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="21" t="str">
@@ -8340,7 +8343,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F38" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="69" t="n">
@@ -8352,7 +8355,7 @@
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="I38" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="69" t="n">
@@ -8360,11 +8363,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K38" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))</x:f>
         <x:v>4831838208</x:v>
       </x:c>
       <x:c r="L38" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M38" s="69" t="n">
@@ -8372,23 +8375,23 @@
         <x:v>4294967296</x:v>
       </x:c>
       <x:c r="N38" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58))))))/(((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3276.8</x:v>
       </x:c>
       <x:c r="O38" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="P38" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.6025997373134329</x:v>
       </x:c>
       <x:c r="Q38" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>17.779367222534844</x:v>
       </x:c>
       <x:c r="R38" s="21" t="str">
-        <x:f>IF(O38&gt;P38,"compute",IF(P38&gt;O38,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O38&gt;P38,"compute",IF(P38&gt;O38,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S38" s="24" t="str">
@@ -8397,7 +8400,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="22" t="n">
-        <x:f>ROW()-5+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-5</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="22" t="str">
@@ -8413,7 +8416,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F39" s="67" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="70" t="n">
@@ -8425,7 +8428,7 @@
         <x:v>9126805504</x:v>
       </x:c>
       <x:c r="I39" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="70" t="n">
@@ -8433,11 +8436,11 @@
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="K39" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))</x:f>
         <x:v>9126805504</x:v>
       </x:c>
       <x:c r="L39" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))</x:f>
         <x:v>536870912</x:v>
       </x:c>
       <x:c r="M39" s="70" t="n">
@@ -8445,23 +8448,23 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="N39" s="67" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59))))))/(((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>3640.8888888888887</x:v>
       </x:c>
       <x:c r="O39" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>35.55873444506969</x:v>
       </x:c>
       <x:c r="P39" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.884679527164179</x:v>
       </x:c>
       <x:c r="Q39" s="67" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$6)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>35.55873444506969</x:v>
       </x:c>
       <x:c r="R39" s="22" t="str">
-        <x:f>IF(O39&gt;P39,"compute",IF(P39&gt;O39,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O39&gt;P39,"compute",IF(P39&gt;O39,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S39" s="25" t="str">
@@ -8575,59 +8578,59 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="63" t="n">
-        <x:f>SUM(G12:G45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(G12:G45)</x:f>
         <x:v>206193819968</x:v>
       </x:c>
       <x:c r="B3" s="63" t="n">
-        <x:f>SUM(K12:K45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K12:K45)</x:f>
         <x:v>118207021632</x:v>
       </x:c>
       <x:c r="C3" s="63" t="n">
-        <x:f>SUM(L12:L45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(L12:L45)</x:f>
         <x:v>137463333568</x:v>
       </x:c>
       <x:c r="D3" s="63" t="n">
-        <x:f>SUM(K12:L45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K12:L45)</x:f>
         <x:v>255670355200</x:v>
       </x:c>
       <x:c r="E3" s="63" t="n">
-        <x:f>SUM(M12:M45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M12:M45)</x:f>
         <x:v>100934352896</x:v>
       </x:c>
       <x:c r="F3" s="64" t="n">
-        <x:f>IF(SUM(K12:L45)=0,"",SUM(G12:G45)/SUM(K12:L45)+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(SUM(K12:L45)=0,"",SUM(G12:G45)/SUM(K12:L45))</x:f>
         <x:v>0.806483097372409</x:v>
       </x:c>
       <x:c r="G3" s="64" t="n">
-        <x:f>SUM(O12:O45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(O12:O45)</x:f>
         <x:v>0.20838772594676758</x:v>
       </x:c>
       <x:c r="H3" s="64" t="n">
-        <x:f>SUM(P12:P45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(P12:P45)</x:f>
         <x:v>76.31950901492539</x:v>
       </x:c>
       <x:c r="I3" s="64" t="n">
-        <x:f>MAX(SUM(O12:O45),SUM(P12:P45))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>MAX(SUM(O12:O45),SUM(P12:P45))</x:f>
         <x:v>76.31950901492539</x:v>
       </x:c>
       <x:c r="J3" s="64" t="n">
-        <x:f>SUM(Q12:Q45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q12:Q45)</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="K3" s="62" t="str">
-        <x:f>IF(SUM(O12:O45)&gt;SUM(P12:P45),"compute",IF(SUM(P12:P45)&gt;SUM(O12:O45),"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(O12:O45)&gt;SUM(P12:P45),"compute",IF(SUM(P12:P45)&gt;SUM(O12:O45),"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="L3" s="62" t="str">
-        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
       <x:c r="M3" s="64" t="n">
-        <x:f>'02_HW'!$C$6/'02_HW'!$C$7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'02_HW'!$C$6/'02_HW'!$C$7</x:f>
         <x:v>295.36477611940296</x:v>
       </x:c>
       <x:c r="N3" s="62" t="str">
-        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(F3&gt;=M3,"compute-side","memory-side")</x:f>
         <x:v>memory-side</x:v>
       </x:c>
       <x:c r="O3" s="72"/>
@@ -8658,19 +8661,19 @@
         <x:v>normal</x:v>
       </x:c>
       <x:c r="B6" s="65" t="n">
-        <x:f>SUM(Q12:Q45)-(Q22+Q27+Q32+Q37+Q42)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q12:Q45)-(Q22+Q27+Q32+Q37+Q42)</x:f>
         <x:v>76.34359890613672</x:v>
       </x:c>
       <x:c r="C6" s="73" t="n">
-        <x:f>SUM(K12:L45)-((K22+L22)+(K27+L27)+(K32+L32)+(K37+L37)+(K42+L42))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K12:L45)-((K22+L22)+(K27+L27)+(K32+L32)+(K37+L37)+(K42+L42))</x:f>
         <x:v>255636799744</x:v>
       </x:c>
       <x:c r="D6" s="73" t="n">
-        <x:f>SUM(M12:M45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M12:M45)</x:f>
         <x:v>100934352896</x:v>
       </x:c>
       <x:c r="E6" s="20" t="str">
-        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
     </x:row>
@@ -8679,19 +8682,19 @@
         <x:v>boundary</x:v>
       </x:c>
       <x:c r="B7" s="66" t="n">
-        <x:f>SUM(Q12:Q45)-(Q22+Q27+Q32+Q37+Q42)+(Q22*('01_Inputs'!$E$48)+Q27*('01_Inputs'!$E$49)+Q32*('01_Inputs'!$E$50)+Q37*('01_Inputs'!$E$51)+Q42*('01_Inputs'!$E$52))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q12:Q45)-(Q22+Q27+Q32+Q37+Q42)+(Q22*('01_Inputs'!$E$48)+Q27*('01_Inputs'!$E$49)+Q32*('01_Inputs'!$E$50)+Q37*('01_Inputs'!$E$51)+Q42*('01_Inputs'!$E$52))</x:f>
         <x:v>96.85750155927104</x:v>
       </x:c>
       <x:c r="C7" s="74" t="n">
-        <x:f>SUM(K12:L45)-((K22+L22)+(K27+L27)+(K32+L32)+(K37+L37)+(K42+L42))+((K22+L22)*('01_Inputs'!$E$48)+(K27+L27)*('01_Inputs'!$E$49)+(K32+L32)*('01_Inputs'!$E$50)+(K37+L37)*('01_Inputs'!$E$51)+(K42+L42)*('01_Inputs'!$E$52))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K12:L45)-((K22+L22)+(K27+L27)+(K32+L32)+(K37+L37)+(K42+L42))+((K22+L22)*('01_Inputs'!$E$48)+(K27+L27)*('01_Inputs'!$E$49)+(K32+L32)*('01_Inputs'!$E$50)+(K37+L37)*('01_Inputs'!$E$51)+(K42+L42)*('01_Inputs'!$E$52))</x:f>
         <x:v>324358373632</x:v>
       </x:c>
       <x:c r="D7" s="74" t="n">
-        <x:f>SUM(M12:M45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M12:M45)</x:f>
         <x:v>100934352896</x:v>
       </x:c>
       <x:c r="E7" s="21" t="str">
-        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
     </x:row>
@@ -8700,19 +8703,19 @@
         <x:v>amortized</x:v>
       </x:c>
       <x:c r="B8" s="67" t="n">
-        <x:f>SUM(Q12:Q45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(Q12:Q45)</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="C8" s="75" t="n">
-        <x:f>SUM(K12:L45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(K12:L45)</x:f>
         <x:v>255670355200</x:v>
       </x:c>
       <x:c r="D8" s="75" t="n">
-        <x:f>SUM(M12:M45)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(M12:M45)</x:f>
         <x:v>100934352896</x:v>
       </x:c>
       <x:c r="E8" s="22" t="str">
-        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(SUM(M12:M45)&lt;='02_HW'!$C$8,"FIT","EXCEEDS")</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
     </x:row>
@@ -8777,7 +8780,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="20" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="20" t="str">
@@ -8793,7 +8796,7 @@
         <x:v>2ND²</x:v>
       </x:c>
       <x:c r="F12" s="65" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G12" s="68" t="n">
@@ -8805,7 +8808,7 @@
         <x:v>67371008</x:v>
       </x:c>
       <x:c r="I12" s="68" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="68" t="n">
@@ -8813,11 +8816,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K12" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))</x:f>
         <x:v>67371008</x:v>
       </x:c>
       <x:c r="L12" s="68" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M12" s="68" t="n">
@@ -8825,23 +8828,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="65" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>63.50387596899225</x:v>
       </x:c>
       <x:c r="O12" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004340665825814171</x:v>
       </x:c>
       <x:c r="P12" s="65" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="Q12" s="65" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="R12" s="20" t="str">
-        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O12&gt;P12,"compute",IF(P12&gt;O12,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S12" s="23" t="str">
@@ -8850,7 +8853,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="21" t="str">
@@ -8866,7 +8869,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F13" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G13" s="69" t="n">
@@ -8878,7 +8881,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I13" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J13" s="69" t="n">
@@ -8886,11 +8889,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L13" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M13" s="69" t="n">
@@ -8898,23 +8901,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N13" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P13" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q13" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R13" s="21" t="str">
-        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O13&gt;P13,"compute",IF(P13&gt;O13,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S13" s="24" t="str">
@@ -8923,7 +8926,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
@@ -8939,7 +8942,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F14" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G14" s="69" t="n">
@@ -8951,7 +8954,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I14" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="69" t="n">
@@ -8959,11 +8962,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L14" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M14" s="69" t="n">
@@ -8971,23 +8974,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N14" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P14" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q14" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R14" s="21" t="str">
-        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O14&gt;P14,"compute",IF(P14&gt;O14,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S14" s="24" t="str">
@@ -8996,7 +8999,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
@@ -9012,7 +9015,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F15" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G15" s="69" t="n">
@@ -9024,7 +9027,7 @@
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="I15" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J15" s="69" t="n">
@@ -9032,11 +9035,11 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))</x:f>
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="L15" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M15" s="69" t="n">
@@ -9044,23 +9047,23 @@
         <x:v>10738728960</x:v>
       </x:c>
       <x:c r="N15" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.0002440661337437</x:v>
       </x:c>
       <x:c r="O15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P15" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="Q15" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="R15" s="21" t="str">
-        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O15&gt;P15,"compute",IF(P15&gt;O15,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S15" s="24" t="str">
@@ -9069,7 +9072,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="B16" s="21" t="str">
@@ -9085,7 +9088,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F16" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G16" s="69" t="n">
@@ -9097,7 +9100,7 @@
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="I16" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="69" t="n">
@@ -9105,11 +9108,11 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))</x:f>
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="L16" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M16" s="69" t="n">
@@ -9117,23 +9120,23 @@
         <x:v>10738728960</x:v>
       </x:c>
       <x:c r="N16" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.0002440661337437</x:v>
       </x:c>
       <x:c r="O16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P16" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="Q16" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="R16" s="21" t="str">
-        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O16&gt;P16,"compute",IF(P16&gt;O16,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S16" s="24" t="str">
@@ -9142,7 +9145,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
@@ -9158,7 +9161,7 @@
         <x:v>2NP + nonlinear terms</x:v>
       </x:c>
       <x:c r="F17" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G17" s="69" t="n">
@@ -9170,7 +9173,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I17" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="69" t="n">
@@ -9178,11 +9181,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L17" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M17" s="69" t="n">
@@ -9190,23 +9193,23 @@
         <x:v>21474836480</x:v>
       </x:c>
       <x:c r="N17" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P17" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q17" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R17" s="21" t="str">
-        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O17&gt;P17,"compute",IF(P17&gt;O17,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S17" s="24" t="str">
@@ -9215,7 +9218,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="21" t="str">
@@ -9231,7 +9234,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F18" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="69" t="n">
@@ -9243,7 +9246,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I18" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="69" t="n">
@@ -9251,35 +9254,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K18" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L18" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M18" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N18" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O18" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P18" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q18" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R18" s="21" t="str">
-        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O18&gt;P18,"compute",IF(P18&gt;O18,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S18" s="24" t="str">
@@ -9288,7 +9291,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="21" t="str">
@@ -9304,7 +9307,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F19" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="69" t="n">
@@ -9316,7 +9319,7 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I19" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J19" s="69" t="n">
@@ -9324,35 +9327,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K19" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L19" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M19" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N19" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O19" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P19" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="Q19" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="R19" s="21" t="str">
-        <x:f>IF(O19&gt;P19,"compute",IF(P19&gt;O19,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O19&gt;P19,"compute",IF(P19&gt;O19,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S19" s="24" t="str">
@@ -9361,7 +9364,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="21" t="str">
@@ -9377,7 +9380,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F20" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G20" s="69" t="n">
@@ -9389,7 +9392,7 @@
         <x:v>786432</x:v>
       </x:c>
       <x:c r="I20" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J20" s="69" t="n">
@@ -9397,35 +9400,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K20" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))</x:f>
         <x:v>786432</x:v>
       </x:c>
       <x:c r="L20" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M20" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N20" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.7499656692961443</x:v>
       </x:c>
       <x:c r="O20" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.013021997477442515</x:v>
       </x:c>
       <x:c r="P20" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="Q20" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="R20" s="21" t="str">
-        <x:f>IF(O20&gt;P20,"compute",IF(P20&gt;O20,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O20&gt;P20,"compute",IF(P20&gt;O20,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S20" s="24" t="str">
@@ -9434,7 +9437,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="B21" s="21" t="str">
@@ -9450,7 +9453,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F21" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G21" s="69" t="n">
@@ -9462,7 +9465,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I21" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J21" s="69" t="n">
@@ -9470,35 +9473,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K21" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L21" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M21" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N21" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.1250762939453125</x:v>
       </x:c>
       <x:c r="O21" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0043433151579832475</x:v>
       </x:c>
       <x:c r="P21" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q21" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$48)+('01_Inputs'!$C$38)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R21" s="21" t="str">
-        <x:f>IF(O21&gt;P21,"compute",IF(P21&gt;O21,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O21&gt;P21,"compute",IF(P21&gt;O21,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S21" s="24" t="str">
@@ -9507,7 +9510,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="21" t="str">
@@ -9523,11 +9526,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F22" s="66" t="n">
-        <x:f>(1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(1/('01_Inputs'!$E$48))</x:f>
         <x:v>0.00048828125</x:v>
       </x:c>
       <x:c r="G22" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="69" t="n">
@@ -9539,39 +9542,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J22" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K22" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$48)))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="L22" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="M22" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N22" s="66" t="n">
-        <x:f>IF((((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((1/('01_Inputs'!$E$48)))*(0))/((((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O22" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P22" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="Q22" s="66" t="n">
-        <x:f>(MAX((((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="R22" s="21" t="str">
-        <x:f>IF(O22&gt;P22,"compute",IF(P22&gt;O22,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O22&gt;P22,"compute",IF(P22&gt;O22,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S22" s="24" t="str">
@@ -9580,7 +9583,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="B23" s="21" t="str">
@@ -9596,7 +9599,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F23" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="69" t="n">
@@ -9608,7 +9611,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I23" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="69" t="n">
@@ -9616,35 +9619,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K23" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L23" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M23" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N23" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O23" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P23" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q23" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R23" s="21" t="str">
-        <x:f>IF(O23&gt;P23,"compute",IF(P23&gt;O23,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O23&gt;P23,"compute",IF(P23&gt;O23,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S23" s="24" t="str">
@@ -9653,7 +9656,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="21" t="str">
@@ -9669,7 +9672,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F24" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="69" t="n">
@@ -9681,7 +9684,7 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I24" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J24" s="69" t="n">
@@ -9689,35 +9692,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K24" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L24" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M24" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N24" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O24" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P24" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="Q24" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="R24" s="21" t="str">
-        <x:f>IF(O24&gt;P24,"compute",IF(P24&gt;O24,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O24&gt;P24,"compute",IF(P24&gt;O24,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S24" s="24" t="str">
@@ -9726,7 +9729,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="21" t="str">
@@ -9742,7 +9745,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F25" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G25" s="69" t="n">
@@ -9754,7 +9757,7 @@
         <x:v>786432</x:v>
       </x:c>
       <x:c r="I25" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J25" s="69" t="n">
@@ -9762,35 +9765,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K25" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))</x:f>
         <x:v>786432</x:v>
       </x:c>
       <x:c r="L25" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M25" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N25" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.7499656692961443</x:v>
       </x:c>
       <x:c r="O25" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.013021997477442515</x:v>
       </x:c>
       <x:c r="P25" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="Q25" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="R25" s="21" t="str">
-        <x:f>IF(O25&gt;P25,"compute",IF(P25&gt;O25,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O25&gt;P25,"compute",IF(P25&gt;O25,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S25" s="24" t="str">
@@ -9799,7 +9802,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>15</x:v>
       </x:c>
       <x:c r="B26" s="21" t="str">
@@ -9815,7 +9818,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F26" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="69" t="n">
@@ -9827,7 +9830,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I26" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="69" t="n">
@@ -9835,35 +9838,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K26" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L26" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M26" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N26" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.1250762939453125</x:v>
       </x:c>
       <x:c r="O26" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0043433151579832475</x:v>
       </x:c>
       <x:c r="P26" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q26" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$49)+('01_Inputs'!$C$38)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R26" s="21" t="str">
-        <x:f>IF(O26&gt;P26,"compute",IF(P26&gt;O26,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O26&gt;P26,"compute",IF(P26&gt;O26,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S26" s="24" t="str">
@@ -9872,7 +9875,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="21" t="str">
@@ -9888,11 +9891,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F27" s="66" t="n">
-        <x:f>(1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(1/('01_Inputs'!$E$49))</x:f>
         <x:v>0.00048828125</x:v>
       </x:c>
       <x:c r="G27" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="69" t="n">
@@ -9904,39 +9907,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J27" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K27" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$49)))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="L27" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="M27" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N27" s="66" t="n">
-        <x:f>IF((((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((1/('01_Inputs'!$E$49)))*(0))/((((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O27" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P27" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="Q27" s="66" t="n">
-        <x:f>(MAX((((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="R27" s="21" t="str">
-        <x:f>IF(O27&gt;P27,"compute",IF(P27&gt;O27,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O27&gt;P27,"compute",IF(P27&gt;O27,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S27" s="24" t="str">
@@ -9945,7 +9948,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="21" t="str">
@@ -9961,7 +9964,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F28" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="69" t="n">
@@ -9973,7 +9976,7 @@
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="I28" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="69" t="n">
@@ -9981,35 +9984,35 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K28" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))</x:f>
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="L28" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M28" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N28" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.0002440661337437</x:v>
       </x:c>
       <x:c r="O28" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P28" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="Q28" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="R28" s="21" t="str">
-        <x:f>IF(O28&gt;P28,"compute",IF(P28&gt;O28,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O28&gt;P28,"compute",IF(P28&gt;O28,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S28" s="24" t="str">
@@ -10018,7 +10021,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="21" t="str">
@@ -10034,7 +10037,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F29" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G29" s="69" t="n">
@@ -10046,7 +10049,7 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I29" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="69" t="n">
@@ -10054,35 +10057,35 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K29" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L29" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M29" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N29" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16387.999633833762</x:v>
       </x:c>
       <x:c r="O29" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P29" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.00007826149253731343</x:v>
       </x:c>
       <x:c r="Q29" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="R29" s="21" t="str">
-        <x:f>IF(O29&gt;P29,"compute",IF(P29&gt;O29,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O29&gt;P29,"compute",IF(P29&gt;O29,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S29" s="24" t="str">
@@ -10091,7 +10094,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="21" t="str">
@@ -10107,7 +10110,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F30" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="69" t="n">
@@ -10119,7 +10122,7 @@
         <x:v>524320</x:v>
       </x:c>
       <x:c r="I30" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="69" t="n">
@@ -10127,35 +10130,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K30" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))</x:f>
         <x:v>524320</x:v>
       </x:c>
       <x:c r="L30" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M30" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N30" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.5000305101287947</x:v>
       </x:c>
       <x:c r="O30" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0043417255586818025</x:v>
       </x:c>
       <x:c r="P30" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.5646291008955227</x:v>
       </x:c>
       <x:c r="Q30" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5646291008955227</x:v>
       </x:c>
       <x:c r="R30" s="21" t="str">
-        <x:f>IF(O30&gt;P30,"compute",IF(P30&gt;O30,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O30&gt;P30,"compute",IF(P30&gt;O30,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S30" s="24" t="str">
@@ -10164,7 +10167,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="21" t="str">
@@ -10180,7 +10183,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F31" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="69" t="n">
@@ -10192,7 +10195,7 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="I31" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J31" s="69" t="n">
@@ -10200,35 +10203,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K31" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="L31" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M31" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N31" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.2500915452847038</x:v>
       </x:c>
       <x:c r="O31" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342785356230394</x:v>
       </x:c>
       <x:c r="P31" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="Q31" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$50)+('01_Inputs'!$C$38)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="R31" s="21" t="str">
-        <x:f>IF(O31&gt;P31,"compute",IF(P31&gt;O31,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O31&gt;P31,"compute",IF(P31&gt;O31,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S31" s="24" t="str">
@@ -10237,7 +10240,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>21</x:v>
       </x:c>
       <x:c r="B32" s="21" t="str">
@@ -10253,11 +10256,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F32" s="66" t="n">
-        <x:f>(1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(1/('01_Inputs'!$E$50))</x:f>
         <x:v>0.00048828125</x:v>
       </x:c>
       <x:c r="G32" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="69" t="n">
@@ -10269,39 +10272,39 @@
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="J32" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K32" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$50)))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>2097408</x:v>
       </x:c>
       <x:c r="L32" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>2097408</x:v>
       </x:c>
       <x:c r="M32" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N32" s="66" t="n">
-        <x:f>IF((((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((1/('01_Inputs'!$E$50)))*(0))/((((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O32" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P32" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0012521838805970148</x:v>
       </x:c>
       <x:c r="Q32" s="66" t="n">
-        <x:f>(MAX((((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0012521838805970148</x:v>
       </x:c>
       <x:c r="R32" s="21" t="str">
-        <x:f>IF(O32&gt;P32,"compute",IF(P32&gt;O32,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O32&gt;P32,"compute",IF(P32&gt;O32,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S32" s="24" t="str">
@@ -10310,7 +10313,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>22</x:v>
       </x:c>
       <x:c r="B33" s="21" t="str">
@@ -10326,7 +10329,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F33" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G33" s="69" t="n">
@@ -10338,7 +10341,7 @@
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="I33" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="69" t="n">
@@ -10346,35 +10349,35 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K33" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))</x:f>
         <x:v>2148007936</x:v>
       </x:c>
       <x:c r="L33" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M33" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N33" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.0002440661337437</x:v>
       </x:c>
       <x:c r="O33" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P33" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="Q33" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6411964083582089</x:v>
       </x:c>
       <x:c r="R33" s="21" t="str">
-        <x:f>IF(O33&gt;P33,"compute",IF(P33&gt;O33,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O33&gt;P33,"compute",IF(P33&gt;O33,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S33" s="24" t="str">
@@ -10383,7 +10386,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="21" t="str">
@@ -10399,7 +10402,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F34" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="69" t="n">
@@ -10411,7 +10414,7 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I34" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" s="69" t="n">
@@ -10419,35 +10422,35 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="K34" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L34" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="M34" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N34" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16387.999633833762</x:v>
       </x:c>
       <x:c r="O34" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="P34" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.00007826149253731343</x:v>
       </x:c>
       <x:c r="Q34" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.004342255457456098</x:v>
       </x:c>
       <x:c r="R34" s="21" t="str">
-        <x:f>IF(O34&gt;P34,"compute",IF(P34&gt;O34,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O34&gt;P34,"compute",IF(P34&gt;O34,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S34" s="24" t="str">
@@ -10456,7 +10459,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="21" t="str">
@@ -10472,7 +10475,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F35" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G35" s="69" t="n">
@@ -10484,7 +10487,7 @@
         <x:v>524320</x:v>
       </x:c>
       <x:c r="I35" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="69" t="n">
@@ -10492,35 +10495,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K35" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))</x:f>
         <x:v>524320</x:v>
       </x:c>
       <x:c r="L35" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M35" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N35" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.5000305101287947</x:v>
       </x:c>
       <x:c r="O35" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0043417255586818025</x:v>
       </x:c>
       <x:c r="P35" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.5646291008955227</x:v>
       </x:c>
       <x:c r="Q35" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5646291008955227</x:v>
       </x:c>
       <x:c r="R35" s="21" t="str">
-        <x:f>IF(O35&gt;P35,"compute",IF(P35&gt;O35,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O35&gt;P35,"compute",IF(P35&gt;O35,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S35" s="24" t="str">
@@ -10529,7 +10532,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="21" t="str">
@@ -10545,7 +10548,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F36" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G36" s="69" t="n">
@@ -10557,7 +10560,7 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="I36" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J36" s="69" t="n">
@@ -10565,35 +10568,35 @@
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="K36" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="L36" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>8590983168</x:v>
       </x:c>
       <x:c r="M36" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N36" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.2500915452847038</x:v>
       </x:c>
       <x:c r="O36" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004342785356230394</x:v>
       </x:c>
       <x:c r="P36" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="Q36" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$51)+('01_Inputs'!$C$38)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.128945174925373</x:v>
       </x:c>
       <x:c r="R36" s="21" t="str">
-        <x:f>IF(O36&gt;P36,"compute",IF(P36&gt;O36,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O36&gt;P36,"compute",IF(P36&gt;O36,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S36" s="24" t="str">
@@ -10602,7 +10605,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="21" t="str">
@@ -10618,11 +10621,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F37" s="66" t="n">
-        <x:f>(1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(1/('01_Inputs'!$E$51))</x:f>
         <x:v>0.00048828125</x:v>
       </x:c>
       <x:c r="G37" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="69" t="n">
@@ -10634,39 +10637,39 @@
         <x:v>4295491584</x:v>
       </x:c>
       <x:c r="J37" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$51)))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>2097408</x:v>
       </x:c>
       <x:c r="L37" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>2097408</x:v>
       </x:c>
       <x:c r="M37" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N37" s="66" t="n">
-        <x:f>IF((((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((1/('01_Inputs'!$E$51)))*(0))/((((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O37" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P37" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0012521838805970148</x:v>
       </x:c>
       <x:c r="Q37" s="66" t="n">
-        <x:f>(MAX((((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0012521838805970148</x:v>
       </x:c>
       <x:c r="R37" s="21" t="str">
-        <x:f>IF(O37&gt;P37,"compute",IF(P37&gt;O37,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O37&gt;P37,"compute",IF(P37&gt;O37,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S37" s="24" t="str">
@@ -10675,7 +10678,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="21" t="str">
@@ -10691,7 +10694,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F38" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="69" t="n">
@@ -10703,7 +10706,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I38" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="69" t="n">
@@ -10711,35 +10714,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K38" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L38" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M38" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N38" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>2.000061027706579</x:v>
       </x:c>
       <x:c r="O38" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P38" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q38" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R38" s="21" t="str">
-        <x:f>IF(O38&gt;P38,"compute",IF(P38&gt;O38,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O38&gt;P38,"compute",IF(P38&gt;O38,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S38" s="24" t="str">
@@ -10748,7 +10751,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="B39" s="21" t="str">
@@ -10764,7 +10767,7 @@
         <x:v>Ffwd(N)</x:v>
       </x:c>
       <x:c r="F39" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="69" t="n">
@@ -10776,7 +10779,7 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="I39" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="69" t="n">
@@ -10784,35 +10787,35 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K39" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="L39" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M39" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N39" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52)))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>16386.5</x:v>
       </x:c>
       <x:c r="O39" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="P39" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="Q39" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00868265631771288</x:v>
       </x:c>
       <x:c r="R39" s="21" t="str">
-        <x:f>IF(O39&gt;P39,"compute",IF(P39&gt;O39,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O39&gt;P39,"compute",IF(P39&gt;O39,"memory","balanced"))</x:f>
         <x:v>compute</x:v>
       </x:c>
       <x:c r="S39" s="24" t="str">
@@ -10821,7 +10824,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="21" t="str">
@@ -10837,7 +10840,7 @@
         <x:v>2NIH + 4NHO</x:v>
       </x:c>
       <x:c r="F40" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G40" s="69" t="n">
@@ -10849,7 +10852,7 @@
         <x:v>786432</x:v>
       </x:c>
       <x:c r="I40" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J40" s="69" t="n">
@@ -10857,35 +10860,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K40" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))</x:f>
         <x:v>786432</x:v>
       </x:c>
       <x:c r="L40" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M40" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N40" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))/((((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))/(((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.7499656692961443</x:v>
       </x:c>
       <x:c r="O40" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.013021997477442515</x:v>
       </x:c>
       <x:c r="P40" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="Q40" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$14)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.12855391522388</x:v>
       </x:c>
       <x:c r="R40" s="21" t="str">
-        <x:f>IF(O40&gt;P40,"compute",IF(P40&gt;O40,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O40&gt;P40,"compute",IF(P40&gt;O40,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S40" s="24" t="str">
@@ -10894,7 +10897,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>30</x:v>
       </x:c>
       <x:c r="B41" s="21" t="str">
@@ -10910,7 +10913,7 @@
         <x:v>μFfwd − (2Ffwd+Fbwd)</x:v>
       </x:c>
       <x:c r="F41" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G41" s="69" t="n">
@@ -10922,7 +10925,7 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="I41" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" s="69" t="n">
@@ -10930,35 +10933,35 @@
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="K41" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="L41" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))</x:f>
         <x:v>17179869184</x:v>
       </x:c>
       <x:c r="M41" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N41" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))))))/((((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))=0,"",((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))))))/(((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))))))</x:f>
         <x:v>0.1250762939453125</x:v>
       </x:c>
       <x:c r="O41" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.0043433151579832475</x:v>
       </x:c>
       <x:c r="P41" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="Q41" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+((0*'01_Inputs'!$C$5))+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*(('01_Inputs'!$C$37)*('01_Inputs'!$C$52)+('01_Inputs'!$C$38)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36)))+(0)+((('01_Inputs'!$C$5)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$36))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.256638318805969</x:v>
       </x:c>
       <x:c r="R41" s="21" t="str">
-        <x:f>IF(O41&gt;P41,"compute",IF(P41&gt;O41,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O41&gt;P41,"compute",IF(P41&gt;O41,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S41" s="24" t="str">
@@ -10967,7 +10970,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>31</x:v>
       </x:c>
       <x:c r="B42" s="21" t="str">
@@ -10983,11 +10986,11 @@
         <x:v>B(1+m)Pbs read + write</x:v>
       </x:c>
       <x:c r="F42" s="66" t="n">
-        <x:f>(1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>(1/('01_Inputs'!$E$52))</x:f>
         <x:v>0.00048828125</x:v>
       </x:c>
       <x:c r="G42" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H42" s="69" t="n">
@@ -10999,39 +11002,39 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="J42" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K42" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$52)))*((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="L42" s="69" t="n">
-        <x:f>((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))</x:f>
         <x:v>4194304</x:v>
       </x:c>
       <x:c r="M42" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="N42" s="66" t="n">
-        <x:f>IF((((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5))))=0,"",(((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5)))/((((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF((((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0)))=0,"",(((1/('01_Inputs'!$E$52)))*(0))/((((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0)))))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="O42" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="P42" s="66" t="n">
-        <x:f>(((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="Q42" s="66" t="n">
-        <x:f>(MAX((((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+((('01_Inputs'!$C$5)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$35)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0025040620895522385</x:v>
       </x:c>
       <x:c r="R42" s="21" t="str">
-        <x:f>IF(O42&gt;P42,"compute",IF(P42&gt;O42,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O42&gt;P42,"compute",IF(P42&gt;O42,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S42" s="24" t="str">
@@ -11040,7 +11043,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="B43" s="21" t="str">
@@ -11056,7 +11059,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F43" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G43" s="69" t="n">
@@ -11068,7 +11071,7 @@
         <x:v>2147745792</x:v>
       </x:c>
       <x:c r="I43" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" s="69" t="n">
@@ -11076,11 +11079,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K43" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))</x:f>
         <x:v>2147745792</x:v>
       </x:c>
       <x:c r="L43" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M43" s="69" t="n">
@@ -11088,23 +11091,23 @@
         <x:v>2147483648</x:v>
       </x:c>
       <x:c r="N43" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57))))))/(((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1.9995118379301928</x:v>
       </x:c>
       <x:c r="O43" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.004340665825814171</x:v>
       </x:c>
       <x:c r="P43" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>0.6411963988059701</x:v>
       </x:c>
       <x:c r="Q43" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$57)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$C$57)+('01_Inputs'!$C$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$57)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6411963988059701</x:v>
       </x:c>
       <x:c r="R43" s="21" t="str">
-        <x:f>IF(O43&gt;P43,"compute",IF(P43&gt;O43,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O43&gt;P43,"compute",IF(P43&gt;O43,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S43" s="24" t="str">
@@ -11113,7 +11116,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="21" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="21" t="str">
@@ -11129,7 +11132,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F44" s="66" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G44" s="69" t="n">
@@ -11141,7 +11144,7 @@
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="I44" s="69" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" s="69" t="n">
@@ -11149,11 +11152,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K44" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))</x:f>
         <x:v>4295229440</x:v>
       </x:c>
       <x:c r="L44" s="69" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M44" s="69" t="n">
@@ -11161,23 +11164,23 @@
         <x:v>4294967296</x:v>
       </x:c>
       <x:c r="N44" s="66" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58))))))/(((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1.9997558891736849</x:v>
       </x:c>
       <x:c r="O44" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.008681331651628342</x:v>
       </x:c>
       <x:c r="P44" s="66" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="Q44" s="66" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$58)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$C$58)+('01_Inputs'!$C$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$58)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2822362937313432</x:v>
       </x:c>
       <x:c r="R44" s="21" t="str">
-        <x:f>IF(O44&gt;P44,"compute",IF(P44&gt;O44,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O44&gt;P44,"compute",IF(P44&gt;O44,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S44" s="24" t="str">
@@ -11186,7 +11189,7 @@
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="22" t="n">
-        <x:f>ROW()-11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>ROW()-11</x:f>
         <x:v>34</x:v>
       </x:c>
       <x:c r="B45" s="22" t="str">
@@ -11202,7 +11205,7 @@
         <x:v>2NPℓ</x:v>
       </x:c>
       <x:c r="F45" s="67" t="n">
-        <x:f>(1+0*'01_Inputs'!$C$5)</x:f>
+        <x:f>1</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="G45" s="70" t="n">
@@ -11214,7 +11217,7 @@
         <x:v>8590196736</x:v>
       </x:c>
       <x:c r="I45" s="70" t="n">
-        <x:f>(0*'01_Inputs'!$C$5)</x:f>
+        <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J45" s="70" t="n">
@@ -11222,11 +11225,11 @@
         <x:v>262144</x:v>
       </x:c>
       <x:c r="K45" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))</x:f>
         <x:v>8590196736</x:v>
       </x:c>
       <x:c r="L45" s="70" t="n">
-        <x:f>((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>(1)*((0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="M45" s="70" t="n">
@@ -11234,23 +11237,23 @@
         <x:v>8589934592</x:v>
       </x:c>
       <x:c r="N45" s="67" t="n">
-        <x:f>IF((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))=0,"",(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59))))))/((((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))))+0*('01_Inputs'!$C$5))</x:f>
+        <x:f>IF(((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))=0,"",((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59))))))/(((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14)))))))</x:f>
         <x:v>1.9998779371376258</x:v>
       </x:c>
       <x:c r="O45" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10))</x:f>
         <x:v>0.017362663303256684</x:v>
       </x:c>
       <x:c r="P45" s="67" t="n">
-        <x:f>(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
+        <x:f>((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10))</x:f>
         <x:v>2.5643160835820895</x:v>
       </x:c>
       <x:c r="Q45" s="67" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((IF(('01_Inputs'!$H$59)=1,('01_Inputs'!$C$5),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$C$59)+('01_Inputs'!$C$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$35)+((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$14)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$D$59)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5643160835820895</x:v>
       </x:c>
       <x:c r="R45" s="22" t="str">
-        <x:f>IF(O45&gt;P45,"compute",IF(P45&gt;O45,"memory","balanced"))&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+        <x:f>IF(O45&gt;P45,"compute",IF(P45&gt;O45,"memory","balanced"))</x:f>
         <x:v>memory</x:v>
       </x:c>
       <x:c r="S45" s="25" t="str">
@@ -11270,18 +11273,23 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="3" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="32" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="3" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="3" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -11310,10 +11318,14 @@
       <x:c r="U1" s="3"/>
       <x:c r="V1" s="3"/>
       <x:c r="W1" s="3"/>
+      <x:c r="X1" s="3"/>
+      <x:c r="Y1" s="3"/>
+      <x:c r="Z1" s="3"/>
+      <x:c r="AA1" s="3"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Formula-linked summary, ratios, HBM-fit checks, and the two approved comparison charts.</x:v>
+        <x:v>Formula-linked section-8 metrics, sweep-derived crossover summaries, and the two approved comparison charts.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -11337,6 +11349,10 @@
       <x:c r="U2" s="7"/>
       <x:c r="V2" s="7"/>
       <x:c r="W2" s="7"/>
+      <x:c r="X2" s="7"/>
+      <x:c r="Y2" s="7"/>
+      <x:c r="Z2" s="7"/>
+      <x:c r="AA2" s="7"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -11352,27 +11368,39 @@
         <x:v>FLOPs</x:v>
       </x:c>
       <x:c r="E5" s="28" t="str">
-        <x:v>HBM GiB</x:v>
+        <x:v>HBM read GiB</x:v>
       </x:c>
       <x:c r="F5" s="28" t="str">
+        <x:v>HBM write GiB</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="str">
+        <x:v>HBM total GiB</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="str">
         <x:v>AI FLOP/B</x:v>
       </x:c>
-      <x:c r="G5" s="28" t="str">
+      <x:c r="I5" s="28" t="str">
+        <x:v>Ridge AI</x:v>
+      </x:c>
+      <x:c r="J5" s="28" t="str">
+        <x:v>Ridge class</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="str">
         <x:v>State GiB</x:v>
       </x:c>
-      <x:c r="H5" s="28" t="str">
+      <x:c r="L5" s="28" t="str">
         <x:v>HBM fit</x:v>
       </x:c>
-      <x:c r="I5" s="15" t="str">
+      <x:c r="M5" s="15" t="str">
         <x:v>Bound</x:v>
       </x:c>
-      <x:c r="K5" s="50" t="str">
+      <x:c r="O5" s="50" t="str">
         <x:v>Case</x:v>
       </x:c>
-      <x:c r="L5" s="51" t="str">
+      <x:c r="P5" s="51" t="str">
         <x:v>AI FLOP/B</x:v>
       </x:c>
-      <x:c r="M5" s="52" t="str">
+      <x:c r="Q5" s="52" t="str">
         <x:v>Effective TFLOP/s</x:v>
       </x:c>
     </x:row>
@@ -11381,46 +11409,62 @@
         <x:v>Attention+MoE · prefill</x:v>
       </x:c>
       <x:c r="B6" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
         <x:v>93.38632175616647</x:v>
       </x:c>
       <x:c r="C6" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$I$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'10_AttnMoE_Prefill'!$I$3</x:f>
         <x:v>91.28530655852009</x:v>
       </x:c>
-      <x:c r="D6" s="76" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="D6" s="79" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$A$3</x:f>
         <x:v>90324254851072</x:v>
       </x:c>
-      <x:c r="E6" s="79" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$D$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="E6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$B$3/'02_HW'!$C$11</x:f>
+        <x:v>56.25146484375</x:v>
+      </x:c>
+      <x:c r="F6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$C$3/'02_HW'!$C$11</x:f>
+        <x:v>7.00048828125</x:v>
+      </x:c>
+      <x:c r="G6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$D$3/'02_HW'!$C$11</x:f>
         <x:v>63.251953125</x:v>
       </x:c>
-      <x:c r="F6" s="79" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="H6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$F$3</x:f>
         <x:v>1329.9354948278524</x:v>
       </x:c>
-      <x:c r="G6" s="79" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$E$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="I6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$M$3</x:f>
+        <x:v>295.36477611940296</x:v>
+      </x:c>
+      <x:c r="J6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$N$3</x:f>
+        <x:v>compute-side</x:v>
+      </x:c>
+      <x:c r="K6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6" s="20" t="str">
-        <x:f>'10_AttnMoE_Prefill'!$L$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="L6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$L$3</x:f>
         <x:v>FIT</x:v>
       </x:c>
-      <x:c r="I6" s="20" t="str">
-        <x:f>'10_AttnMoE_Prefill'!$K$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="M6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$K$3</x:f>
         <x:v>compute</x:v>
       </x:c>
-      <x:c r="K6" s="20" t="str">
+      <x:c r="O6" s="20" t="str">
         <x:v>Attention+MoE · prefill</x:v>
       </x:c>
-      <x:c r="L6" s="79" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="P6" s="82" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$F$3</x:f>
         <x:v>1329.9354948278524</x:v>
       </x:c>
-      <x:c r="M6" s="79" t="n">
-        <x:f>('10_AttnMoE_Prefill'!$A$3/('10_AttnMoE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="Q6" s="82" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$A$3/('10_AttnMoE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
         <x:v>967.2107558418503</x:v>
       </x:c>
     </x:row>
@@ -11429,46 +11473,62 @@
         <x:v>HOPE shipped · prefill</x:v>
       </x:c>
       <x:c r="B7" s="66" t="n">
-        <x:f>'20_HOPE_Prefill'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'20_HOPE_Prefill'!$J$3</x:f>
         <x:v>451.376552017883</x:v>
       </x:c>
       <x:c r="C7" s="66" t="n">
-        <x:f>'20_HOPE_Prefill'!$I$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'20_HOPE_Prefill'!$I$3</x:f>
         <x:v>426.77806273898</x:v>
       </x:c>
-      <x:c r="D7" s="77" t="n">
-        <x:f>'20_HOPE_Prefill'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="D7" s="80" t="n">
+        <x:f>'20_HOPE_Prefill'!$A$3</x:f>
         <x:v>422284943294464</x:v>
       </x:c>
-      <x:c r="E7" s="80" t="n">
-        <x:f>'20_HOPE_Prefill'!$D$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="E7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$B$3/'02_HW'!$C$11</x:f>
+        <x:v>158.0665283203125</x:v>
+      </x:c>
+      <x:c r="F7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$C$3/'02_HW'!$C$11</x:f>
+        <x:v>166.5052490234375</x:v>
+      </x:c>
+      <x:c r="G7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$D$3/'02_HW'!$C$11</x:f>
         <x:v>324.57177734375</x:v>
       </x:c>
-      <x:c r="F7" s="80" t="n">
-        <x:f>'20_HOPE_Prefill'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="H7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$F$3</x:f>
         <x:v>1211.6996241291486</x:v>
       </x:c>
-      <x:c r="G7" s="80" t="n">
-        <x:f>'20_HOPE_Prefill'!$E$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="I7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$M$3</x:f>
+        <x:v>295.36477611940296</x:v>
+      </x:c>
+      <x:c r="J7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$N$3</x:f>
+        <x:v>compute-side</x:v>
+      </x:c>
+      <x:c r="K7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
-      <x:c r="H7" s="21" t="str">
-        <x:f>'20_HOPE_Prefill'!$L$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="L7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$L$3</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
-      <x:c r="I7" s="21" t="str">
-        <x:f>'20_HOPE_Prefill'!$K$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="M7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$K$3</x:f>
         <x:v>compute</x:v>
       </x:c>
-      <x:c r="K7" s="21" t="str">
+      <x:c r="O7" s="21" t="str">
         <x:v>HOPE shipped · prefill</x:v>
       </x:c>
-      <x:c r="L7" s="80" t="n">
-        <x:f>'20_HOPE_Prefill'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="P7" s="83" t="n">
+        <x:f>'20_HOPE_Prefill'!$F$3</x:f>
         <x:v>1211.6996241291486</x:v>
       </x:c>
-      <x:c r="M7" s="80" t="n">
-        <x:f>('20_HOPE_Prefill'!$A$3/('20_HOPE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="Q7" s="83" t="n">
+        <x:f>('20_HOPE_Prefill'!$A$3/('20_HOPE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
         <x:v>935.5491360963154</x:v>
       </x:c>
     </x:row>
@@ -11477,46 +11537,62 @@
         <x:v>Attention+MoE · decode</x:v>
       </x:c>
       <x:c r="B8" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="C8" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$I$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'11_AttnMoE_Decode'!$I$3</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
-      <x:c r="D8" s="77" t="n">
-        <x:f>'11_AttnMoE_Decode'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="D8" s="80" t="n">
+        <x:f>'11_AttnMoE_Decode'!$A$3</x:f>
         <x:v>181800013824</x:v>
       </x:c>
-      <x:c r="E8" s="80" t="n">
-        <x:f>'11_AttnMoE_Decode'!$D$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="E8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$B$3/'02_HW'!$C$11</x:f>
+        <x:v>74.97162500149246</x:v>
+      </x:c>
+      <x:c r="F8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$C$3/'02_HW'!$C$11</x:f>
+        <x:v>0.0664064884185791</x:v>
+      </x:c>
+      <x:c r="G8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$D$3/'02_HW'!$C$11</x:f>
         <x:v>75.03803148991103</x:v>
       </x:c>
-      <x:c r="F8" s="80" t="n">
-        <x:f>'11_AttnMoE_Decode'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="H8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$F$3</x:f>
         <x:v>2.2563819116505184</x:v>
       </x:c>
-      <x:c r="G8" s="80" t="n">
-        <x:f>'11_AttnMoE_Decode'!$E$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="I8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$M$3</x:f>
+        <x:v>295.36477611940296</x:v>
+      </x:c>
+      <x:c r="J8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$N$3</x:f>
+        <x:v>memory-side</x:v>
+      </x:c>
+      <x:c r="K8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H8" s="21" t="str">
-        <x:f>'11_AttnMoE_Decode'!$L$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="L8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$L$3</x:f>
         <x:v>FIT</x:v>
       </x:c>
-      <x:c r="I8" s="21" t="str">
-        <x:f>'11_AttnMoE_Decode'!$K$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="M8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$K$3</x:f>
         <x:v>memory</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="str">
+      <x:c r="O8" s="21" t="str">
         <x:v>Attention+MoE · decode</x:v>
       </x:c>
-      <x:c r="L8" s="80" t="n">
-        <x:f>'11_AttnMoE_Decode'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="P8" s="83" t="n">
+        <x:f>'11_AttnMoE_Decode'!$F$3</x:f>
         <x:v>2.2563819116505184</x:v>
       </x:c>
-      <x:c r="M8" s="80" t="n">
-        <x:f>('11_AttnMoE_Decode'!$A$3/('11_AttnMoE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="Q8" s="83" t="n">
+        <x:f>('11_AttnMoE_Decode'!$A$3/('11_AttnMoE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
         <x:v>7.558879404029238</x:v>
       </x:c>
     </x:row>
@@ -11525,127 +11601,187 @@
         <x:v>HOPE shipped · decode amortized</x:v>
       </x:c>
       <x:c r="B9" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$J$3</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="C9" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$I$3+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$I$3</x:f>
         <x:v>76.31950901492539</x:v>
       </x:c>
-      <x:c r="D9" s="78" t="n">
-        <x:f>'21_HOPE_Decode'!$A$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="D9" s="81" t="n">
+        <x:f>'21_HOPE_Decode'!$A$3</x:f>
         <x:v>206193819968</x:v>
       </x:c>
-      <x:c r="E9" s="81" t="n">
-        <x:f>'21_HOPE_Decode'!$D$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="E9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$B$3/'02_HW'!$C$11</x:f>
+        <x:v>110.0888677239418</x:v>
+      </x:c>
+      <x:c r="F9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$C$3/'02_HW'!$C$11</x:f>
+        <x:v>128.0227057337761</x:v>
+      </x:c>
+      <x:c r="G9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$D$3/'02_HW'!$C$11</x:f>
         <x:v>238.1115734577179</x:v>
       </x:c>
-      <x:c r="F9" s="81" t="n">
-        <x:f>'21_HOPE_Decode'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="H9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$F$3</x:f>
         <x:v>0.806483097372409</x:v>
       </x:c>
-      <x:c r="G9" s="81" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="I9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$M$3</x:f>
+        <x:v>295.36477611940296</x:v>
+      </x:c>
+      <x:c r="J9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$N$3</x:f>
+        <x:v>memory-side</x:v>
+      </x:c>
+      <x:c r="K9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
-      <x:c r="H9" s="22" t="str">
-        <x:f>'21_HOPE_Decode'!$L$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="L9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$L$3</x:f>
         <x:v>EXCEEDS</x:v>
       </x:c>
-      <x:c r="I9" s="22" t="str">
-        <x:f>'21_HOPE_Decode'!$K$3&amp;IF('01_Inputs'!$C$5&gt;0,"","")</x:f>
+      <x:c r="M9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$K$3</x:f>
         <x:v>memory</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="str">
+      <x:c r="O9" s="22" t="str">
         <x:v>HOPE shipped · decode amortized</x:v>
       </x:c>
-      <x:c r="L9" s="81" t="n">
-        <x:f>'21_HOPE_Decode'!$F$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="P9" s="84" t="n">
+        <x:f>'21_HOPE_Decode'!$F$3</x:f>
         <x:v>0.806483097372409</x:v>
       </x:c>
-      <x:c r="M9" s="81" t="n">
-        <x:f>('21_HOPE_Decode'!$A$3/('21_HOPE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="Q9" s="84" t="n">
+        <x:f>('21_HOPE_Decode'!$A$3/('21_HOPE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
         <x:v>2.7005115438910767</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="50" t="str">
-        <x:v>Ratio / timing</x:v>
+        <x:v>Crossover summary</x:v>
       </x:c>
       <x:c r="B12" s="51" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C12" s="52" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>First crossover</x:v>
+      </x:c>
+      <x:c r="C12" s="51" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="str">
+        <x:v>Rule</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="20" t="str">
+        <x:v>Context crossover</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:f>IF('40_Sweeps'!$G$6="YES",'40_Sweeps'!$A$6,IF('40_Sweeps'!$G$7="YES",'40_Sweeps'!$A$7,IF('40_Sweeps'!$G$8="YES",'40_Sweeps'!$A$8,IF('40_Sweeps'!$G$9="YES",'40_Sweeps'!$A$9,IF('40_Sweeps'!$G$10="YES",'40_Sweeps'!$A$10,IF('40_Sweeps'!$G$11="YES",'40_Sweeps'!$A$11,"None in sweep"))))))</x:f>
+        <x:v>None in sweep</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>tokens</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>First sweep row where Attention decode ms &gt;= HOPE decode ms</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="22" t="str">
+        <x:v>Batch crossover</x:v>
+      </x:c>
+      <x:c r="B14" s="22" t="str">
+        <x:f>IF('40_Sweeps'!$G$17="YES",'40_Sweeps'!$A$17,IF('40_Sweeps'!$G$18="YES",'40_Sweeps'!$A$18,IF('40_Sweeps'!$G$19="YES",'40_Sweeps'!$A$19,IF('40_Sweeps'!$G$20="YES",'40_Sweeps'!$A$20,IF('40_Sweeps'!$G$21="YES",'40_Sweeps'!$A$21,IF('40_Sweeps'!$G$22="YES",'40_Sweeps'!$A$22,"None in sweep"))))))</x:f>
+        <x:v>None in sweep</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="str">
+        <x:v>requests</x:v>
+      </x:c>
+      <x:c r="D14" s="22" t="str">
+        <x:v>First sweep row where Attention decode ms &gt;= HOPE decode ms</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="50" t="str">
+        <x:v>Ratio / timing</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="str">
+        <x:v>Interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="20" t="str">
         <x:v>Prefill Attn / HOPE stagewise</x:v>
       </x:c>
-      <x:c r="B13" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$J$3/'20_HOPE_Prefill'!$J$3+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="B18" s="65" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$J$3/'20_HOPE_Prefill'!$J$3</x:f>
         <x:v>0.206892275060993</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="str">
+      <x:c r="C18" s="20" t="str">
         <x:v>&lt;1 means Attention is faster</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="21" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="21" t="str">
         <x:v>Decode Attn / HOPE amortized</x:v>
       </x:c>
-      <x:c r="B14" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$J$3/'21_HOPE_Decode'!$B$8+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="B19" s="66" t="n">
+        <x:f>'11_AttnMoE_Decode'!$J$3/'21_HOPE_Decode'!$B$8</x:f>
         <x:v>0.31499734185340744</x:v>
       </x:c>
-      <x:c r="C14" s="21" t="str">
+      <x:c r="C19" s="21" t="str">
         <x:v>&lt;1 means Attention is faster</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="21" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="21" t="str">
         <x:v>HOPE normal decode ms</x:v>
       </x:c>
-      <x:c r="B15" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$6+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="B20" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
         <x:v>76.34359890613672</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="str">
+      <x:c r="C20" s="21" t="str">
         <x:v>No state apply</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="21" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="21" t="str">
         <x:v>HOPE boundary decode ms</x:v>
       </x:c>
-      <x:c r="B16" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$7+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="B21" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$7</x:f>
         <x:v>96.85750155927104</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="str">
+      <x:c r="C21" s="21" t="str">
         <x:v>All memory boundaries simultaneous</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="22" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="22" t="str">
         <x:v>HOPE amortized decode ms</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="B22" s="67" t="n">
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
-      <x:c r="C17" s="22" t="str">
+      <x:c r="C22" s="22" t="str">
         <x:v>Per-memory-period expectation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:W1"/>
-    <x:mergeCell ref="A2:W2"/>
+    <x:mergeCell ref="A1:AA1"/>
+    <x:mergeCell ref="A2:AA2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd6ad35bb5345de"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d2469d15b274915"/>
 </x:worksheet>
 </file>
 
@@ -11659,7 +11795,7 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="3" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
@@ -11759,8 +11895,11 @@
       <x:c r="E5" s="28" t="str">
         <x:v>HOPE state GiB</x:v>
       </x:c>
-      <x:c r="F5" s="15" t="str">
+      <x:c r="F5" s="28" t="str">
         <x:v>Attn / HOPE latency</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="str">
+        <x:v>Attention &gt;= HOPE?</x:v>
       </x:c>
       <x:c r="H5" s="50" t="str">
         <x:v>qkv_projection</x:v>
@@ -11803,16 +11942,16 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="82" t="n">
-        <x:f>'01_Inputs'!$B$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A6" s="76" t="n">
+        <x:f>'01_Inputs'!$B$64</x:f>
         <x:v>1024</x:v>
       </x:c>
       <x:c r="B6" s="65" t="n">
-        <x:f>SUM(H6:T6)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H6:T6)</x:f>
         <x:v>3.657791245775076</x:v>
       </x:c>
       <x:c r="C6" s="65" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$6)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D6" s="65" t="n">
@@ -11820,78 +11959,81 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="E6" s="65" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$6)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F6" s="65" t="n">
-        <x:f>B6/C6+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B6/C6</x:f>
         <x:v>0.047905933775766435</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="20" t="str">
+        <x:f>IF(B6&gt;=C6,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$6)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$6)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$6)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$6)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$6)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$6)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.1603382256716418</x:v>
       </x:c>
       <x:c r="L6" s="20" t="n">
-        <x:f>(MAX((((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$6)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T6" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="83" t="n">
-        <x:f>'01_Inputs'!$C$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A7" s="77" t="n">
+        <x:f>'01_Inputs'!$C$64</x:f>
         <x:v>4096</x:v>
       </x:c>
       <x:c r="B7" s="66" t="n">
-        <x:f>SUM(H7:T7)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H7:T7)</x:f>
         <x:v>4.13983297950642</x:v>
       </x:c>
       <x:c r="C7" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$7)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D7" s="66" t="n">
@@ -11899,78 +12041,81 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E7" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$7)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F7" s="66" t="n">
-        <x:f>B7/C7+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B7/C7</x:f>
         <x:v>0.05421921351800502</x:v>
       </x:c>
-      <x:c r="G7" s="21"/>
+      <x:c r="G7" s="21" t="str">
+        <x:f>IF(B7&gt;=C7,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$7)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$7)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$7)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$7)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$7)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6416708011940299</x:v>
       </x:c>
       <x:c r="L7" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$7)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0007091582089552239</x:v>
       </x:c>
       <x:c r="M7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T7" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="83" t="n">
-        <x:f>'01_Inputs'!$D$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A8" s="77" t="n">
+        <x:f>'01_Inputs'!$D$64</x:f>
         <x:v>16384</x:v>
       </x:c>
       <x:c r="B8" s="66" t="n">
-        <x:f>SUM(H8:T8)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H8:T8)</x:f>
         <x:v>6.06673810189448</x:v>
       </x:c>
       <x:c r="C8" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$8)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D8" s="66" t="n">
@@ -11978,78 +12123,81 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E8" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$8)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F8" s="66" t="n">
-        <x:f>B8/C8+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B8/C8</x:f>
         <x:v>0.07945580658272139</x:v>
       </x:c>
-      <x:c r="G8" s="21"/>
+      <x:c r="G8" s="21" t="str">
+        <x:f>IF(B8&gt;=C8,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$8)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$8)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$8)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$8)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$8)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$8)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5666832047761194</x:v>
       </x:c>
       <x:c r="L8" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$8)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0026018770149253733</x:v>
       </x:c>
       <x:c r="M8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T8" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="83" t="n">
-        <x:f>'01_Inputs'!$E$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A9" s="77" t="n">
+        <x:f>'01_Inputs'!$E$64</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
-        <x:f>SUM(H9:T9)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H9:T9)</x:f>
         <x:v>13.774358591446713</x:v>
       </x:c>
       <x:c r="C9" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$9)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D9" s="66" t="n">
@@ -12057,78 +12205,81 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$9)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F9" s="66" t="n">
-        <x:f>B9/C9+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B9/C9</x:f>
         <x:v>0.18040217884158677</x:v>
       </x:c>
-      <x:c r="G9" s="21"/>
+      <x:c r="G9" s="21" t="str">
+        <x:f>IF(B9&gt;=C9,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.266732819104478</x:v>
       </x:c>
       <x:c r="L9" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$9)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.01017275223880597</x:v>
       </x:c>
       <x:c r="M9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T9" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="83" t="n">
-        <x:f>'01_Inputs'!$F$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A10" s="77" t="n">
+        <x:f>'01_Inputs'!$F$64</x:f>
         <x:v>131072</x:v>
       </x:c>
       <x:c r="B10" s="66" t="n">
-        <x:f>SUM(H10:T10)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H10:T10)</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="C10" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$10)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D10" s="66" t="n">
@@ -12136,78 +12287,81 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="E10" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$10)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F10" s="66" t="n">
-        <x:f>B10/C10+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B10/C10</x:f>
         <x:v>0.31499734185340744</x:v>
       </x:c>
-      <x:c r="G10" s="21"/>
+      <x:c r="G10" s="21" t="str">
+        <x:f>IF(B10&gt;=C10,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$10)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$10)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$10)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$10)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$10)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$10)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>20.533465638208956</x:v>
       </x:c>
       <x:c r="L10" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$10)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020267252537313433</x:v>
       </x:c>
       <x:c r="M10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T10" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="84" t="n">
-        <x:f>'01_Inputs'!$G$64+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A11" s="78" t="n">
+        <x:f>'01_Inputs'!$G$64</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="B11" s="67" t="n">
-        <x:f>SUM(H11:T11)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H11:T11)</x:f>
         <x:v>44.60484054965567</x:v>
       </x:c>
       <x:c r="C11" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8+0*($A$11)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D11" s="67" t="n">
@@ -12215,64 +12369,67 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="E11" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11+0*($A$11)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F11" s="67" t="n">
-        <x:f>B11/C11+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B11/C11</x:f>
         <x:v>0.5841876678770486</x:v>
       </x:c>
-      <x:c r="G11" s="22"/>
+      <x:c r="G11" s="22" t="str">
+        <x:f>IF(B11&gt;=C11,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$11)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$11)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*('01_Inputs'!$C$5)*($A$11)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$11)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*($A$11)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$11)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>41.06693127641791</x:v>
       </x:c>
       <x:c r="L11" s="22" t="n">
-        <x:f>(MAX((((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*(((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$11)+('01_Inputs'!$C$20)-1)/('01_Inputs'!$C$20))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.04045625313432836</x:v>
       </x:c>
       <x:c r="M11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T11" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
@@ -12292,8 +12449,11 @@
       <x:c r="E16" s="28" t="str">
         <x:v>HOPE state GiB</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str">
+      <x:c r="F16" s="28" t="str">
         <x:v>Attn / HOPE latency</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="str">
+        <x:v>Attention &gt;= HOPE?</x:v>
       </x:c>
       <x:c r="H16" s="50" t="str">
         <x:v>qkv_projection</x:v>
@@ -12336,16 +12496,16 @@
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="82" t="n">
-        <x:f>'01_Inputs'!$B$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A17" s="76" t="n">
+        <x:f>'01_Inputs'!$B$65</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B17" s="65" t="n">
-        <x:f>SUM(H17:T17)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H17:T17)</x:f>
         <x:v>0.8430081576119405</x:v>
       </x:c>
       <x:c r="C17" s="65" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$17)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$17)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>2.405456964324235</x:v>
       </x:c>
       <x:c r="D17" s="65" t="n">
@@ -12357,74 +12517,77 @@
         <x:v>2.9375762939453125</x:v>
       </x:c>
       <x:c r="F17" s="65" t="n">
-        <x:f>B17/C17+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B17/C17</x:f>
         <x:v>0.3504565536256712</x:v>
       </x:c>
-      <x:c r="G17" s="20"/>
+      <x:c r="G17" s="20" t="str">
+        <x:f>IF(B17&gt;=C17,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06010238089552239</x:v>
       </x:c>
       <x:c r="I17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000004890746268656716</x:v>
       </x:c>
       <x:c r="J17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000002445373134328358</x:v>
       </x:c>
       <x:c r="K17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$17)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$17)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$17)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$17)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$17)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$17)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$17)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$17)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6416708011940299</x:v>
       </x:c>
       <x:c r="L17" s="20" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$17)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$17)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0006333516417910448</x:v>
       </x:c>
       <x:c r="M17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020037387462686566</x:v>
       </x:c>
       <x:c r="N17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003154555223880597</x:v>
       </x:c>
       <x:c r="O17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000004893134328358209</x:v>
       </x:c>
       <x:c r="P17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.04007232955223881</x:v>
       </x:c>
       <x:c r="Q17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.04007232955223881</x:v>
       </x:c>
       <x:c r="R17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000014672238805970149</x:v>
       </x:c>
       <x:c r="S17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.04007232955223881</x:v>
       </x:c>
       <x:c r="T17" s="20" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$17)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000004890746268656716</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="83" t="n">
-        <x:f>'01_Inputs'!$C$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A18" s="77" t="n">
+        <x:f>'01_Inputs'!$C$65</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="66" t="n">
-        <x:f>SUM(H18:T18)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H18:T18)</x:f>
         <x:v>1.6046342973134329</x:v>
       </x:c>
       <x:c r="C18" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$18)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$18)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>4.7908814319320525</x:v>
       </x:c>
       <x:c r="D18" s="66" t="n">
@@ -12436,74 +12599,77 @@
         <x:v>5.875152587890625</x:v>
       </x:c>
       <x:c r="F18" s="66" t="n">
-        <x:f>B18/C18+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B18/C18</x:f>
         <x:v>0.33493508869125166</x:v>
       </x:c>
-      <x:c r="G18" s="21"/>
+      <x:c r="G18" s="21" t="str">
+        <x:f>IF(B18&gt;=C18,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06010727164179104</x:v>
       </x:c>
       <x:c r="I18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000009781492537313432</x:v>
       </x:c>
       <x:c r="J18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000004890746268656716</x:v>
       </x:c>
       <x:c r="K18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$18)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$18)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$18)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$18)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$18)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$18)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$18)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$18)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.2833416023880597</x:v>
       </x:c>
       <x:c r="L18" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$18)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$18)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0012667032835820896</x:v>
       </x:c>
       <x:c r="M18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020042278208955225</x:v>
       </x:c>
       <x:c r="N18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003179032835820896</x:v>
       </x:c>
       <x:c r="O18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000009786268656716418</x:v>
       </x:c>
       <x:c r="P18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.07983165134328357</x:v>
       </x:c>
       <x:c r="Q18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.07983165134328357</x:v>
       </x:c>
       <x:c r="R18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000029344477611940298</x:v>
       </x:c>
       <x:c r="S18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.07983165134328357</x:v>
       </x:c>
       <x:c r="T18" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$18)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000009781492537313432</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="83" t="n">
-        <x:f>'01_Inputs'!$D$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A19" s="77" t="n">
+        <x:f>'01_Inputs'!$D$65</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B19" s="66" t="n">
-        <x:f>SUM(H19:T19)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H19:T19)</x:f>
         <x:v>3.1250987940298502</x:v>
       </x:c>
       <x:c r="C19" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$19)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$19)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>9.561730367147687</x:v>
       </x:c>
       <x:c r="D19" s="66" t="n">
@@ -12515,74 +12681,77 @@
         <x:v>11.75030517578125</x:v>
       </x:c>
       <x:c r="F19" s="66" t="n">
-        <x:f>B19/C19+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B19/C19</x:f>
         <x:v>0.32683402208946444</x:v>
       </x:c>
-      <x:c r="G19" s="21"/>
+      <x:c r="G19" s="21" t="str">
+        <x:f>IF(B19&gt;=C19,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06011705313432836</x:v>
       </x:c>
       <x:c r="I19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000019562985074626863</x:v>
       </x:c>
       <x:c r="J19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000009781492537313432</x:v>
       </x:c>
       <x:c r="K19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$19)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$19)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$19)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$19)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$19)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$19)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$19)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$19)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>2.5666832047761194</x:v>
       </x:c>
       <x:c r="L19" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$19)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$19)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.002533406567164179</x:v>
       </x:c>
       <x:c r="M19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020052059701492535</x:v>
       </x:c>
       <x:c r="N19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00032279880597014924</x:v>
       </x:c>
       <x:c r="O19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000019572537313432837</x:v>
       </x:c>
       <x:c r="P19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.15842103402985075</x:v>
       </x:c>
       <x:c r="Q19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.15842103402985075</x:v>
       </x:c>
       <x:c r="R19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000058688955223880597</x:v>
       </x:c>
       <x:c r="S19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.15842103402985075</x:v>
       </x:c>
       <x:c r="T19" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$19)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000019562985074626863</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="83" t="n">
-        <x:f>'01_Inputs'!$E$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A20" s="77" t="n">
+        <x:f>'01_Inputs'!$E$65</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="66" t="n">
-        <x:f>SUM(H20:T20)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H20:T20)</x:f>
         <x:v>6.15507848229033</x:v>
       </x:c>
       <x:c r="C20" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$20)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$20)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>19.103428237578957</x:v>
       </x:c>
       <x:c r="D20" s="66" t="n">
@@ -12594,74 +12763,77 @@
         <x:v>23.5006103515625</x:v>
       </x:c>
       <x:c r="F20" s="66" t="n">
-        <x:f>B20/C20+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B20/C20</x:f>
         <x:v>0.3221975870374136</x:v>
       </x:c>
-      <x:c r="G20" s="21"/>
+      <x:c r="G20" s="21" t="str">
+        <x:f>IF(B20&gt;=C20,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.060136616119402984</x:v>
       </x:c>
       <x:c r="I20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000039125970149253726</x:v>
       </x:c>
       <x:c r="J20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000019562985074626863</x:v>
       </x:c>
       <x:c r="K20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$20)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$20)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$20)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$20)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$20)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$20)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$20)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$20)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>5.133366409552239</x:v>
       </x:c>
       <x:c r="L20" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$20)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$20)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.005066813134328358</x:v>
       </x:c>
       <x:c r="M20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.02007162268656716</x:v>
       </x:c>
       <x:c r="N20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003325898507462687</x:v>
       </x:c>
       <x:c r="O20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000039145074626865673</x:v>
       </x:c>
       <x:c r="P20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3119500310121997</x:v>
       </x:c>
       <x:c r="Q20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3119500310121997</x:v>
       </x:c>
       <x:c r="R20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00011737791044776119</x:v>
       </x:c>
       <x:c r="S20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.3119500310121997</x:v>
       </x:c>
       <x:c r="T20" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$20)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000039125970149253726</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="83" t="n">
-        <x:f>'01_Inputs'!$F$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A21" s="77" t="n">
+        <x:f>'01_Inputs'!$F$65</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="66" t="n">
-        <x:f>SUM(H21:T21)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H21:T21)</x:f>
         <x:v>12.172808652893874</x:v>
       </x:c>
       <x:c r="C21" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$21)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$21)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>38.186823978441495</x:v>
       </x:c>
       <x:c r="D21" s="66" t="n">
@@ -12673,74 +12845,77 @@
         <x:v>47.001220703125</x:v>
       </x:c>
       <x:c r="F21" s="66" t="n">
-        <x:f>B21/C21+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B21/C21</x:f>
         <x:v>0.318769863127818</x:v>
       </x:c>
-      <x:c r="G21" s="21"/>
+      <x:c r="G21" s="21" t="str">
+        <x:f>IF(B21&gt;=C21,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.060175742089552245</x:v>
       </x:c>
       <x:c r="I21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="J21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.000039125970149253726</x:v>
       </x:c>
       <x:c r="K21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$21)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$21)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$21)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$21)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$21)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$21)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$21)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$21)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>10.266732819104478</x:v>
       </x:c>
       <x:c r="L21" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$21)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$21)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.010133626268656716</x:v>
       </x:c>
       <x:c r="M21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.02011074865671642</x:v>
       </x:c>
       <x:c r="N21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00035217194029850743</x:v>
       </x:c>
       <x:c r="O21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007829014925373135</x:v>
       </x:c>
       <x:c r="P21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6049316230044248</x:v>
       </x:c>
       <x:c r="Q21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6049316230044248</x:v>
       </x:c>
       <x:c r="R21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00023475582089552239</x:v>
       </x:c>
       <x:c r="S21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.6049316230044248</x:v>
       </x:c>
       <x:c r="T21" s="21" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$21)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="84" t="n">
-        <x:f>'01_Inputs'!$G$65+0*('01_Inputs'!$C$5)</x:f>
+      <x:c r="A22" s="78" t="n">
+        <x:f>'01_Inputs'!$G$65</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="67" t="n">
-        <x:f>SUM(H22:T22)+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>SUM(H22:T22)</x:f>
         <x:v>24.051185910849703</x:v>
       </x:c>
       <x:c r="C22" s="67" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$22)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$22)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$45)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
         <x:v>76.35361546016657</x:v>
       </x:c>
       <x:c r="D22" s="67" t="n">
@@ -12752,60 +12927,63 @@
         <x:v>94.00244140625</x:v>
       </x:c>
       <x:c r="F22" s="67" t="n">
-        <x:f>B22/C22+0*('01_Inputs'!$C$5)</x:f>
+        <x:f>B22/C22</x:f>
         <x:v>0.31499734185340744</x:v>
       </x:c>
-      <x:c r="G22" s="22"/>
+      <x:c r="G22" s="22" t="str">
+        <x:f>IF(B22&gt;=C22,"YES","NO")</x:f>
+        <x:v>NO</x:v>
+      </x:c>
       <x:c r="H22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)+('01_Inputs'!$C$10)*(((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))+2*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11))))*('01_Inputs'!$C$15)))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.06025399402985075</x:v>
       </x:c>
       <x:c r="I22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((0*'01_Inputs'!$C$5))+((2*((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
       <x:c r="J22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0)+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007825194029850745</x:v>
       </x:c>
       <x:c r="K22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((4*((($A$22)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$22)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((2*($A$22)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$22)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((4*((($A$22)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))*('01_Inputs'!$C$11)+('01_Inputs'!$C$22)*((($A$22)*('01_Inputs'!$C$12)*('01_Inputs'!$C$8)*('01_Inputs'!$C$9)))))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$22)*('01_Inputs'!$C$9)*((('01_Inputs'!$C$13)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$16)*('01_Inputs'!$C$21)))+((IF(('01_Inputs'!$C$19)=1,(((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)),0)))+((IF(('01_Inputs'!$C$19)=1,0,($A$22)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>20.533465638208956</x:v>
       </x:c>
       <x:c r="L22" s="22" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$19)=1,0,($A$22)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX((((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$19)=1,0,($A$22)*('01_Inputs'!$C$8)*('01_Inputs'!$C$12)*('01_Inputs'!$C$19)*(('01_Inputs'!$C$11)*('01_Inputs'!$C$17)+('01_Inputs'!$C$18)))))+((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$19)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020267252537313433</x:v>
       </x:c>
       <x:c r="M22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$8)))*((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$14)+((('01_Inputs'!$C$12)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$15)))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.020189000597014926</x:v>
       </x:c>
       <x:c r="N22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$23)+('01_Inputs'!$C$27)*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$23)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+('01_Inputs'!$C$10)*('01_Inputs'!$C$23)*('01_Inputs'!$C$15)))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0003913361194029851</x:v>
       </x:c>
       <x:c r="O22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$28)))))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565802985074627</x:v>
       </x:c>
       <x:c r="P22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="Q22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="R22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$33)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$34)=1,0,(2*((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00046951164179104477</x:v>
       </x:c>
       <x:c r="S22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+((0*'01_Inputs'!$C$5))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$29)&gt;0,('01_Inputs'!$C$29),('01_Inputs'!$C$23)*(1-POWER(1-1/('01_Inputs'!$C$23),((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24))))))*('01_Inputs'!$C$10)*('01_Inputs'!$C$25)*('01_Inputs'!$C$15)*('01_Inputs'!$C$30)))+(IF(('01_Inputs'!$C$34)=1,0,((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$25)*('01_Inputs'!$C$14)))))))+(0)+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14))))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>1.1385337792384582</x:v>
       </x:c>
       <x:c r="T22" s="22" t="n">
-        <x:f>(MAX((((1+0*'01_Inputs'!$C$5))*((0*'01_Inputs'!$C$5))/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1+0*'01_Inputs'!$C$5))*(((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((0*'01_Inputs'!$C$5)))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1+0*'01_Inputs'!$C$5))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$31)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$24)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+((((($A$22)*('01_Inputs'!$C$8)))*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)))+(0))/(('01_Inputs'!$C$32)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0001565038805970149</x:v>
       </x:c>
     </x:row>
@@ -12815,6 +12993,6 @@
     <x:mergeCell ref="A2:AD2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49aba4c276f64009"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d84d255fe604ea4"/>
 </x:worksheet>
 </file>
--- a/experiments/E5-attn-vs-hope/sheet/Attn-vs-HOPE.xlsx
+++ b/experiments/E5-attn-vs-hope/sheet/Attn-vs-HOPE.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Guide" sheetId="1" r:id="R9569bc1daac64f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Inputs" sheetId="2" r:id="Raa4feb95a10b4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_HW" sheetId="3" r:id="R508e0baffc4c41ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_AttnMoE_Prefill" sheetId="4" r:id="Raee353742fe146eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AttnMoE_Decode" sheetId="5" r:id="R4780e485c6764646"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_HOPE_Prefill" sheetId="6" r:id="R90c8a2731903496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_HOPE_Decode" sheetId="7" r:id="R1dd64e26005843ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Compare" sheetId="8" r:id="Rc458ad1b052746ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_Sweeps" sheetId="9" r:id="Rc5f8b9d0e3354b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_QA" sheetId="10" r:id="R59d0ddcd7a904a04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Sources" sheetId="11" r:id="R07364ef32c51448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Guide" sheetId="1" r:id="R9be84727da2d4928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Inputs" sheetId="2" r:id="R6afd24d2e8784997"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_HW" sheetId="3" r:id="Read36b07709a4f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_AttnMoE_Prefill" sheetId="4" r:id="R15e0ebbe42f3420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_AttnMoE_Decode" sheetId="5" r:id="R0ad6ec79d7df4667"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_HOPE_Prefill" sheetId="6" r:id="Rf1b26f80a0bc4b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_HOPE_Decode" sheetId="7" r:id="R50012d8c19da4869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Compare" sheetId="8" r:id="R5a7d8b2eb9624477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_Sweeps" sheetId="9" r:id="R208a12f33cbd4121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_QA" sheetId="10" r:id="Rfb63325a6c044557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Sources" sheetId="11" r:id="R514ff57756614cb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -165,7 +165,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="88">
+  <x:cellXfs count="90">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -344,6 +344,12 @@
     <x:xf numFmtId="202" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="206" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
@@ -399,7 +405,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Stagewise vs aggregate latency (ms)</a:t>
+              <a:t>TTFT/ITL invocation diagnostics (ms; prefill is full sequence)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -450,6 +456,54 @@
           <c:val>
             <c:numRef>
               <c:f>'30_Compare'!$C$6:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Compute ms</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'30_Compare'!$A$6:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'30_Compare'!$D$6:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>HBM ms</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'30_Compare'!$A$6:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'30_Compare'!$E$6:$E$9</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -556,7 +610,7 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>'30_Compare'!$P$6:$P$9</c:f>
+              <c:f>'30_Compare'!$R$6:$R$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="0"/>
@@ -565,7 +619,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'30_Compare'!$Q$6:$Q$9</c:f>
+              <c:f>'30_Compare'!$S$6:$S$9</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -647,7 +701,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Context sweep: ITL ms and persistent state GiB</a:t>
+              <a:t>Context sweep: forward-primary ITL with online sensitivity (ms)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -687,7 +741,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>HOPE including-online ITL ms</c:v>
+            <c:v>HOPE forward ITL ms (primary)</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
@@ -714,7 +768,7 @@
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>Attention state GiB</c:v>
+            <c:v>HOPE including-online ITL ms</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
@@ -730,33 +784,6 @@
           <c:val>
             <c:numRef>
               <c:f>'40_Sweeps'!$D$6:$D$11</c:f>
-              <c:numCache>
-                <c:formatCode>0.000000</c:formatCode>
-                <c:ptCount val="0"/>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>HOPE state GiB</c:v>
-          </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'40_Sweeps'!$A$6:$A$11</c:f>
-              <c:strCache>
-                <c:ptCount val="0"/>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'40_Sweeps'!$E$6:$E$11</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -838,13 +865,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -860,7 +887,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae9915c58031409e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R510789b7931e4aef"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -868,13 +895,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -890,7 +917,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb276c09666814c99"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rceaeeec0462241a4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -903,13 +930,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -925,7 +952,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8c2ea0c103f741cc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdaabd929cc340de"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1242,7 +1269,7 @@
         <x:v>Charts</x:v>
       </x:c>
       <x:c r="B14" s="24" t="str">
-        <x:v>Only three approved native charts: stagewise latency, roofline scatter, and context decode/state sweep.</x:v>
+        <x:v>Only three approved native charts: full-invocation latency diagnostics, roofline scatter, and context forward/sensitivity ITL sweep.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1324,18 +1351,18 @@
       <x:c r="A6" s="20" t="str">
         <x:v>Attention prefill FLOPs</x:v>
       </x:c>
-      <x:c r="B6" s="85" t="n">
+      <x:c r="B6" s="87" t="n">
         <x:f>'10_AttnMoE_Prefill'!$A$3</x:f>
         <x:v>14733800617541632</x:v>
       </x:c>
-      <x:c r="C6" s="85" t="n">
+      <x:c r="C6" s="87" t="n">
         <x:v>14733800617541632</x:v>
       </x:c>
-      <x:c r="D6" s="85" t="n">
+      <x:c r="D6" s="87" t="n">
         <x:f>B6-C6</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="85" t="n">
+      <x:c r="E6" s="87" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1351,18 +1378,18 @@
       <x:c r="A7" s="21" t="str">
         <x:v>Attention prefill effective HBM B</x:v>
       </x:c>
-      <x:c r="B7" s="86" t="n">
+      <x:c r="B7" s="88" t="n">
         <x:f>'10_AttnMoE_Prefill'!$D$3</x:f>
         <x:v>1082668351488</x:v>
       </x:c>
-      <x:c r="C7" s="86" t="n">
+      <x:c r="C7" s="88" t="n">
         <x:v>1082668351488</x:v>
       </x:c>
-      <x:c r="D7" s="86" t="n">
+      <x:c r="D7" s="88" t="n">
         <x:f>B7-C7</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="86" t="n">
+      <x:c r="E7" s="88" t="n">
         <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
@@ -1378,18 +1405,18 @@
       <x:c r="A8" s="21" t="str">
         <x:v>Attention prefill stagewise ms</x:v>
       </x:c>
-      <x:c r="B8" s="86" t="n">
+      <x:c r="B8" s="88" t="n">
         <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
         <x:v>3256.329489278666</x:v>
       </x:c>
-      <x:c r="C8" s="86" t="n">
+      <x:c r="C8" s="88" t="n">
         <x:v>3256.329489278667</x:v>
       </x:c>
-      <x:c r="D8" s="86" t="n">
+      <x:c r="D8" s="88" t="n">
         <x:f>B8-C8</x:f>
         <x:v>-9.094947017729282e-13</x:v>
       </x:c>
-      <x:c r="E8" s="86" t="n">
+      <x:c r="E8" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1405,18 +1432,18 @@
       <x:c r="A9" s="21" t="str">
         <x:v>Attention decode FLOPs</x:v>
       </x:c>
-      <x:c r="B9" s="86" t="n">
+      <x:c r="B9" s="88" t="n">
         <x:f>'11_AttnMoE_Decode'!$A$3</x:f>
         <x:v>181800013824</x:v>
       </x:c>
-      <x:c r="C9" s="86" t="n">
+      <x:c r="C9" s="88" t="n">
         <x:v>181800013824</x:v>
       </x:c>
-      <x:c r="D9" s="86" t="n">
+      <x:c r="D9" s="88" t="n">
         <x:f>B9-C9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E9" s="86" t="n">
+      <x:c r="E9" s="88" t="n">
         <x:f>0</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -1432,18 +1459,18 @@
       <x:c r="A10" s="21" t="str">
         <x:v>Attention decode effective HBM B</x:v>
       </x:c>
-      <x:c r="B10" s="86" t="n">
+      <x:c r="B10" s="88" t="n">
         <x:f>'11_AttnMoE_Decode'!$D$3</x:f>
         <x:v>80571472801.34651</x:v>
       </x:c>
-      <x:c r="C10" s="86" t="n">
+      <x:c r="C10" s="88" t="n">
         <x:v>80571472801.34651</x:v>
       </x:c>
-      <x:c r="D10" s="86" t="n">
+      <x:c r="D10" s="88" t="n">
         <x:f>B10-C10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="86" t="n">
+      <x:c r="E10" s="88" t="n">
         <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
@@ -1459,18 +1486,18 @@
       <x:c r="A11" s="21" t="str">
         <x:v>Attention decode stagewise ms</x:v>
       </x:c>
-      <x:c r="B11" s="86" t="n">
+      <x:c r="B11" s="88" t="n">
         <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
         <x:v>10.888036865046827</x:v>
       </x:c>
-      <x:c r="C11" s="86" t="n">
+      <x:c r="C11" s="88" t="n">
         <x:v>10.888036865046825</x:v>
       </x:c>
-      <x:c r="D11" s="86" t="n">
+      <x:c r="D11" s="88" t="n">
         <x:f>B11-C11</x:f>
         <x:v>1.7763568394002505e-15</x:v>
       </x:c>
-      <x:c r="E11" s="86" t="n">
+      <x:c r="E11" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1486,18 +1513,18 @@
       <x:c r="A12" s="21" t="str">
         <x:v>HOPE prefill FLOPs</x:v>
       </x:c>
-      <x:c r="B12" s="86" t="n">
+      <x:c r="B12" s="88" t="n">
         <x:f>'20_HOPE_Prefill'!$A$3</x:f>
         <x:v>308817305272320</x:v>
       </x:c>
-      <x:c r="C12" s="86" t="n">
+      <x:c r="C12" s="88" t="n">
         <x:v>308817305272320</x:v>
       </x:c>
-      <x:c r="D12" s="86" t="n">
+      <x:c r="D12" s="88" t="n">
         <x:f>B12-C12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="86" t="n">
+      <x:c r="E12" s="88" t="n">
         <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
@@ -1513,18 +1540,18 @@
       <x:c r="A13" s="21" t="str">
         <x:v>HOPE prefill effective HBM B</x:v>
       </x:c>
-      <x:c r="B13" s="86" t="n">
+      <x:c r="B13" s="88" t="n">
         <x:f>'20_HOPE_Prefill'!$D$3</x:f>
         <x:v>334155874304</x:v>
       </x:c>
-      <x:c r="C13" s="86" t="n">
+      <x:c r="C13" s="88" t="n">
         <x:v>334155874304</x:v>
       </x:c>
-      <x:c r="D13" s="86" t="n">
+      <x:c r="D13" s="88" t="n">
         <x:f>B13-C13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="86" t="n">
+      <x:c r="E13" s="88" t="n">
         <x:f>0.01</x:f>
         <x:v>0.01</x:v>
       </x:c>
@@ -1540,18 +1567,18 @@
       <x:c r="A14" s="21" t="str">
         <x:v>HOPE prefill stagewise ms</x:v>
       </x:c>
-      <x:c r="B14" s="86" t="n">
+      <x:c r="B14" s="88" t="n">
         <x:f>'20_HOPE_Prefill'!$J$3</x:f>
         <x:v>87.76370645169284</x:v>
       </x:c>
-      <x:c r="C14" s="86" t="n">
+      <x:c r="C14" s="88" t="n">
         <x:v>87.76370645169283</x:v>
       </x:c>
-      <x:c r="D14" s="86" t="n">
+      <x:c r="D14" s="88" t="n">
         <x:f>B14-C14</x:f>
         <x:v>1.4210854715202004e-14</x:v>
       </x:c>
-      <x:c r="E14" s="86" t="n">
+      <x:c r="E14" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1567,18 +1594,18 @@
       <x:c r="A15" s="21" t="str">
         <x:v>HOPE forward-only ITL ms</x:v>
       </x:c>
-      <x:c r="B15" s="86" t="n">
+      <x:c r="B15" s="88" t="n">
         <x:f>'21_HOPE_Decode'!$B$6</x:f>
         <x:v>0.6194056302702703</x:v>
       </x:c>
-      <x:c r="C15" s="86" t="n">
+      <x:c r="C15" s="88" t="n">
         <x:v>0.6194056302702702</x:v>
       </x:c>
-      <x:c r="D15" s="86" t="n">
+      <x:c r="D15" s="88" t="n">
         <x:f>B15-C15</x:f>
         <x:v>1.1102230246251565e-16</x:v>
       </x:c>
-      <x:c r="E15" s="86" t="n">
+      <x:c r="E15" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1594,18 +1621,18 @@
       <x:c r="A16" s="21" t="str">
         <x:v>HOPE online-overhead ITL ms</x:v>
       </x:c>
-      <x:c r="B16" s="86" t="n">
+      <x:c r="B16" s="88" t="n">
         <x:f>'21_HOPE_Decode'!$B$7</x:f>
         <x:v>30.194499154265625</x:v>
       </x:c>
-      <x:c r="C16" s="86" t="n">
+      <x:c r="C16" s="88" t="n">
         <x:v>30.194499154265632</x:v>
       </x:c>
-      <x:c r="D16" s="86" t="n">
+      <x:c r="D16" s="88" t="n">
         <x:f>B16-C16</x:f>
         <x:v>-7.105427357601002e-15</x:v>
       </x:c>
-      <x:c r="E16" s="86" t="n">
+      <x:c r="E16" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1621,18 +1648,18 @@
       <x:c r="A17" s="21" t="str">
         <x:v>HOPE including-online ITL ms</x:v>
       </x:c>
-      <x:c r="B17" s="86" t="n">
+      <x:c r="B17" s="88" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="C17" s="86" t="n">
+      <x:c r="C17" s="88" t="n">
         <x:v>30.8139047845359</x:v>
       </x:c>
-      <x:c r="D17" s="86" t="n">
+      <x:c r="D17" s="88" t="n">
         <x:f>B17-C17</x:f>
         <x:v>-3.552713678800501e-15</x:v>
       </x:c>
-      <x:c r="E17" s="86" t="n">
+      <x:c r="E17" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1648,18 +1675,18 @@
       <x:c r="A18" s="21" t="str">
         <x:v>Context sweep 1K Attention decode ms</x:v>
       </x:c>
-      <x:c r="B18" s="86" t="n">
+      <x:c r="B18" s="88" t="n">
         <x:f>'40_Sweeps'!$B$6</x:f>
         <x:v>1.655891982884663</x:v>
       </x:c>
-      <x:c r="C18" s="86" t="n">
+      <x:c r="C18" s="88" t="n">
         <x:v>1.655891982884663</x:v>
       </x:c>
-      <x:c r="D18" s="86" t="n">
+      <x:c r="D18" s="88" t="n">
         <x:f>B18-C18</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="86" t="n">
+      <x:c r="E18" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1675,18 +1702,18 @@
       <x:c r="A19" s="21" t="str">
         <x:v>Context sweep 256K Attention decode ms</x:v>
       </x:c>
-      <x:c r="B19" s="86" t="n">
+      <x:c r="B19" s="88" t="n">
         <x:f>'40_Sweeps'!$B$11</x:f>
         <x:v>20.192731870452235</x:v>
       </x:c>
-      <x:c r="C19" s="86" t="n">
+      <x:c r="C19" s="88" t="n">
         <x:v>20.192731870452228</x:v>
       </x:c>
-      <x:c r="D19" s="86" t="n">
+      <x:c r="D19" s="88" t="n">
         <x:f>B19-C19</x:f>
         <x:v>7.105427357601002e-15</x:v>
       </x:c>
-      <x:c r="E19" s="86" t="n">
+      <x:c r="E19" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1700,20 +1727,20 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21" t="str">
-        <x:v>Batch sweep B=1 HOPE decode ms</x:v>
-      </x:c>
-      <x:c r="B20" s="86" t="n">
-        <x:f>'40_Sweeps'!$C$17</x:f>
-        <x:v>0.9717198910032332</x:v>
-      </x:c>
-      <x:c r="C20" s="86" t="n">
-        <x:v>0.9717198910032334</x:v>
-      </x:c>
-      <x:c r="D20" s="86" t="n">
+        <x:v>Context sweep 1K HOPE forward ms</x:v>
+      </x:c>
+      <x:c r="B20" s="88" t="n">
+        <x:f>'40_Sweeps'!$C$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="C20" s="88" t="n">
+        <x:v>0.6194056302702702</x:v>
+      </x:c>
+      <x:c r="D20" s="88" t="n">
         <x:f>B20-C20</x:f>
-        <x:v>-2.220446049250313e-16</x:v>
-      </x:c>
-      <x:c r="E20" s="86" t="n">
+        <x:v>1.1102230246251565e-16</x:v>
+      </x:c>
+      <x:c r="E20" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
@@ -1722,105 +1749,169 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
-        <x:v>Static-q read is not batch-linear</x:v>
+        <x:v>Primary serving axis</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="22" t="str">
-        <x:v>Batch sweep B=32 HOPE decode ms</x:v>
-      </x:c>
-      <x:c r="B21" s="87" t="n">
-        <x:f>'40_Sweeps'!$C$22</x:f>
+      <x:c r="A21" s="21" t="str">
+        <x:v>Context sweep 1K HOPE including-online ms</x:v>
+      </x:c>
+      <x:c r="B21" s="88" t="n">
+        <x:f>'40_Sweeps'!$D$6</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="C21" s="87" t="n">
+      <x:c r="C21" s="88" t="n">
         <x:v>30.8139047845359</x:v>
       </x:c>
-      <x:c r="D21" s="87" t="n">
+      <x:c r="D21" s="88" t="n">
         <x:f>B21-C21</x:f>
         <x:v>-3.552713678800501e-15</x:v>
       </x:c>
-      <x:c r="E21" s="87" t="n">
+      <x:c r="E21" s="88" t="n">
         <x:f>1e-8</x:f>
         <x:v>1e-8</x:v>
       </x:c>
-      <x:c r="F21" s="22" t="str">
+      <x:c r="F21" s="21" t="str">
         <x:f>IF(ABS(D21)&lt;=E21,"PASS","REVIEW")</x:f>
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="G21" s="22" t="str">
+      <x:c r="G21" s="21" t="str">
+        <x:v>Sensitivity axis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="21" t="str">
+        <x:v>Batch sweep B=1 HOPE forward ms</x:v>
+      </x:c>
+      <x:c r="B22" s="88" t="n">
+        <x:f>'40_Sweeps'!$C$17</x:f>
+        <x:v>0.028141792432432432</x:v>
+      </x:c>
+      <x:c r="C22" s="88" t="n">
+        <x:v>0.028141792432432432</x:v>
+      </x:c>
+      <x:c r="D22" s="88" t="n">
+        <x:f>B22-C22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="88" t="n">
+        <x:f>1e-8</x:f>
+        <x:v>1e-8</x:v>
+      </x:c>
+      <x:c r="F22" s="21" t="str">
+        <x:f>IF(ABS(D22)&lt;=E22,"PASS","REVIEW")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G22" s="21" t="str">
+        <x:v>Exact forward-stage reconstruction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="21" t="str">
+        <x:v>Batch sweep B=1 HOPE including-online ms</x:v>
+      </x:c>
+      <x:c r="B23" s="88" t="n">
+        <x:f>'40_Sweeps'!$D$17</x:f>
+        <x:v>0.9717198910032334</x:v>
+      </x:c>
+      <x:c r="C23" s="88" t="n">
+        <x:v>0.9717198910032334</x:v>
+      </x:c>
+      <x:c r="D23" s="88" t="n">
+        <x:f>B23-C23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="88" t="n">
+        <x:f>1e-8</x:f>
+        <x:v>1e-8</x:v>
+      </x:c>
+      <x:c r="F23" s="21" t="str">
+        <x:f>IF(ABS(D23)&lt;=E23,"PASS","REVIEW")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G23" s="21" t="str">
+        <x:v>Static-q read is not batch-linear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="21" t="str">
+        <x:v>Batch sweep B=32 HOPE forward ms</x:v>
+      </x:c>
+      <x:c r="B24" s="88" t="n">
+        <x:f>'40_Sweeps'!$C$22</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="C24" s="88" t="n">
+        <x:v>0.6194056302702702</x:v>
+      </x:c>
+      <x:c r="D24" s="88" t="n">
+        <x:f>B24-C24</x:f>
+        <x:v>1.1102230246251565e-16</x:v>
+      </x:c>
+      <x:c r="E24" s="88" t="n">
+        <x:f>1e-8</x:f>
+        <x:v>1e-8</x:v>
+      </x:c>
+      <x:c r="F24" s="21" t="str">
+        <x:f>IF(ABS(D24)&lt;=E24,"PASS","REVIEW")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G24" s="21" t="str">
         <x:v>Formula-driven sweep endpoint</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="50" t="str">
+      <x:c r="A25" s="22" t="str">
+        <x:v>Batch sweep B=32 HOPE including-online ms</x:v>
+      </x:c>
+      <x:c r="B25" s="89" t="n">
+        <x:f>'40_Sweeps'!$D$22</x:f>
+        <x:v>30.8139047845359</x:v>
+      </x:c>
+      <x:c r="C25" s="89" t="n">
+        <x:v>30.8139047845359</x:v>
+      </x:c>
+      <x:c r="D25" s="89" t="n">
+        <x:f>B25-C25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="89" t="n">
+        <x:f>1e-8</x:f>
+        <x:v>1e-8</x:v>
+      </x:c>
+      <x:c r="F25" s="22" t="str">
+        <x:f>IF(ABS(D25)&lt;=E25,"PASS","REVIEW")</x:f>
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="G25" s="22" t="str">
+        <x:v>Formula-driven sweep endpoint</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="50" t="str">
         <x:v>Upstream invariant</x:v>
       </x:c>
-      <x:c r="B25" s="51" t="str">
+      <x:c r="B29" s="51" t="str">
         <x:v>Engine result</x:v>
       </x:c>
-      <x:c r="C25" s="52" t="str">
+      <x:c r="C29" s="52" t="str">
         <x:v>Meaning</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="20" t="str">
+    <x:row r="30">
+      <x:c r="A30" s="20" t="str">
         <x:v>adaptive_q_is_excluded_from_defaults</x:v>
       </x:c>
-      <x:c r="B26" s="20" t="str">
+      <x:c r="B30" s="20" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C26" s="20" t="str">
-        <x:v>Imported from results.json QA contract</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="21" t="str">
-        <x:v>all_stagewise_not_below_aggregate</x:v>
-      </x:c>
-      <x:c r="B27" s="21" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="C27" s="21" t="str">
-        <x:v>Imported from results.json QA contract</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="21" t="str">
-        <x:v>causal_flash_has_no_quadratic_temporary_write</x:v>
-      </x:c>
-      <x:c r="B28" s="21" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="C28" s="21" t="str">
-        <x:v>Imported from results.json QA contract</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="21" t="str">
-        <x:v>cms_forward_read_is_not_divided_by_update_period</x:v>
-      </x:c>
-      <x:c r="B29" s="21" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="C29" s="21" t="str">
-        <x:v>Imported from results.json QA contract</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="21" t="str">
-        <x:v>cms_is_router_plus_sparse_low_rank_ab</x:v>
-      </x:c>
-      <x:c r="B30" s="21" t="str">
-        <x:v>PASS</x:v>
-      </x:c>
-      <x:c r="C30" s="21" t="str">
+      <x:c r="C30" s="20" t="str">
         <x:v>Imported from results.json QA contract</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="21" t="str">
-        <x:v>cms_online_update_is_excluded</x:v>
+        <x:v>all_stagewise_not_below_aggregate</x:v>
       </x:c>
       <x:c r="B31" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1831,7 +1922,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="21" t="str">
-        <x:v>decode_kv_read_is_linear_in_context</x:v>
+        <x:v>causal_flash_has_no_quadratic_temporary_write</x:v>
       </x:c>
       <x:c r="B32" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1842,7 +1933,7 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="21" t="str">
-        <x:v>decode_metrics_are_one_token_without_osl</x:v>
+        <x:v>cms_forward_read_is_not_divided_by_update_period</x:v>
       </x:c>
       <x:c r="B33" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1853,7 +1944,7 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="21" t="str">
-        <x:v>flash_decode_partials_zero_at_one_split</x:v>
+        <x:v>cms_is_router_plus_sparse_low_rank_ab</x:v>
       </x:c>
       <x:c r="B34" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1864,7 +1955,7 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="21" t="str">
-        <x:v>hope_dependency_partition_is_canonical</x:v>
+        <x:v>cms_online_update_is_excluded</x:v>
       </x:c>
       <x:c r="B35" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1875,7 +1966,7 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="21" t="str">
-        <x:v>hope_group_summaries_conserve_totals</x:v>
+        <x:v>decode_kv_read_is_linear_in_context</x:v>
       </x:c>
       <x:c r="B36" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1886,7 +1977,7 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="21" t="str">
-        <x:v>hope_state_is_batch_linear</x:v>
+        <x:v>decode_metrics_are_one_token_without_osl</x:v>
       </x:c>
       <x:c r="B37" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1897,7 +1988,7 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="21" t="str">
-        <x:v>hope_state_is_context_independent</x:v>
+        <x:v>flash_decode_partials_zero_at_one_split</x:v>
       </x:c>
       <x:c r="B38" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1908,7 +1999,7 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="21" t="str">
-        <x:v>hope_ttft_uses_prefill_chunk_count</x:v>
+        <x:v>hope_dependency_partition_is_canonical</x:v>
       </x:c>
       <x:c r="B39" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1919,7 +2010,7 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="21" t="str">
-        <x:v>kv_append_is_context_independent</x:v>
+        <x:v>hope_group_summaries_conserve_totals</x:v>
       </x:c>
       <x:c r="B40" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1930,7 +2021,7 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="21" t="str">
-        <x:v>legacy_flops_anchor_matches</x:v>
+        <x:v>hope_state_is_batch_linear</x:v>
       </x:c>
       <x:c r="B41" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1941,7 +2032,7 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="21" t="str">
-        <x:v>legacy_hbm_anchor_matches</x:v>
+        <x:v>hope_state_is_context_independent</x:v>
       </x:c>
       <x:c r="B42" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1952,7 +2043,7 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="21" t="str">
-        <x:v>reference_hardware_matches_live_sheet</x:v>
+        <x:v>hope_ttft_uses_prefill_chunk_count</x:v>
       </x:c>
       <x:c r="B43" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1963,7 +2054,7 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="21" t="str">
-        <x:v>shipped_default_has_no_M_q</x:v>
+        <x:v>kv_append_is_context_independent</x:v>
       </x:c>
       <x:c r="B44" s="21" t="str">
         <x:v>PASS</x:v>
@@ -1973,171 +2064,215 @@
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="22" t="str">
+      <x:c r="A45" s="21" t="str">
+        <x:v>legacy_flops_anchor_matches</x:v>
+      </x:c>
+      <x:c r="B45" s="21" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C45" s="21" t="str">
+        <x:v>Imported from results.json QA contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="21" t="str">
+        <x:v>legacy_hbm_anchor_matches</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C46" s="21" t="str">
+        <x:v>Imported from results.json QA contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="21" t="str">
+        <x:v>reference_hardware_matches_live_sheet</x:v>
+      </x:c>
+      <x:c r="B47" s="21" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C47" s="21" t="str">
+        <x:v>Imported from results.json QA contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="21" t="str">
+        <x:v>shipped_default_has_no_M_q</x:v>
+      </x:c>
+      <x:c r="B48" s="21" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="C48" s="21" t="str">
+        <x:v>Imported from results.json QA contract</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="22" t="str">
         <x:v>shipped_forward_is_static_q_plus_M_mem</x:v>
       </x:c>
-      <x:c r="B45" s="22" t="str">
+      <x:c r="B49" s="22" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="C45" s="22" t="str">
+      <x:c r="C49" s="22" t="str">
         <x:v>Imported from results.json QA contract</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="50" t="str">
+    <x:row r="52">
+      <x:c r="A52" s="50" t="str">
         <x:v>Native operational metric</x:v>
       </x:c>
-      <x:c r="B48" s="51" t="str">
+      <x:c r="B52" s="51" t="str">
         <x:v>Native Sheet ms</x:v>
       </x:c>
-      <x:c r="C48" s="51" t="str">
+      <x:c r="C52" s="51" t="str">
         <x:v>Generated companion ms</x:v>
       </x:c>
-      <x:c r="D48" s="51" t="str">
+      <x:c r="D52" s="51" t="str">
         <x:v>Delta ms</x:v>
       </x:c>
-      <x:c r="E48" s="51" t="str">
+      <x:c r="E52" s="51" t="str">
         <x:v>Reconciliation</x:v>
       </x:c>
-      <x:c r="F48" s="52" t="str">
+      <x:c r="F52" s="52" t="str">
         <x:v>Why exact equality is not asserted</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="20" t="str">
+    <x:row r="53">
+      <x:c r="A53" s="20" t="str">
         <x:v>Full Attention TTFT</x:v>
       </x:c>
-      <x:c r="B49" s="65" t="n">
+      <x:c r="B53" s="65" t="n">
         <x:v>3204.916</x:v>
       </x:c>
-      <x:c r="C49" s="65" t="n">
+      <x:c r="C53" s="65" t="n">
         <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
         <x:v>3256.329489278666</x:v>
       </x:c>
-      <x:c r="D49" s="65" t="n">
-        <x:f>C49-B49</x:f>
+      <x:c r="D53" s="65" t="n">
+        <x:f>C53-B53</x:f>
         <x:v>51.41348927866602</x:v>
       </x:c>
-      <x:c r="E49" s="20" t="str">
-        <x:f>IF(ABS(D49)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E53" s="20" t="str">
+        <x:f>IF(ABS(D53)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>ASSUMPTION DIFFERENCE</x:v>
       </x:c>
-      <x:c r="F49" s="23" t="str">
+      <x:c r="F53" s="23" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="21" t="str">
+    <x:row r="54">
+      <x:c r="A54" s="21" t="str">
         <x:v>HOPE forward TTFT</x:v>
       </x:c>
-      <x:c r="B50" s="66" t="n">
+      <x:c r="B54" s="66" t="n">
         <x:v>552.123</x:v>
       </x:c>
-      <x:c r="C50" s="66" t="n">
+      <x:c r="C54" s="66" t="n">
         <x:f>(('20_HOPE_Prefill'!$E$47)*('01_Inputs'!$C$9))</x:f>
         <x:v>539.123762358741</x:v>
       </x:c>
-      <x:c r="D50" s="66" t="n">
-        <x:f>C50-B50</x:f>
+      <x:c r="D54" s="66" t="n">
+        <x:f>C54-B54</x:f>
         <x:v>-12.999237641259015</x:v>
       </x:c>
-      <x:c r="E50" s="21" t="str">
-        <x:f>IF(ABS(D50)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E54" s="21" t="str">
+        <x:f>IF(ABS(D54)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>ASSUMPTION DIFFERENCE</x:v>
       </x:c>
-      <x:c r="F50" s="24" t="str">
+      <x:c r="F54" s="24" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="21" t="str">
+    <x:row r="55">
+      <x:c r="A55" s="21" t="str">
         <x:v>HOPE including-online TTFT</x:v>
       </x:c>
-      <x:c r="B51" s="66" t="n">
+      <x:c r="B55" s="66" t="n">
         <x:v>6757.768</x:v>
       </x:c>
-      <x:c r="C51" s="66" t="n">
+      <x:c r="C55" s="66" t="n">
         <x:f>(('20_HOPE_Prefill'!$J$3)*('01_Inputs'!$C$9))</x:f>
         <x:v>5616.877212908342</x:v>
       </x:c>
-      <x:c r="D51" s="66" t="n">
-        <x:f>C51-B51</x:f>
+      <x:c r="D55" s="66" t="n">
+        <x:f>C55-B55</x:f>
         <x:v>-1140.8907870916582</x:v>
       </x:c>
-      <x:c r="E51" s="21" t="str">
-        <x:f>IF(ABS(D51)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E55" s="21" t="str">
+        <x:f>IF(ABS(D55)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>ASSUMPTION DIFFERENCE</x:v>
       </x:c>
-      <x:c r="F51" s="24" t="str">
+      <x:c r="F55" s="24" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="21" t="str">
+    <x:row r="56">
+      <x:c r="A56" s="21" t="str">
         <x:v>Full Attention ITL</x:v>
       </x:c>
-      <x:c r="B52" s="66" t="n">
+      <x:c r="B56" s="66" t="n">
         <x:v>10.888</x:v>
       </x:c>
-      <x:c r="C52" s="66" t="n">
+      <x:c r="C56" s="66" t="n">
         <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
         <x:v>10.888036865046827</x:v>
       </x:c>
-      <x:c r="D52" s="66" t="n">
-        <x:f>C52-B52</x:f>
+      <x:c r="D56" s="66" t="n">
+        <x:f>C56-B56</x:f>
         <x:v>0.00003686504682676173</x:v>
       </x:c>
-      <x:c r="E52" s="21" t="str">
-        <x:f>IF(ABS(D52)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E56" s="21" t="str">
+        <x:f>IF(ABS(D56)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>MATCH</x:v>
       </x:c>
-      <x:c r="F52" s="24" t="str">
+      <x:c r="F56" s="24" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="21" t="str">
+    <x:row r="57">
+      <x:c r="A57" s="21" t="str">
         <x:v>HOPE forward ITL</x:v>
       </x:c>
-      <x:c r="B53" s="66" t="n">
+      <x:c r="B57" s="66" t="n">
         <x:v>0.604</x:v>
       </x:c>
-      <x:c r="C53" s="66" t="n">
+      <x:c r="C57" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$B$6</x:f>
         <x:v>0.6194056302702703</x:v>
       </x:c>
-      <x:c r="D53" s="66" t="n">
-        <x:f>C53-B53</x:f>
+      <x:c r="D57" s="66" t="n">
+        <x:f>C57-B57</x:f>
         <x:v>0.01540563027027031</x:v>
       </x:c>
-      <x:c r="E53" s="21" t="str">
-        <x:f>IF(ABS(D53)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E57" s="21" t="str">
+        <x:f>IF(ABS(D57)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>ASSUMPTION DIFFERENCE</x:v>
       </x:c>
-      <x:c r="F53" s="24" t="str">
+      <x:c r="F57" s="24" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="22" t="str">
+    <x:row r="58">
+      <x:c r="A58" s="22" t="str">
         <x:v>HOPE including-online ITL</x:v>
       </x:c>
-      <x:c r="B54" s="67" t="n">
+      <x:c r="B58" s="67" t="n">
         <x:v>18.89</x:v>
       </x:c>
-      <x:c r="C54" s="67" t="n">
+      <x:c r="C58" s="67" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D54" s="67" t="n">
-        <x:f>C54-B54</x:f>
+      <x:c r="D58" s="67" t="n">
+        <x:f>C58-B58</x:f>
         <x:v>11.923904784535896</x:v>
       </x:c>
-      <x:c r="E54" s="22" t="str">
-        <x:f>IF(ABS(D54)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
+      <x:c r="E58" s="22" t="str">
+        <x:f>IF(ABS(D58)&lt;=0.001,"MATCH","ASSUMPTION DIFFERENCE")</x:f>
         <x:v>ASSUMPTION DIFFERENCE</x:v>
       </x:c>
-      <x:c r="F54" s="25" t="str">
+      <x:c r="F58" s="25" t="str">
         <x:v>The native Sheet is the user-reviewed operational contract. Exact numerical equality is not asserted: the generated engine uses an explicit sparse-CMS unique-active HBM upper bound, explicit MoE traffic, and its own stagewise roofline partition.</x:v>
       </x:c>
     </x:row>
@@ -2210,7 +2345,7 @@
         <x:v>Raw inputs, QA references, stage/group-order assertion</x:v>
       </x:c>
       <x:c r="E6" s="23" t="str">
-        <x:v>Schema v2 dependency and TTFT/ITL contract</x:v>
+        <x:v>Schema v3 dependency, TTFT/ITL, and crossover-axis contract</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -12162,560 +12297,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="3" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="45" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="3" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="3" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="48" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="3" t="str">
         <x:v>30 · Architecture comparison</x:v>
-      </x:c>
-      <x:c r="B1" s="3"/>
-      <x:c r="C1" s="3"/>
-      <x:c r="D1" s="3"/>
-      <x:c r="E1" s="3"/>
-      <x:c r="F1" s="3"/>
-      <x:c r="G1" s="3"/>
-      <x:c r="H1" s="3"/>
-      <x:c r="I1" s="3"/>
-      <x:c r="J1" s="3"/>
-      <x:c r="K1" s="3"/>
-      <x:c r="L1" s="3"/>
-      <x:c r="M1" s="3"/>
-      <x:c r="N1" s="3"/>
-      <x:c r="O1" s="3"/>
-      <x:c r="P1" s="3"/>
-      <x:c r="Q1" s="3"/>
-      <x:c r="R1" s="3"/>
-      <x:c r="S1" s="3"/>
-      <x:c r="T1" s="3"/>
-      <x:c r="U1" s="3"/>
-      <x:c r="V1" s="3"/>
-      <x:c r="W1" s="3"/>
-      <x:c r="X1" s="3"/>
-      <x:c r="Y1" s="3"/>
-      <x:c r="Z1" s="3"/>
-      <x:c r="AA1" s="3"/>
-    </x:row>
-    <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Formula-linked section-8 metrics, sweep-derived crossover summaries, and the two approved comparison charts.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
-      <x:c r="J2" s="7"/>
-      <x:c r="K2" s="7"/>
-      <x:c r="L2" s="7"/>
-      <x:c r="M2" s="7"/>
-      <x:c r="N2" s="7"/>
-      <x:c r="O2" s="7"/>
-      <x:c r="P2" s="7"/>
-      <x:c r="Q2" s="7"/>
-      <x:c r="R2" s="7"/>
-      <x:c r="S2" s="7"/>
-      <x:c r="T2" s="7"/>
-      <x:c r="U2" s="7"/>
-      <x:c r="V2" s="7"/>
-      <x:c r="W2" s="7"/>
-      <x:c r="X2" s="7"/>
-      <x:c r="Y2" s="7"/>
-      <x:c r="Z2" s="7"/>
-      <x:c r="AA2" s="7"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>Architecture / phase</x:v>
-      </x:c>
-      <x:c r="B5" s="28" t="str">
-        <x:v>Stagewise ms</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="str">
-        <x:v>Aggregate ms</x:v>
-      </x:c>
-      <x:c r="D5" s="28" t="str">
-        <x:v>FLOPs</x:v>
-      </x:c>
-      <x:c r="E5" s="28" t="str">
-        <x:v>HBM read GiB</x:v>
-      </x:c>
-      <x:c r="F5" s="28" t="str">
-        <x:v>HBM write GiB</x:v>
-      </x:c>
-      <x:c r="G5" s="28" t="str">
-        <x:v>HBM total GiB</x:v>
-      </x:c>
-      <x:c r="H5" s="28" t="str">
-        <x:v>AI FLOP/B</x:v>
-      </x:c>
-      <x:c r="I5" s="28" t="str">
-        <x:v>Ridge AI</x:v>
-      </x:c>
-      <x:c r="J5" s="28" t="str">
-        <x:v>Ridge class</x:v>
-      </x:c>
-      <x:c r="K5" s="28" t="str">
-        <x:v>State GiB</x:v>
-      </x:c>
-      <x:c r="L5" s="28" t="str">
-        <x:v>HBM fit</x:v>
-      </x:c>
-      <x:c r="M5" s="15" t="str">
-        <x:v>Bound</x:v>
-      </x:c>
-      <x:c r="O5" s="50" t="str">
-        <x:v>Case</x:v>
-      </x:c>
-      <x:c r="P5" s="51" t="str">
-        <x:v>AI FLOP/B</x:v>
-      </x:c>
-      <x:c r="Q5" s="52" t="str">
-        <x:v>Effective TFLOP/s</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="20" t="str">
-        <x:v>Attention+MoE · prefill full ISL</x:v>
-      </x:c>
-      <x:c r="B6" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
-        <x:v>3256.329489278666</x:v>
-      </x:c>
-      <x:c r="C6" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$I$3</x:f>
-        <x:v>3193.2814515694904</x:v>
-      </x:c>
-      <x:c r="D6" s="79" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$A$3</x:f>
-        <x:v>14733800617541632</x:v>
-      </x:c>
-      <x:c r="E6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$B$3/'02_HW'!$C$11</x:f>
-        <x:v>560.2822265625</x:v>
-      </x:c>
-      <x:c r="F6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$C$3/'02_HW'!$C$11</x:f>
-        <x:v>448.03125</x:v>
-      </x:c>
-      <x:c r="G6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$D$3/'02_HW'!$C$11</x:f>
-        <x:v>1008.3134765625</x:v>
-      </x:c>
-      <x:c r="H6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$F$3</x:f>
-        <x:v>13608.784811426103</x:v>
-      </x:c>
-      <x:c r="I6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$M$3</x:f>
-        <x:v>623.5135135135135</x:v>
-      </x:c>
-      <x:c r="J6" s="20" t="str">
-        <x:f>'10_AttnMoE_Prefill'!$N$3</x:f>
-        <x:v>compute-side</x:v>
-      </x:c>
-      <x:c r="K6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L6" s="20" t="str">
-        <x:f>'10_AttnMoE_Prefill'!$L$3</x:f>
-        <x:v>FIT</x:v>
-      </x:c>
-      <x:c r="M6" s="20" t="str">
-        <x:f>'10_AttnMoE_Prefill'!$K$3</x:f>
-        <x:v>compute</x:v>
-      </x:c>
-      <x:c r="O6" s="20" t="str">
-        <x:v>Attention+MoE · prefill full ISL</x:v>
-      </x:c>
-      <x:c r="P6" s="82" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$F$3</x:f>
-        <x:v>13608.784811426103</x:v>
-      </x:c>
-      <x:c r="Q6" s="82" t="n">
-        <x:f>('10_AttnMoE_Prefill'!$A$3/('10_AttnMoE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
-        <x:v>4524.665168574642</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="21" t="str">
-        <x:v>HOPE shipped · prefill per 2K chunk</x:v>
-      </x:c>
-      <x:c r="B7" s="66" t="n">
-        <x:f>'20_HOPE_Prefill'!$J$3</x:f>
-        <x:v>87.76370645169284</x:v>
-      </x:c>
-      <x:c r="C7" s="66" t="n">
-        <x:f>'20_HOPE_Prefill'!$I$3</x:f>
-        <x:v>66.93049529092329</x:v>
-      </x:c>
-      <x:c r="D7" s="80" t="n">
-        <x:f>'20_HOPE_Prefill'!$A$3</x:f>
-        <x:v>308817305272320</x:v>
-      </x:c>
-      <x:c r="E7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$B$3/'02_HW'!$C$11</x:f>
-        <x:v>145.6885986328125</x:v>
-      </x:c>
-      <x:c r="F7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$C$3/'02_HW'!$C$11</x:f>
-        <x:v>165.518310546875</x:v>
-      </x:c>
-      <x:c r="G7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$D$3/'02_HW'!$C$11</x:f>
-        <x:v>311.2069091796875</x:v>
-      </x:c>
-      <x:c r="H7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$F$3</x:f>
-        <x:v>924.1714092728231</x:v>
-      </x:c>
-      <x:c r="I7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$M$3</x:f>
-        <x:v>623.5135135135135</x:v>
-      </x:c>
-      <x:c r="J7" s="21" t="str">
-        <x:f>'20_HOPE_Prefill'!$N$3</x:f>
-        <x:v>compute-side</x:v>
-      </x:c>
-      <x:c r="K7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
-        <x:v>94.11181640625</x:v>
-      </x:c>
-      <x:c r="L7" s="21" t="str">
-        <x:f>'20_HOPE_Prefill'!$L$3</x:f>
-        <x:v>EXCEEDS</x:v>
-      </x:c>
-      <x:c r="M7" s="21" t="str">
-        <x:f>'20_HOPE_Prefill'!$K$3</x:f>
-        <x:v>compute</x:v>
-      </x:c>
-      <x:c r="O7" s="21" t="str">
-        <x:v>HOPE shipped · prefill per 2K chunk</x:v>
-      </x:c>
-      <x:c r="P7" s="83" t="n">
-        <x:f>'20_HOPE_Prefill'!$F$3</x:f>
-        <x:v>924.1714092728231</x:v>
-      </x:c>
-      <x:c r="Q7" s="83" t="n">
-        <x:f>('20_HOPE_Prefill'!$A$3/('20_HOPE_Prefill'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
-        <x:v>3518.7359075622003</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="21" t="str">
-        <x:v>Attention+MoE · decode Q=1</x:v>
-      </x:c>
-      <x:c r="B8" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
-        <x:v>10.888036865046827</x:v>
-      </x:c>
-      <x:c r="C8" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$I$3</x:f>
-        <x:v>10.888036865046827</x:v>
-      </x:c>
-      <x:c r="D8" s="80" t="n">
-        <x:f>'11_AttnMoE_Decode'!$A$3</x:f>
-        <x:v>181800013824</x:v>
-      </x:c>
-      <x:c r="E8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$B$3/'02_HW'!$C$11</x:f>
-        <x:v>74.97162500149246</x:v>
-      </x:c>
-      <x:c r="F8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$C$3/'02_HW'!$C$11</x:f>
-        <x:v>0.0664064884185791</x:v>
-      </x:c>
-      <x:c r="G8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$D$3/'02_HW'!$C$11</x:f>
-        <x:v>75.03803148991103</x:v>
-      </x:c>
-      <x:c r="H8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$F$3</x:f>
-        <x:v>2.2563819116505184</x:v>
-      </x:c>
-      <x:c r="I8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$M$3</x:f>
-        <x:v>623.5135135135135</x:v>
-      </x:c>
-      <x:c r="J8" s="21" t="str">
-        <x:f>'11_AttnMoE_Decode'!$N$3</x:f>
-        <x:v>memory-side</x:v>
-      </x:c>
-      <x:c r="K8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$E$3/'02_HW'!$C$11</x:f>
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L8" s="21" t="str">
-        <x:f>'11_AttnMoE_Decode'!$L$3</x:f>
-        <x:v>FIT</x:v>
-      </x:c>
-      <x:c r="M8" s="21" t="str">
-        <x:f>'11_AttnMoE_Decode'!$K$3</x:f>
-        <x:v>memory</x:v>
-      </x:c>
-      <x:c r="O8" s="21" t="str">
-        <x:v>Attention+MoE · decode Q=1</x:v>
-      </x:c>
-      <x:c r="P8" s="83" t="n">
-        <x:f>'11_AttnMoE_Decode'!$F$3</x:f>
-        <x:v>2.2563819116505184</x:v>
-      </x:c>
-      <x:c r="Q8" s="83" t="n">
-        <x:f>('11_AttnMoE_Decode'!$A$3/('11_AttnMoE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
-        <x:v>16.697226146213836</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="22" t="str">
-        <x:v>HOPE shipped · including-online Q=1</x:v>
-      </x:c>
-      <x:c r="B9" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$J$3</x:f>
-        <x:v>30.8139047845359</x:v>
-      </x:c>
-      <x:c r="C9" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$I$3</x:f>
-        <x:v>30.806739814054048</x:v>
-      </x:c>
-      <x:c r="D9" s="81" t="n">
-        <x:f>'21_HOPE_Decode'!$A$3</x:f>
-        <x:v>150789699840</x:v>
-      </x:c>
-      <x:c r="E9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$B$3/'02_HW'!$C$11</x:f>
-        <x:v>84.29126673936844</x:v>
-      </x:c>
-      <x:c r="F9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$C$3/'02_HW'!$C$11</x:f>
-        <x:v>128.02222383022308</x:v>
-      </x:c>
-      <x:c r="G9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$D$3/'02_HW'!$C$11</x:f>
-        <x:v>212.31349056959152</x:v>
-      </x:c>
-      <x:c r="H9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$F$3</x:f>
-        <x:v>0.6614457286898262</x:v>
-      </x:c>
-      <x:c r="I9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$M$3</x:f>
-        <x:v>623.5135135135135</x:v>
-      </x:c>
-      <x:c r="J9" s="22" t="str">
-        <x:f>'21_HOPE_Decode'!$N$3</x:f>
-        <x:v>memory-side</x:v>
-      </x:c>
-      <x:c r="K9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
-        <x:v>94.11181640625</x:v>
-      </x:c>
-      <x:c r="L9" s="22" t="str">
-        <x:f>'21_HOPE_Decode'!$L$3</x:f>
-        <x:v>EXCEEDS</x:v>
-      </x:c>
-      <x:c r="M9" s="22" t="str">
-        <x:f>'21_HOPE_Decode'!$K$3</x:f>
-        <x:v>memory</x:v>
-      </x:c>
-      <x:c r="O9" s="22" t="str">
-        <x:v>HOPE shipped · including-online Q=1</x:v>
-      </x:c>
-      <x:c r="P9" s="84" t="n">
-        <x:f>'21_HOPE_Decode'!$F$3</x:f>
-        <x:v>0.6614457286898262</x:v>
-      </x:c>
-      <x:c r="Q9" s="84" t="n">
-        <x:f>('21_HOPE_Decode'!$A$3/('21_HOPE_Decode'!$J$3/'02_HW'!$C$10))/'02_HW'!$C$12</x:f>
-        <x:v>4.893560257759819</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="50" t="str">
-        <x:v>Crossover summary</x:v>
-      </x:c>
-      <x:c r="B12" s="51" t="str">
-        <x:v>First crossover</x:v>
-      </x:c>
-      <x:c r="C12" s="51" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="D12" s="52" t="str">
-        <x:v>Rule</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="20" t="str">
-        <x:v>Context crossover</x:v>
-      </x:c>
-      <x:c r="B13" s="20" t="str">
-        <x:f>IF('40_Sweeps'!$G$6="YES",'40_Sweeps'!$A$6,IF('40_Sweeps'!$G$7="YES",'40_Sweeps'!$A$7,IF('40_Sweeps'!$G$8="YES",'40_Sweeps'!$A$8,IF('40_Sweeps'!$G$9="YES",'40_Sweeps'!$A$9,IF('40_Sweeps'!$G$10="YES",'40_Sweeps'!$A$10,IF('40_Sweeps'!$G$11="YES",'40_Sweeps'!$A$11,"None in sweep"))))))</x:f>
-        <x:v>None in sweep</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="str">
-        <x:v>tokens</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="str">
-        <x:v>First sweep row where Attention decode ms &gt;= HOPE decode ms</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="22" t="str">
-        <x:v>Batch crossover</x:v>
-      </x:c>
-      <x:c r="B14" s="22" t="str">
-        <x:f>IF('40_Sweeps'!$G$17="YES",'40_Sweeps'!$A$17,IF('40_Sweeps'!$G$18="YES",'40_Sweeps'!$A$18,IF('40_Sweeps'!$G$19="YES",'40_Sweeps'!$A$19,IF('40_Sweeps'!$G$20="YES",'40_Sweeps'!$A$20,IF('40_Sweeps'!$G$21="YES",'40_Sweeps'!$A$21,IF('40_Sweeps'!$G$22="YES",'40_Sweeps'!$A$22,"None in sweep"))))))</x:f>
-        <x:v>None in sweep</x:v>
-      </x:c>
-      <x:c r="C14" s="22" t="str">
-        <x:v>requests</x:v>
-      </x:c>
-      <x:c r="D14" s="22" t="str">
-        <x:v>First sweep row where Attention decode ms &gt;= HOPE decode ms</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="50" t="str">
-        <x:v>End-to-end metric</x:v>
-      </x:c>
-      <x:c r="B17" s="51" t="str">
-        <x:v>ms</x:v>
-      </x:c>
-      <x:c r="C17" s="52" t="str">
-        <x:v>Definition</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="20" t="str">
-        <x:v>Full Attention TTFT</x:v>
-      </x:c>
-      <x:c r="B18" s="65" t="n">
-        <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
-        <x:v>3256.329489278666</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="str">
-        <x:v>Full ISL causal invocation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="21" t="str">
-        <x:v>HOPE forward TTFT</x:v>
-      </x:c>
-      <x:c r="B19" s="66" t="n">
-        <x:f>('20_HOPE_Prefill'!$E$47)*('01_Inputs'!$C$9)</x:f>
-        <x:v>539.123762358741</x:v>
-      </x:c>
-      <x:c r="C19" s="21" t="str">
-        <x:v>64 × (Titans + CMS forward per 2K chunk)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="21" t="str">
-        <x:v>HOPE including-online TTFT</x:v>
-      </x:c>
-      <x:c r="B20" s="66" t="n">
-        <x:f>('20_HOPE_Prefill'!$J$3)*('01_Inputs'!$C$9)</x:f>
-        <x:v>5616.877212908342</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="str">
-        <x:v>64 × (forward + loss + backward/update per 2K chunk)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="21" t="str">
-        <x:v>Full Attention ITL</x:v>
-      </x:c>
-      <x:c r="B21" s="66" t="n">
-        <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
-        <x:v>10.888036865046827</x:v>
-      </x:c>
-      <x:c r="C21" s="21" t="str">
-        <x:v>One Q=1 Flash-Decode invocation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="21" t="str">
-        <x:v>HOPE forward ITL</x:v>
-      </x:c>
-      <x:c r="B22" s="66" t="n">
-        <x:f>'21_HOPE_Decode'!$B$6</x:f>
-        <x:v>0.6194056302702703</x:v>
-      </x:c>
-      <x:c r="C22" s="21" t="str">
-        <x:v>One Q=1 Titans + CMS forward</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="22" t="str">
-        <x:v>HOPE including-online ITL</x:v>
-      </x:c>
-      <x:c r="B23" s="67" t="n">
-        <x:f>'21_HOPE_Decode'!$B$8</x:f>
-        <x:v>30.813904784535897</x:v>
-      </x:c>
-      <x:c r="C23" s="22" t="str">
-        <x:v>One Q=1 forward + amortized online overhead; no OSL multiplier</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:AA1"/>
-    <x:mergeCell ref="A2:AA2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5034ad5cb8b49ea"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>40 · Context and batch sweeps</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -12745,11 +12350,10 @@
       <x:c r="AA1" s="3"/>
       <x:c r="AB1" s="3"/>
       <x:c r="AC1" s="3"/>
-      <x:c r="AD1" s="3"/>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>All sweep outputs are formulas. Imported engine values appear only on 90_QA as references.</x:v>
+        <x:v>Primary prefill rows are full-sequence TTFT; decode rows are one-token ITL. Forward serving and including-online sensitivity remain separate.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -12779,7 +12383,588 @@
       <x:c r="AA2" s="7"/>
       <x:c r="AB2" s="7"/>
       <x:c r="AC2" s="7"/>
-      <x:c r="AD2" s="7"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>Architecture / phase</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="str">
+        <x:v>Stagewise ms</x:v>
+      </x:c>
+      <x:c r="C5" s="28" t="str">
+        <x:v>Aggregate ms</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str">
+        <x:v>Compute ms</x:v>
+      </x:c>
+      <x:c r="E5" s="28" t="str">
+        <x:v>HBM ms</x:v>
+      </x:c>
+      <x:c r="F5" s="28" t="str">
+        <x:v>FLOPs</x:v>
+      </x:c>
+      <x:c r="G5" s="28" t="str">
+        <x:v>HBM read GiB</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="str">
+        <x:v>HBM write GiB</x:v>
+      </x:c>
+      <x:c r="I5" s="28" t="str">
+        <x:v>HBM total GiB</x:v>
+      </x:c>
+      <x:c r="J5" s="28" t="str">
+        <x:v>AI FLOP/B</x:v>
+      </x:c>
+      <x:c r="K5" s="28" t="str">
+        <x:v>Ridge AI</x:v>
+      </x:c>
+      <x:c r="L5" s="28" t="str">
+        <x:v>Ridge class</x:v>
+      </x:c>
+      <x:c r="M5" s="28" t="str">
+        <x:v>State GiB</x:v>
+      </x:c>
+      <x:c r="N5" s="28" t="str">
+        <x:v>HBM fit</x:v>
+      </x:c>
+      <x:c r="O5" s="15" t="str">
+        <x:v>Bound</x:v>
+      </x:c>
+      <x:c r="Q5" s="50" t="str">
+        <x:v>Case</x:v>
+      </x:c>
+      <x:c r="R5" s="51" t="str">
+        <x:v>AI FLOP/B</x:v>
+      </x:c>
+      <x:c r="S5" s="52" t="str">
+        <x:v>Effective TFLOP/s</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>Attention+MoE · TTFT full ISL</x:v>
+      </x:c>
+      <x:c r="B6" s="65" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$J$3)*(1)</x:f>
+        <x:v>3256.329489278666</x:v>
+      </x:c>
+      <x:c r="C6" s="65" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$I$3)*(1)</x:f>
+        <x:v>3193.2814515694904</x:v>
+      </x:c>
+      <x:c r="D6" s="65" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$G$3)*(1)</x:f>
+        <x:v>3193.2814515694904</x:v>
+      </x:c>
+      <x:c r="E6" s="65" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$H$3)*(1)</x:f>
+        <x:v>146.30653398486487</x:v>
+      </x:c>
+      <x:c r="F6" s="81" t="n">
+        <x:f>('10_AttnMoE_Prefill'!$A$3)*(1)</x:f>
+        <x:v>14733800617541632</x:v>
+      </x:c>
+      <x:c r="G6" s="84" t="n">
+        <x:f>(('10_AttnMoE_Prefill'!$B$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>560.2822265625</x:v>
+      </x:c>
+      <x:c r="H6" s="84" t="n">
+        <x:f>(('10_AttnMoE_Prefill'!$C$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>448.03125</x:v>
+      </x:c>
+      <x:c r="I6" s="84" t="n">
+        <x:f>(('10_AttnMoE_Prefill'!$D$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>1008.3134765625</x:v>
+      </x:c>
+      <x:c r="J6" s="84" t="n">
+        <x:f>F6/(I6*('02_HW'!$C$11))</x:f>
+        <x:v>13608.784811426103</x:v>
+      </x:c>
+      <x:c r="K6" s="84" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$M$3</x:f>
+        <x:v>623.5135135135135</x:v>
+      </x:c>
+      <x:c r="L6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$N$3</x:f>
+        <x:v>compute-side</x:v>
+      </x:c>
+      <x:c r="M6" s="84" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$L$3</x:f>
+        <x:v>FIT</x:v>
+      </x:c>
+      <x:c r="O6" s="20" t="str">
+        <x:f>'10_AttnMoE_Prefill'!$K$3</x:f>
+        <x:v>compute</x:v>
+      </x:c>
+      <x:c r="Q6" s="20" t="str">
+        <x:v>Attention+MoE · TTFT full ISL</x:v>
+      </x:c>
+      <x:c r="R6" s="84" t="n">
+        <x:f>J6</x:f>
+        <x:v>13608.784811426103</x:v>
+      </x:c>
+      <x:c r="S6" s="84" t="n">
+        <x:f>(F6/(B6/('02_HW'!$C$10)))/'02_HW'!$C$12</x:f>
+        <x:v>4524.665168574642</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="21" t="str">
+        <x:v>HOPE shipped · TTFT (64×2K, including online)</x:v>
+      </x:c>
+      <x:c r="B7" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$J$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>5616.877212908342</x:v>
+      </x:c>
+      <x:c r="C7" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$I$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>4283.5516986190905</x:v>
+      </x:c>
+      <x:c r="D7" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$G$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>4283.5516986190905</x:v>
+      </x:c>
+      <x:c r="E7" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$H$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>2889.9967507372976</x:v>
+      </x:c>
+      <x:c r="F7" s="82" t="n">
+        <x:f>('20_HOPE_Prefill'!$A$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>19764307537428480</x:v>
+      </x:c>
+      <x:c r="G7" s="85" t="n">
+        <x:f>(('20_HOPE_Prefill'!$B$3)*('01_Inputs'!$C$9))/'02_HW'!$C$11</x:f>
+        <x:v>9324.0703125</x:v>
+      </x:c>
+      <x:c r="H7" s="85" t="n">
+        <x:f>(('20_HOPE_Prefill'!$C$3)*('01_Inputs'!$C$9))/'02_HW'!$C$11</x:f>
+        <x:v>10593.171875</x:v>
+      </x:c>
+      <x:c r="I7" s="85" t="n">
+        <x:f>(('20_HOPE_Prefill'!$D$3)*('01_Inputs'!$C$9))/'02_HW'!$C$11</x:f>
+        <x:v>19917.2421875</x:v>
+      </x:c>
+      <x:c r="J7" s="85" t="n">
+        <x:f>F7/(I7*('02_HW'!$C$11))</x:f>
+        <x:v>924.1714092728231</x:v>
+      </x:c>
+      <x:c r="K7" s="85" t="n">
+        <x:f>'20_HOPE_Prefill'!$M$3</x:f>
+        <x:v>623.5135135135135</x:v>
+      </x:c>
+      <x:c r="L7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$N$3</x:f>
+        <x:v>compute-side</x:v>
+      </x:c>
+      <x:c r="M7" s="85" t="n">
+        <x:f>'20_HOPE_Prefill'!$E$3/'02_HW'!$C$11</x:f>
+        <x:v>94.11181640625</x:v>
+      </x:c>
+      <x:c r="N7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$L$3</x:f>
+        <x:v>EXCEEDS</x:v>
+      </x:c>
+      <x:c r="O7" s="21" t="str">
+        <x:f>'20_HOPE_Prefill'!$K$3</x:f>
+        <x:v>compute</x:v>
+      </x:c>
+      <x:c r="Q7" s="21" t="str">
+        <x:v>HOPE shipped · TTFT (64×2K, including online)</x:v>
+      </x:c>
+      <x:c r="R7" s="85" t="n">
+        <x:f>J7</x:f>
+        <x:v>924.1714092728231</x:v>
+      </x:c>
+      <x:c r="S7" s="85" t="n">
+        <x:f>(F7/(B7/('02_HW'!$C$10)))/'02_HW'!$C$12</x:f>
+        <x:v>3518.7359075622003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="21" t="str">
+        <x:v>Attention+MoE · ITL Q=1</x:v>
+      </x:c>
+      <x:c r="B8" s="66" t="n">
+        <x:f>('11_AttnMoE_Decode'!$J$3)*(1)</x:f>
+        <x:v>10.888036865046827</x:v>
+      </x:c>
+      <x:c r="C8" s="66" t="n">
+        <x:f>('11_AttnMoE_Decode'!$I$3)*(1)</x:f>
+        <x:v>10.888036865046827</x:v>
+      </x:c>
+      <x:c r="D8" s="66" t="n">
+        <x:f>('11_AttnMoE_Decode'!$G$3)*(1)</x:f>
+        <x:v>0.039401823542262675</x:v>
+      </x:c>
+      <x:c r="E8" s="66" t="n">
+        <x:f>('11_AttnMoE_Decode'!$H$3)*(1)</x:f>
+        <x:v>10.888036865046827</x:v>
+      </x:c>
+      <x:c r="F8" s="82" t="n">
+        <x:f>('11_AttnMoE_Decode'!$A$3)*(1)</x:f>
+        <x:v>181800013824</x:v>
+      </x:c>
+      <x:c r="G8" s="85" t="n">
+        <x:f>(('11_AttnMoE_Decode'!$B$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>74.97162500149246</x:v>
+      </x:c>
+      <x:c r="H8" s="85" t="n">
+        <x:f>(('11_AttnMoE_Decode'!$C$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>0.0664064884185791</x:v>
+      </x:c>
+      <x:c r="I8" s="85" t="n">
+        <x:f>(('11_AttnMoE_Decode'!$D$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>75.03803148991103</x:v>
+      </x:c>
+      <x:c r="J8" s="85" t="n">
+        <x:f>F8/(I8*('02_HW'!$C$11))</x:f>
+        <x:v>2.2563819116505184</x:v>
+      </x:c>
+      <x:c r="K8" s="85" t="n">
+        <x:f>'11_AttnMoE_Decode'!$M$3</x:f>
+        <x:v>623.5135135135135</x:v>
+      </x:c>
+      <x:c r="L8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$N$3</x:f>
+        <x:v>memory-side</x:v>
+      </x:c>
+      <x:c r="M8" s="85" t="n">
+        <x:f>'11_AttnMoE_Decode'!$E$3/'02_HW'!$C$11</x:f>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$L$3</x:f>
+        <x:v>FIT</x:v>
+      </x:c>
+      <x:c r="O8" s="21" t="str">
+        <x:f>'11_AttnMoE_Decode'!$K$3</x:f>
+        <x:v>memory</x:v>
+      </x:c>
+      <x:c r="Q8" s="21" t="str">
+        <x:v>Attention+MoE · ITL Q=1</x:v>
+      </x:c>
+      <x:c r="R8" s="85" t="n">
+        <x:f>J8</x:f>
+        <x:v>2.2563819116505184</x:v>
+      </x:c>
+      <x:c r="S8" s="85" t="n">
+        <x:f>(F8/(B8/('02_HW'!$C$10)))/'02_HW'!$C$12</x:f>
+        <x:v>16.697226146213836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="22" t="str">
+        <x:v>HOPE shipped · ITL Q=1 (including online)</x:v>
+      </x:c>
+      <x:c r="B9" s="67" t="n">
+        <x:f>('21_HOPE_Decode'!$J$3)*(1)</x:f>
+        <x:v>30.8139047845359</x:v>
+      </x:c>
+      <x:c r="C9" s="67" t="n">
+        <x:f>('21_HOPE_Decode'!$I$3)*(1)</x:f>
+        <x:v>30.806739814054048</x:v>
+      </x:c>
+      <x:c r="D9" s="67" t="n">
+        <x:f>('21_HOPE_Decode'!$G$3)*(1)</x:f>
+        <x:v>0.03268090590377114</x:v>
+      </x:c>
+      <x:c r="E9" s="67" t="n">
+        <x:f>('21_HOPE_Decode'!$H$3)*(1)</x:f>
+        <x:v>30.806739814054048</x:v>
+      </x:c>
+      <x:c r="F9" s="83" t="n">
+        <x:f>('21_HOPE_Decode'!$A$3)*(1)</x:f>
+        <x:v>150789699840</x:v>
+      </x:c>
+      <x:c r="G9" s="86" t="n">
+        <x:f>(('21_HOPE_Decode'!$B$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>84.29126673936844</x:v>
+      </x:c>
+      <x:c r="H9" s="86" t="n">
+        <x:f>(('21_HOPE_Decode'!$C$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>128.02222383022308</x:v>
+      </x:c>
+      <x:c r="I9" s="86" t="n">
+        <x:f>(('21_HOPE_Decode'!$D$3)*(1))/'02_HW'!$C$11</x:f>
+        <x:v>212.31349056959152</x:v>
+      </x:c>
+      <x:c r="J9" s="86" t="n">
+        <x:f>F9/(I9*('02_HW'!$C$11))</x:f>
+        <x:v>0.6614457286898262</x:v>
+      </x:c>
+      <x:c r="K9" s="86" t="n">
+        <x:f>'21_HOPE_Decode'!$M$3</x:f>
+        <x:v>623.5135135135135</x:v>
+      </x:c>
+      <x:c r="L9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$N$3</x:f>
+        <x:v>memory-side</x:v>
+      </x:c>
+      <x:c r="M9" s="86" t="n">
+        <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
+        <x:v>94.11181640625</x:v>
+      </x:c>
+      <x:c r="N9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$L$3</x:f>
+        <x:v>EXCEEDS</x:v>
+      </x:c>
+      <x:c r="O9" s="22" t="str">
+        <x:f>'21_HOPE_Decode'!$K$3</x:f>
+        <x:v>memory</x:v>
+      </x:c>
+      <x:c r="Q9" s="22" t="str">
+        <x:v>HOPE shipped · ITL Q=1 (including online)</x:v>
+      </x:c>
+      <x:c r="R9" s="86" t="n">
+        <x:f>J9</x:f>
+        <x:v>0.6614457286898262</x:v>
+      </x:c>
+      <x:c r="S9" s="86" t="n">
+        <x:f>(F9/(B9/('02_HW'!$C$10)))/'02_HW'!$C$12</x:f>
+        <x:v>4.893560257759819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="50" t="str">
+        <x:v>Serving comparison</x:v>
+      </x:c>
+      <x:c r="B12" s="51" t="str">
+        <x:v>First satisfying grid point</x:v>
+      </x:c>
+      <x:c r="C12" s="51" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D12" s="52" t="str">
+        <x:v>Rule</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="20" t="str">
+        <x:v>Context crossover · forward primary</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="n">
+        <x:f>IF('40_Sweeps'!$H$6="YES",'40_Sweeps'!$A$6,IF('40_Sweeps'!$H$7="YES",'40_Sweeps'!$A$7,IF('40_Sweeps'!$H$8="YES",'40_Sweeps'!$A$8,IF('40_Sweeps'!$H$9="YES",'40_Sweeps'!$A$9,IF('40_Sweeps'!$H$10="YES",'40_Sweeps'!$A$10,IF('40_Sweeps'!$H$11="YES",'40_Sweeps'!$A$11,"None in sweep"))))))</x:f>
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>tokens</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>First grid row where Attention ITL &gt;= HOPE forward ITL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="21" t="str">
+        <x:v>Batch crossover · forward primary</x:v>
+      </x:c>
+      <x:c r="B14" s="21" t="n">
+        <x:f>IF('40_Sweeps'!$H$17="YES",'40_Sweeps'!$A$17,IF('40_Sweeps'!$H$18="YES",'40_Sweeps'!$A$18,IF('40_Sweeps'!$H$19="YES",'40_Sweeps'!$A$19,IF('40_Sweeps'!$H$20="YES",'40_Sweeps'!$A$20,IF('40_Sweeps'!$H$21="YES",'40_Sweeps'!$A$21,IF('40_Sweeps'!$H$22="YES",'40_Sweeps'!$A$22,"None in sweep"))))))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="21" t="str">
+        <x:v>requests</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="str">
+        <x:v>First grid row where Attention ITL &gt;= HOPE forward ITL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="21" t="str">
+        <x:v>Context crossover · including-online sensitivity</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="str">
+        <x:f>IF('40_Sweeps'!$J$6="YES",'40_Sweeps'!$A$6,IF('40_Sweeps'!$J$7="YES",'40_Sweeps'!$A$7,IF('40_Sweeps'!$J$8="YES",'40_Sweeps'!$A$8,IF('40_Sweeps'!$J$9="YES",'40_Sweeps'!$A$9,IF('40_Sweeps'!$J$10="YES",'40_Sweeps'!$A$10,IF('40_Sweeps'!$J$11="YES",'40_Sweeps'!$A$11,"None in sweep"))))))</x:f>
+        <x:v>None in sweep</x:v>
+      </x:c>
+      <x:c r="C15" s="21" t="str">
+        <x:v>tokens</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="str">
+        <x:v>Sensitivity: first grid row where Attention ITL &gt;= HOPE including-online ITL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="22" t="str">
+        <x:v>Batch crossover · including-online sensitivity</x:v>
+      </x:c>
+      <x:c r="B16" s="22" t="str">
+        <x:f>IF('40_Sweeps'!$J$17="YES",'40_Sweeps'!$A$17,IF('40_Sweeps'!$J$18="YES",'40_Sweeps'!$A$18,IF('40_Sweeps'!$J$19="YES",'40_Sweeps'!$A$19,IF('40_Sweeps'!$J$20="YES",'40_Sweeps'!$A$20,IF('40_Sweeps'!$J$21="YES",'40_Sweeps'!$A$21,IF('40_Sweeps'!$J$22="YES",'40_Sweeps'!$A$22,"None in sweep"))))))</x:f>
+        <x:v>None in sweep</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="str">
+        <x:v>requests</x:v>
+      </x:c>
+      <x:c r="D16" s="22" t="str">
+        <x:v>Sensitivity: first grid row where Attention ITL &gt;= HOPE including-online ITL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="50" t="str">
+        <x:v>End-to-end metric</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="str">
+        <x:v>ms</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="20" t="str">
+        <x:v>Full Attention TTFT</x:v>
+      </x:c>
+      <x:c r="B20" s="65" t="n">
+        <x:f>'10_AttnMoE_Prefill'!$J$3</x:f>
+        <x:v>3256.329489278666</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>Full ISL causal invocation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="21" t="str">
+        <x:v>HOPE forward TTFT</x:v>
+      </x:c>
+      <x:c r="B21" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$E$47)*('01_Inputs'!$C$9)</x:f>
+        <x:v>539.123762358741</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="str">
+        <x:v>64 × (Titans + CMS forward per 2K chunk)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="21" t="str">
+        <x:v>HOPE including-online TTFT</x:v>
+      </x:c>
+      <x:c r="B22" s="66" t="n">
+        <x:f>('20_HOPE_Prefill'!$J$3)*('01_Inputs'!$C$9)</x:f>
+        <x:v>5616.877212908342</x:v>
+      </x:c>
+      <x:c r="C22" s="21" t="str">
+        <x:v>64 × (forward + loss + backward/update per 2K chunk)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="21" t="str">
+        <x:v>Full Attention ITL</x:v>
+      </x:c>
+      <x:c r="B23" s="66" t="n">
+        <x:f>'11_AttnMoE_Decode'!$J$3</x:f>
+        <x:v>10.888036865046827</x:v>
+      </x:c>
+      <x:c r="C23" s="21" t="str">
+        <x:v>One Q=1 Flash-Decode invocation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="21" t="str">
+        <x:v>HOPE forward ITL</x:v>
+      </x:c>
+      <x:c r="B24" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="C24" s="21" t="str">
+        <x:v>One Q=1 Titans + CMS forward</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="22" t="str">
+        <x:v>HOPE including-online ITL</x:v>
+      </x:c>
+      <x:c r="B25" s="67" t="n">
+        <x:f>'21_HOPE_Decode'!$B$8</x:f>
+        <x:v>30.813904784535897</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="str">
+        <x:v>One Q=1 forward + amortized online overhead; no OSL multiplier</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:AC1"/>
+    <x:mergeCell ref="A2:AC2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc73fe9313bb64d23"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="16" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>40 · Context and batch sweeps</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
+      <x:c r="L1" s="3"/>
+      <x:c r="M1" s="3"/>
+      <x:c r="N1" s="3"/>
+      <x:c r="O1" s="3"/>
+      <x:c r="P1" s="3"/>
+      <x:c r="Q1" s="3"/>
+      <x:c r="R1" s="3"/>
+      <x:c r="S1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Forward-only ITL is the primary serving axis; including-online ITL is retained as a separate sensitivity. Imported engine values appear only on 90_QA.</x:v>
+      </x:c>
+      <x:c r="B2" s="7"/>
+      <x:c r="C2" s="7"/>
+      <x:c r="D2" s="7"/>
+      <x:c r="E2" s="7"/>
+      <x:c r="F2" s="7"/>
+      <x:c r="G2" s="7"/>
+      <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7"/>
+      <x:c r="J2" s="7"/>
+      <x:c r="K2" s="7"/>
+      <x:c r="L2" s="7"/>
+      <x:c r="M2" s="7"/>
+      <x:c r="N2" s="7"/>
+      <x:c r="O2" s="7"/>
+      <x:c r="P2" s="7"/>
+      <x:c r="Q2" s="7"/>
+      <x:c r="R2" s="7"/>
+      <x:c r="S2" s="7"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -12789,550 +12974,280 @@
         <x:v>Attention ITL ms</x:v>
       </x:c>
       <x:c r="C5" s="28" t="str">
+        <x:v>HOPE forward ITL ms (primary)</x:v>
+      </x:c>
+      <x:c r="D5" s="28" t="str">
         <x:v>HOPE including-online ITL ms</x:v>
       </x:c>
-      <x:c r="D5" s="28" t="str">
+      <x:c r="E5" s="28" t="str">
         <x:v>Attention state GiB</x:v>
       </x:c>
-      <x:c r="E5" s="28" t="str">
+      <x:c r="F5" s="28" t="str">
         <x:v>HOPE state GiB</x:v>
       </x:c>
-      <x:c r="F5" s="28" t="str">
-        <x:v>Attn / HOPE ITL</x:v>
-      </x:c>
-      <x:c r="G5" s="15" t="str">
-        <x:v>Attention &gt;= HOPE?</x:v>
-      </x:c>
-      <x:c r="H5" s="50" t="str">
-        <x:v>qkv_projection</x:v>
-      </x:c>
-      <x:c r="I5" s="51" t="str">
-        <x:v>kv_cache_append</x:v>
-      </x:c>
-      <x:c r="J5" s="51" t="str">
-        <x:v>q_materialization_read</x:v>
-      </x:c>
-      <x:c r="K5" s="51" t="str">
-        <x:v>flash_decode_partials</x:v>
-      </x:c>
-      <x:c r="L5" s="51" t="str">
-        <x:v>flash_decode_reduce</x:v>
-      </x:c>
-      <x:c r="M5" s="51" t="str">
-        <x:v>output_projection</x:v>
-      </x:c>
-      <x:c r="N5" s="51" t="str">
-        <x:v>moe_router</x:v>
-      </x:c>
-      <x:c r="O5" s="51" t="str">
-        <x:v>moe_dispatch</x:v>
-      </x:c>
-      <x:c r="P5" s="51" t="str">
-        <x:v>expert_up_projection</x:v>
-      </x:c>
-      <x:c r="Q5" s="51" t="str">
-        <x:v>expert_gate_projection</x:v>
-      </x:c>
-      <x:c r="R5" s="51" t="str">
-        <x:v>expert_swiglu_activation</x:v>
-      </x:c>
-      <x:c r="S5" s="51" t="str">
-        <x:v>expert_down_projection</x:v>
-      </x:c>
-      <x:c r="T5" s="52" t="str">
-        <x:v>moe_combine</x:v>
+      <x:c r="G5" s="28" t="str">
+        <x:v>Attn / HOPE forward ITL</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="str">
+        <x:v>Forward primary crossover?</x:v>
+      </x:c>
+      <x:c r="I5" s="28" t="str">
+        <x:v>Attn / HOPE including-online ITL</x:v>
+      </x:c>
+      <x:c r="J5" s="15" t="str">
+        <x:v>Including-online sensitivity?</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="76" t="n">
+      <x:c r="A6" s="78" t="n">
         <x:f>'01_Inputs'!$B$64</x:f>
         <x:v>1024</x:v>
       </x:c>
       <x:c r="B6" s="65" t="n">
-        <x:f>SUM(H6:T6)</x:f>
+        <x:f>SUM(C26:C38)</x:f>
         <x:v>1.655891982884663</x:v>
       </x:c>
       <x:c r="C6" s="65" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D6" s="65" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D6" s="65" t="n">
+      <x:c r="E6" s="65" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$6)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="E6" s="65" t="n">
+      <x:c r="F6" s="65" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F6" s="65" t="n">
+      <x:c r="G6" s="65" t="n">
         <x:f>B6/C6</x:f>
+        <x:v>2.6733563628766728</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="str">
+        <x:f>IF(B6&gt;=C6,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I6" s="65" t="n">
+        <x:f>B6/D6</x:f>
         <x:v>0.05373846626915262</x:v>
       </x:c>
-      <x:c r="G6" s="20" t="str">
-        <x:f>IF(B6&gt;=C6,"YES","NO")</x:f>
+      <x:c r="J6" s="20" t="str">
+        <x:f>IF(B6&gt;=D6,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I6" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J6" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K6" s="20" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$6)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$6)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$6)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0725855481081081</x:v>
-      </x:c>
-      <x:c r="L6" s="20" t="n">
-        <x:f>(MAX((((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$6)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O6" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R6" s="20" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S6" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T6" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="77" t="n">
+      <x:c r="A7" s="79" t="n">
         <x:f>'01_Inputs'!$C$64</x:f>
         <x:v>4096</x:v>
       </x:c>
       <x:c r="B7" s="66" t="n">
-        <x:f>SUM(H7:T7)</x:f>
+        <x:f>SUM(D26:D38)</x:f>
         <x:v>1.8741135785603384</x:v>
       </x:c>
       <x:c r="C7" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D7" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D7" s="66" t="n">
+      <x:c r="E7" s="66" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$7)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E7" s="66" t="n">
+      <x:c r="F7" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F7" s="66" t="n">
+      <x:c r="G7" s="66" t="n">
         <x:f>B7/C7</x:f>
+        <x:v>3.0256644224279836</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="str">
+        <x:f>IF(B7&gt;=C7,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I7" s="66" t="n">
+        <x:f>B7/D7</x:f>
         <x:v>0.06082038585063945</x:v>
       </x:c>
-      <x:c r="G7" s="21" t="str">
-        <x:f>IF(B7&gt;=C7,"YES","NO")</x:f>
+      <x:c r="J7" s="21" t="str">
+        <x:f>IF(B7&gt;=D7,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I7" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J7" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K7" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$7)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$7)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$7)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.2904861059459459</x:v>
-      </x:c>
-      <x:c r="L7" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$7)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00032103783783783783</x:v>
-      </x:c>
-      <x:c r="M7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O7" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R7" s="21" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S7" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T7" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="77" t="n">
+      <x:c r="A8" s="79" t="n">
         <x:f>'01_Inputs'!$D$64</x:f>
         <x:v>16384</x:v>
       </x:c>
       <x:c r="B8" s="66" t="n">
-        <x:f>SUM(H8:T8)</x:f>
+        <x:f>SUM(E26:E38)</x:f>
         <x:v>2.746428735317095</x:v>
       </x:c>
       <x:c r="C8" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D8" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D8" s="66" t="n">
+      <x:c r="E8" s="66" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$8)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E8" s="66" t="n">
+      <x:c r="F8" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F8" s="66" t="n">
+      <x:c r="G8" s="66" t="n">
         <x:f>B8/C8</x:f>
+        <x:v>4.433974444369715</x:v>
+      </x:c>
+      <x:c r="H8" s="21" t="str">
+        <x:f>IF(B8&gt;=C8,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I8" s="66" t="n">
+        <x:f>B8/D8</x:f>
         <x:v>0.08912952624866302</x:v>
       </x:c>
-      <x:c r="G8" s="21" t="str">
-        <x:f>IF(B8&gt;=C8,"YES","NO")</x:f>
+      <x:c r="J8" s="21" t="str">
+        <x:f>IF(B8&gt;=D8,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I8" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J8" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K8" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$8)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$8)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$8)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>1.1619444237837837</x:v>
-      </x:c>
-      <x:c r="L8" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$8)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0011778767567567567</x:v>
-      </x:c>
-      <x:c r="M8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O8" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R8" s="21" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S8" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T8" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="77" t="n">
+      <x:c r="A9" s="79" t="n">
         <x:f>'01_Inputs'!$E$64</x:f>
         <x:v>65536</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
-        <x:f>SUM(H9:T9)</x:f>
+        <x:f>SUM(F26:F38)</x:f>
         <x:v>6.2356893623441225</x:v>
       </x:c>
       <x:c r="C9" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D9" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D9" s="66" t="n">
+      <x:c r="E9" s="66" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$9)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E9" s="66" t="n">
+      <x:c r="F9" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F9" s="66" t="n">
+      <x:c r="G9" s="66" t="n">
         <x:f>B9/C9</x:f>
+        <x:v>10.067214532136644</x:v>
+      </x:c>
+      <x:c r="H9" s="21" t="str">
+        <x:f>IF(B9&gt;=C9,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I9" s="66" t="n">
+        <x:f>B9/D9</x:f>
         <x:v>0.2023660878407573</x:v>
       </x:c>
-      <x:c r="G9" s="21" t="str">
-        <x:f>IF(B9&gt;=C9,"YES","NO")</x:f>
+      <x:c r="J9" s="21" t="str">
+        <x:f>IF(B9&gt;=D9,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I9" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J9" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K9" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$9)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$9)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$9)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>4.647777695135135</x:v>
-      </x:c>
-      <x:c r="L9" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$9)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.004605232432432433</x:v>
-      </x:c>
-      <x:c r="M9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O9" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R9" s="21" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S9" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T9" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="77" t="n">
+      <x:c r="A10" s="79" t="n">
         <x:f>'01_Inputs'!$F$64</x:f>
         <x:v>131072</x:v>
       </x:c>
       <x:c r="B10" s="66" t="n">
-        <x:f>SUM(H10:T10)</x:f>
+        <x:f>SUM(G26:G38)</x:f>
         <x:v>10.888036865046827</x:v>
       </x:c>
       <x:c r="C10" s="66" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D10" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D10" s="66" t="n">
+      <x:c r="E10" s="66" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$10)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E10" s="66" t="n">
+      <x:c r="F10" s="66" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F10" s="66" t="n">
+      <x:c r="G10" s="66" t="n">
         <x:f>B10/C10</x:f>
+        <x:v>17.578201315825886</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="str">
+        <x:f>IF(B10&gt;=C10,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I10" s="66" t="n">
+        <x:f>B10/D10</x:f>
         <x:v>0.3533481699635497</x:v>
       </x:c>
-      <x:c r="G10" s="21" t="str">
-        <x:f>IF(B10&gt;=C10,"YES","NO")</x:f>
+      <x:c r="J10" s="21" t="str">
+        <x:f>IF(B10&gt;=D10,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I10" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J10" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K10" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$10)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$10)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$10)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>9.29555539027027</x:v>
-      </x:c>
-      <x:c r="L10" s="21" t="n">
-        <x:f>(MAX((((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$10)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00917504</x:v>
-      </x:c>
-      <x:c r="M10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O10" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R10" s="21" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S10" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T10" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="78" t="n">
+      <x:c r="A11" s="80" t="n">
         <x:f>'01_Inputs'!$G$64</x:f>
         <x:v>262144</x:v>
       </x:c>
       <x:c r="B11" s="67" t="n">
-        <x:f>SUM(H11:T11)</x:f>
+        <x:f>SUM(H26:H38)</x:f>
         <x:v>20.192731870452235</x:v>
       </x:c>
       <x:c r="C11" s="67" t="n">
+        <x:f>'21_HOPE_Decode'!$B$6</x:f>
+        <x:v>0.6194056302702703</x:v>
+      </x:c>
+      <x:c r="D11" s="67" t="n">
         <x:f>'21_HOPE_Decode'!$B$8</x:f>
         <x:v>30.813904784535897</x:v>
       </x:c>
-      <x:c r="D11" s="67" t="n">
+      <x:c r="E11" s="67" t="n">
         <x:f>(2*('01_Inputs'!$C$5)*($A$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>128</x:v>
       </x:c>
-      <x:c r="E11" s="67" t="n">
+      <x:c r="F11" s="67" t="n">
         <x:f>'21_HOPE_Decode'!$E$3/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F11" s="67" t="n">
+      <x:c r="G11" s="67" t="n">
         <x:f>B11/C11</x:f>
+        <x:v>32.60017488320437</x:v>
+      </x:c>
+      <x:c r="H11" s="22" t="str">
+        <x:f>IF(B11&gt;=C11,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I11" s="67" t="n">
+        <x:f>B11/D11</x:f>
         <x:v>0.6553123342091345</x:v>
       </x:c>
-      <x:c r="G11" s="22" t="str">
-        <x:f>IF(B11&gt;=C11,"YES","NO")</x:f>
+      <x:c r="J11" s="22" t="str">
+        <x:f>IF(B11&gt;=D11,"YES","NO")</x:f>
         <x:v>NO</x:v>
-      </x:c>
-      <x:c r="H11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027277145945945946</x:v>
-      </x:c>
-      <x:c r="I11" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
-      </x:c>
-      <x:c r="J11" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="K11" s="22" t="n">
-        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*($A$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*($A$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>18.59111078054054</x:v>
-      </x:c>
-      <x:c r="L11" s="22" t="n">
-        <x:f>(MAX((((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((($A$11)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.018314655135135135</x:v>
-      </x:c>
-      <x:c r="M11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009139615135135136</x:v>
-      </x:c>
-      <x:c r="N11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00017715891891891892</x:v>
-      </x:c>
-      <x:c r="O11" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007088432432432432</x:v>
-      </x:c>
-      <x:c r="P11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="Q11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="R11" s="22" t="n">
-        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0002125491891891892</x:v>
-      </x:c>
-      <x:c r="S11" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5154173189795723</x:v>
-      </x:c>
-      <x:c r="T11" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00007084972972972974</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -13343,558 +13258,2256 @@
         <x:v>Attention ITL ms</x:v>
       </x:c>
       <x:c r="C16" s="28" t="str">
+        <x:v>HOPE forward ITL ms (primary)</x:v>
+      </x:c>
+      <x:c r="D16" s="28" t="str">
         <x:v>HOPE including-online ITL ms</x:v>
       </x:c>
-      <x:c r="D16" s="28" t="str">
+      <x:c r="E16" s="28" t="str">
         <x:v>Attention state GiB</x:v>
       </x:c>
-      <x:c r="E16" s="28" t="str">
+      <x:c r="F16" s="28" t="str">
         <x:v>HOPE state GiB</x:v>
       </x:c>
-      <x:c r="F16" s="28" t="str">
-        <x:v>Attn / HOPE ITL</x:v>
-      </x:c>
-      <x:c r="G16" s="15" t="str">
-        <x:v>Attention &gt;= HOPE?</x:v>
-      </x:c>
-      <x:c r="H16" s="50" t="str">
-        <x:v>qkv_projection</x:v>
-      </x:c>
-      <x:c r="I16" s="51" t="str">
-        <x:v>kv_cache_append</x:v>
-      </x:c>
-      <x:c r="J16" s="51" t="str">
-        <x:v>q_materialization_read</x:v>
-      </x:c>
-      <x:c r="K16" s="51" t="str">
-        <x:v>flash_decode_partials</x:v>
-      </x:c>
-      <x:c r="L16" s="51" t="str">
-        <x:v>flash_decode_reduce</x:v>
-      </x:c>
-      <x:c r="M16" s="51" t="str">
-        <x:v>output_projection</x:v>
-      </x:c>
-      <x:c r="N16" s="51" t="str">
-        <x:v>moe_router</x:v>
-      </x:c>
-      <x:c r="O16" s="51" t="str">
-        <x:v>moe_dispatch</x:v>
-      </x:c>
-      <x:c r="P16" s="51" t="str">
-        <x:v>expert_up_projection</x:v>
-      </x:c>
-      <x:c r="Q16" s="51" t="str">
-        <x:v>expert_gate_projection</x:v>
-      </x:c>
-      <x:c r="R16" s="51" t="str">
-        <x:v>expert_swiglu_activation</x:v>
-      </x:c>
-      <x:c r="S16" s="51" t="str">
-        <x:v>expert_down_projection</x:v>
-      </x:c>
-      <x:c r="T16" s="52" t="str">
-        <x:v>moe_combine</x:v>
+      <x:c r="G16" s="28" t="str">
+        <x:v>Attn / HOPE forward ITL</x:v>
+      </x:c>
+      <x:c r="H16" s="28" t="str">
+        <x:v>Forward primary crossover?</x:v>
+      </x:c>
+      <x:c r="I16" s="28" t="str">
+        <x:v>Attn / HOPE including-online ITL</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="str">
+        <x:v>Including-online sensitivity?</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="76" t="n">
+      <x:c r="A17" s="78" t="n">
         <x:f>'01_Inputs'!$B$65</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B17" s="65" t="n">
-        <x:f>SUM(H17:T17)</x:f>
+        <x:f>SUM(I$26:I$38)</x:f>
         <x:v>0.3816320713513514</x:v>
       </x:c>
       <x:c r="C17" s="65" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$17)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
-        <x:v>0.9717198910032332</x:v>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",C$42:C$77)+SUMIF($A$42:$A$77,"cms_forward",C$42:C$77)</x:f>
+        <x:v>0.028141792432432432</x:v>
       </x:c>
       <x:c r="D17" s="65" t="n">
+        <x:f>SUM(C$42:C$77)</x:f>
+        <x:v>0.9717198910032334</x:v>
+      </x:c>
+      <x:c r="E17" s="65" t="n">
         <x:f>(2*($A$17)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E17" s="65" t="n">
+      <x:c r="F17" s="65" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$17)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>2.9409942626953125</x:v>
       </x:c>
-      <x:c r="F17" s="65" t="n">
+      <x:c r="G17" s="65" t="n">
         <x:f>B17/C17</x:f>
-        <x:v>0.3927387664745062</x:v>
-      </x:c>
-      <x:c r="G17" s="20" t="str">
+        <x:v>13.561043500254582</x:v>
+      </x:c>
+      <x:c r="H17" s="20" t="str">
         <x:f>IF(B17&gt;=C17,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I17" s="65" t="n">
+        <x:f>B17/D17</x:f>
+        <x:v>0.3927387664745061</x:v>
+      </x:c>
+      <x:c r="J17" s="20" t="str">
+        <x:f>IF(B17&gt;=D17,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.02720851027027027</x:v>
-      </x:c>
-      <x:c r="I17" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0000022140540540540544</x:v>
-      </x:c>
-      <x:c r="J17" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0000011070270270270272</x:v>
-      </x:c>
-      <x:c r="K17" s="20" t="n">
-        <x:f>(MAX(((1)*((4*((($A$17)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$17)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$17)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$17)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.2904861059459459</x:v>
-      </x:c>
-      <x:c r="L17" s="20" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$17)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00028672</x:v>
-      </x:c>
-      <x:c r="M17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009070979459459458</x:v>
-      </x:c>
-      <x:c r="N17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00014280756756756757</x:v>
-      </x:c>
-      <x:c r="O17" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000002215135135135135</x:v>
-      </x:c>
-      <x:c r="P17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.01814085189189189</x:v>
-      </x:c>
-      <x:c r="Q17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.01814085189189189</x:v>
-      </x:c>
-      <x:c r="R17" s="20" t="n">
-        <x:f>(MAX(((1)*((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000006642162162162162</x:v>
-      </x:c>
-      <x:c r="S17" s="20" t="n">
-        <x:f>(MAX(((1)*((2*((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.01814085189189189</x:v>
-      </x:c>
-      <x:c r="T17" s="20" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$17)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0000022140540540540544</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="77" t="n">
+      <x:c r="A18" s="79" t="n">
         <x:f>'01_Inputs'!$C$65</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="66" t="n">
-        <x:f>SUM(H18:T18)</x:f>
+        <x:f>SUM(J$26:J$38)</x:f>
         <x:v>0.7264222832432432</x:v>
       </x:c>
       <x:c r="C18" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$18)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",D$42:D$77)+SUMIF($A$42:$A$77,"cms_forward",D$42:D$77)</x:f>
+        <x:v>0.047214819459459455</x:v>
+      </x:c>
+      <x:c r="D18" s="66" t="n">
+        <x:f>SUM(D$42:D$77)</x:f>
         <x:v>1.934371016601061</x:v>
       </x:c>
-      <x:c r="D18" s="66" t="n">
+      <x:c r="E18" s="66" t="n">
         <x:f>(2*($A$18)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E18" s="66" t="n">
+      <x:c r="F18" s="66" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$18)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>5.881988525390625</x:v>
       </x:c>
-      <x:c r="F18" s="66" t="n">
+      <x:c r="G18" s="66" t="n">
         <x:f>B18/C18</x:f>
+        <x:v>15.385472009841711</x:v>
+      </x:c>
+      <x:c r="H18" s="21" t="str">
+        <x:f>IF(B18&gt;=C18,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I18" s="66" t="n">
+        <x:f>B18/D18</x:f>
         <x:v>0.3755341023045624</x:v>
       </x:c>
-      <x:c r="G18" s="21" t="str">
-        <x:f>IF(B18&gt;=C18,"YES","NO")</x:f>
+      <x:c r="J18" s="21" t="str">
+        <x:f>IF(B18&gt;=D18,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027210724324324323</x:v>
-      </x:c>
-      <x:c r="I18" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000004428108108108109</x:v>
-      </x:c>
-      <x:c r="J18" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0000022140540540540544</x:v>
-      </x:c>
-      <x:c r="K18" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((($A$18)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$18)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$18)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$18)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.5809722118918919</x:v>
-      </x:c>
-      <x:c r="L18" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$18)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00057344</x:v>
-      </x:c>
-      <x:c r="M18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009073193513513513</x:v>
-      </x:c>
-      <x:c r="N18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0001439156756756757</x:v>
-      </x:c>
-      <x:c r="O18" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00000443027027027027</x:v>
-      </x:c>
-      <x:c r="P18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.03614000432432432</x:v>
-      </x:c>
-      <x:c r="Q18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.03614000432432432</x:v>
-      </x:c>
-      <x:c r="R18" s="21" t="n">
-        <x:f>(MAX(((1)*((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000013284324324324324</x:v>
-      </x:c>
-      <x:c r="S18" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.03614000432432432</x:v>
-      </x:c>
-      <x:c r="T18" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$18)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000004428108108108109</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="77" t="n">
+      <x:c r="A19" s="79" t="n">
         <x:f>'01_Inputs'!$D$65</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="B19" s="66" t="n">
-        <x:f>SUM(H19:T19)</x:f>
+        <x:f>SUM(K$26:K$38)</x:f>
         <x:v>1.41474067027027</x:v>
       </x:c>
       <x:c r="C19" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$19)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
-        <x:v>3.8596732677967167</x:v>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",E$42:E$77)+SUMIF($A$42:$A$77,"cms_forward",E$42:E$77)</x:f>
+        <x:v>0.08536087351351351</x:v>
       </x:c>
       <x:c r="D19" s="66" t="n">
+        <x:f>SUM(E$42:E$77)</x:f>
+        <x:v>3.859673267796717</x:v>
+      </x:c>
+      <x:c r="E19" s="66" t="n">
         <x:f>(2*($A$19)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E19" s="66" t="n">
+      <x:c r="F19" s="66" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$19)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>11.76397705078125</x:v>
       </x:c>
-      <x:c r="F19" s="66" t="n">
+      <x:c r="G19" s="66" t="n">
         <x:f>B19/C19</x:f>
-        <x:v>0.3665441533805971</x:v>
-      </x:c>
-      <x:c r="G19" s="21" t="str">
+        <x:v>16.573643310319476</x:v>
+      </x:c>
+      <x:c r="H19" s="21" t="str">
         <x:f>IF(B19&gt;=C19,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I19" s="66" t="n">
+        <x:f>B19/D19</x:f>
+        <x:v>0.36654415338059704</x:v>
+      </x:c>
+      <x:c r="J19" s="21" t="str">
+        <x:f>IF(B19&gt;=D19,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027215152432432433</x:v>
-      </x:c>
-      <x:c r="I19" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000008856216216216217</x:v>
-      </x:c>
-      <x:c r="J19" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000004428108108108109</x:v>
-      </x:c>
-      <x:c r="K19" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((($A$19)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$19)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$19)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$19)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>1.1619444237837837</x:v>
-      </x:c>
-      <x:c r="L19" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$19)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00114688</x:v>
-      </x:c>
-      <x:c r="M19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009077621621621621</x:v>
-      </x:c>
-      <x:c r="N19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00014613189189189188</x:v>
-      </x:c>
-      <x:c r="O19" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00000886054054054054</x:v>
-      </x:c>
-      <x:c r="P19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.07171763027027027</x:v>
-      </x:c>
-      <x:c r="Q19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.07171763027027027</x:v>
-      </x:c>
-      <x:c r="R19" s="21" t="n">
-        <x:f>(MAX(((1)*((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00002656864864864865</x:v>
-      </x:c>
-      <x:c r="S19" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.07171763027027027</x:v>
-      </x:c>
-      <x:c r="T19" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$19)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000008856216216216217</x:v>
-      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="77" t="n">
+      <x:c r="A20" s="79" t="n">
         <x:f>'01_Inputs'!$E$65</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="66" t="n">
-        <x:f>SUM(H20:T20)</x:f>
+        <x:f>SUM(L$26:L$38)</x:f>
         <x:v>2.7864206642800817</x:v>
       </x:c>
       <x:c r="C20" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$20)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
-        <x:v>7.710277770188028</x:v>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",F$42:F$77)+SUMIF($A$42:$A$77,"cms_forward",F$42:F$77)</x:f>
+        <x:v>0.16165298162162162</x:v>
       </x:c>
       <x:c r="D20" s="66" t="n">
+        <x:f>SUM(F$42:F$77)</x:f>
+        <x:v>7.7102777701880285</x:v>
+      </x:c>
+      <x:c r="E20" s="66" t="n">
         <x:f>(2*($A$20)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E20" s="66" t="n">
+      <x:c r="F20" s="66" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$20)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>23.5279541015625</x:v>
       </x:c>
-      <x:c r="F20" s="66" t="n">
+      <x:c r="G20" s="66" t="n">
         <x:f>B20/C20</x:f>
-        <x:v>0.3613904384941673</x:v>
-      </x:c>
-      <x:c r="G20" s="21" t="str">
+        <x:v>17.237050850087066</x:v>
+      </x:c>
+      <x:c r="H20" s="21" t="str">
         <x:f>IF(B20&gt;=C20,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I20" s="66" t="n">
+        <x:f>B20/D20</x:f>
+        <x:v>0.36139043849416724</x:v>
+      </x:c>
+      <x:c r="J20" s="21" t="str">
+        <x:f>IF(B20&gt;=D20,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.02722400864864865</x:v>
-      </x:c>
-      <x:c r="I20" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000017712432432432435</x:v>
-      </x:c>
-      <x:c r="J20" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000008856216216216217</x:v>
-      </x:c>
-      <x:c r="K20" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((($A$20)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$20)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$20)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$20)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>2.3238888475675674</x:v>
-      </x:c>
-      <x:c r="L20" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$20)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00229376</x:v>
-      </x:c>
-      <x:c r="M20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009086477837837838</x:v>
-      </x:c>
-      <x:c r="N20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00015056432432432432</x:v>
-      </x:c>
-      <x:c r="O20" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00001772108108108108</x:v>
-      </x:c>
-      <x:c r="P20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.14122062214741476</x:v>
-      </x:c>
-      <x:c r="Q20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.14122062214741476</x:v>
-      </x:c>
-      <x:c r="R20" s="21" t="n">
-        <x:f>(MAX(((1)*((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0000531372972972973</x:v>
-      </x:c>
-      <x:c r="S20" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.14122062214741476</x:v>
-      </x:c>
-      <x:c r="T20" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$20)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000017712432432432435</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="77" t="n">
+      <x:c r="A21" s="79" t="n">
         <x:f>'01_Inputs'!$F$65</x:f>
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="66" t="n">
-        <x:f>SUM(H21:T21)</x:f>
+        <x:f>SUM(M$26:M$38)</x:f>
         <x:v>5.510663376647901</x:v>
       </x:c>
       <x:c r="C21" s="66" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$21)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
-        <x:v>15.41148677497065</x:v>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",G$42:G$77)+SUMIF($A$42:$A$77,"cms_forward",G$42:G$77)</x:f>
+        <x:v>0.3142371978378378</x:v>
       </x:c>
       <x:c r="D21" s="66" t="n">
+        <x:f>SUM(G$42:G$77)</x:f>
+        <x:v>15.411486774970651</x:v>
+      </x:c>
+      <x:c r="E21" s="66" t="n">
         <x:f>(2*($A$21)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E21" s="66" t="n">
+      <x:c r="F21" s="66" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$21)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>47.055908203125</x:v>
       </x:c>
-      <x:c r="F21" s="66" t="n">
+      <x:c r="G21" s="66" t="n">
         <x:f>B21/C21</x:f>
-        <x:v>0.35756857577152196</x:v>
-      </x:c>
-      <x:c r="G21" s="21" t="str">
+        <x:v>17.53663606525565</x:v>
+      </x:c>
+      <x:c r="H21" s="21" t="str">
         <x:f>IF(B21&gt;=C21,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I21" s="66" t="n">
+        <x:f>B21/D21</x:f>
+        <x:v>0.3575685757715219</x:v>
+      </x:c>
+      <x:c r="J21" s="21" t="str">
+        <x:f>IF(B21&gt;=D21,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.027241721081081083</x:v>
-      </x:c>
-      <x:c r="I21" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
-      <x:c r="J21" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.000017712432432432435</x:v>
-      </x:c>
-      <x:c r="K21" s="21" t="n">
-        <x:f>(MAX(((1)*((4*((($A$21)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$21)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$21)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$21)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>4.647777695135135</x:v>
-      </x:c>
-      <x:c r="L21" s="21" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$21)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00458752</x:v>
-      </x:c>
-      <x:c r="M21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.009104190270270271</x:v>
-      </x:c>
-      <x:c r="N21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00015942918918918918</x:v>
-      </x:c>
-      <x:c r="O21" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003544216216216216</x:v>
-      </x:c>
-      <x:c r="P21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.2738541806844355</x:v>
-      </x:c>
-      <x:c r="Q21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.2738541806844355</x:v>
-      </x:c>
-      <x:c r="R21" s="21" t="n">
-        <x:f>(MAX(((1)*((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.0001062745945945946</x:v>
-      </x:c>
-      <x:c r="S21" s="21" t="n">
-        <x:f>(MAX(((1)*((2*((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.2738541806844355</x:v>
-      </x:c>
-      <x:c r="T21" s="21" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$21)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
-        <x:v>0.00003542486486486487</x:v>
-      </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="78" t="n">
+      <x:c r="A22" s="80" t="n">
         <x:f>'01_Inputs'!$G$65</x:f>
         <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="67" t="n">
-        <x:f>SUM(H22:T22)</x:f>
+        <x:f>SUM(N$26:N$38)</x:f>
         <x:v>10.888036865046827</x:v>
       </x:c>
       <x:c r="C22" s="67" t="n">
-        <x:f>(('21_HOPE_Decode'!$B$8)-('21_HOPE_Decode'!$Q$12)-((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10))))*($A$22)/('01_Inputs'!$C$5)+((((SUM('21_HOPE_Decode'!$F$12:$F$47)-'21_HOPE_Decode'!$F$12))*('02_HW'!$C$9)*('02_HW'!$C$10)))+((MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10)))</x:f>
-        <x:v>30.813904784535897</x:v>
+        <x:f>SUMIF($A$42:$A$77,"titans_forward",H$42:H$77)+SUMIF($A$42:$A$77,"cms_forward",H$42:H$77)</x:f>
+        <x:v>0.6194056302702703</x:v>
       </x:c>
       <x:c r="D22" s="67" t="n">
+        <x:f>SUM(H$42:H$77)</x:f>
+        <x:v>30.8139047845359</x:v>
+      </x:c>
+      <x:c r="E22" s="67" t="n">
         <x:f>(2*($A$22)*('01_Inputs'!$C$11)*('01_Inputs'!$C$15)*('01_Inputs'!$C$13)*('01_Inputs'!$C$18))/'02_HW'!$C$11</x:f>
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="n">
+      <x:c r="F22" s="67" t="n">
         <x:f>('21_HOPE_Decode'!$E$3)*($A$22)/('01_Inputs'!$C$5)/'02_HW'!$C$11</x:f>
         <x:v>94.11181640625</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="n">
+      <x:c r="G22" s="67" t="n">
         <x:f>B22/C22</x:f>
-        <x:v>0.3533481699635497</x:v>
-      </x:c>
-      <x:c r="G22" s="22" t="str">
+        <x:v>17.578201315825886</x:v>
+      </x:c>
+      <x:c r="H22" s="22" t="str">
         <x:f>IF(B22&gt;=C22,"YES","NO")</x:f>
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="I22" s="67" t="n">
+        <x:f>B22/D22</x:f>
+        <x:v>0.3533481699635496</x:v>
+      </x:c>
+      <x:c r="J22" s="22" t="str">
+        <x:f>IF(B22&gt;=D22,"YES","NO")</x:f>
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="H22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="50" t="str">
+        <x:v>Component</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="str">
+        <x:v>Attention stage</x:v>
+      </x:c>
+      <x:c r="C25" s="76" t="n">
+        <x:f>'01_Inputs'!$B$64</x:f>
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="D25" s="76" t="n">
+        <x:f>'01_Inputs'!$C$64</x:f>
+        <x:v>4096</x:v>
+      </x:c>
+      <x:c r="E25" s="76" t="n">
+        <x:f>'01_Inputs'!$D$64</x:f>
+        <x:v>16384</x:v>
+      </x:c>
+      <x:c r="F25" s="76" t="n">
+        <x:f>'01_Inputs'!$E$64</x:f>
+        <x:v>65536</x:v>
+      </x:c>
+      <x:c r="G25" s="76" t="n">
+        <x:f>'01_Inputs'!$F$64</x:f>
+        <x:v>131072</x:v>
+      </x:c>
+      <x:c r="H25" s="76" t="n">
+        <x:f>'01_Inputs'!$G$64</x:f>
+        <x:v>262144</x:v>
+      </x:c>
+      <x:c r="I25" s="76" t="n">
+        <x:f>'01_Inputs'!$B$65</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="76" t="n">
+        <x:f>'01_Inputs'!$C$65</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K25" s="76" t="n">
+        <x:f>'01_Inputs'!$D$65</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L25" s="76" t="n">
+        <x:f>'01_Inputs'!$E$65</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M25" s="76" t="n">
+        <x:f>'01_Inputs'!$F$65</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N25" s="77" t="n">
+        <x:f>'01_Inputs'!$G$65</x:f>
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="20" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B26" s="20" t="str">
+        <x:v>qkv_projection</x:v>
+      </x:c>
+      <x:c r="C26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.027277145945945946</x:v>
       </x:c>
-      <x:c r="I22" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+      <x:c r="E26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+      <x:c r="F26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+      <x:c r="G26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+      <x:c r="H26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+      <x:c r="I26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.02720851027027027</x:v>
+      </x:c>
+      <x:c r="J26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027210724324324323</x:v>
+      </x:c>
+      <x:c r="K26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027215152432432433</x:v>
+      </x:c>
+      <x:c r="L26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.02722400864864865</x:v>
+      </x:c>
+      <x:c r="M26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027241721081081083</x:v>
+      </x:c>
+      <x:c r="N26" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)+('01_Inputs'!$C$12)*(((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))+2*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13))))*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.027277145945945946</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="21" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B27" s="21" t="str">
+        <x:v>kv_cache_append</x:v>
+      </x:c>
+      <x:c r="C27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007084972972972974</x:v>
       </x:c>
-      <x:c r="J22" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="E27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="F27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="G27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="H27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="I27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000022140540540540544</x:v>
+      </x:c>
+      <x:c r="J27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000004428108108108109</x:v>
+      </x:c>
+      <x:c r="K27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000008856216216216217</x:v>
+      </x:c>
+      <x:c r="L27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000017712432432432435</x:v>
+      </x:c>
+      <x:c r="M27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00003542486486486487</x:v>
       </x:c>
-      <x:c r="K22" s="22" t="n">
-        <x:f>(MAX(((1)*((4*((($A$22)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((($A$22)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*($A$22)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,($A$22)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="N27" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*((0)+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="21" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B28" s="21" t="str">
+        <x:v>q_materialization_read</x:v>
+      </x:c>
+      <x:c r="C28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="D28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="E28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="F28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="G28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="H28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="I28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000011070270270270272</x:v>
+      </x:c>
+      <x:c r="J28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000022140540540540544</x:v>
+      </x:c>
+      <x:c r="K28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000004428108108108109</x:v>
+      </x:c>
+      <x:c r="L28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000008856216216216217</x:v>
+      </x:c>
+      <x:c r="M28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000017712432432432435</x:v>
+      </x:c>
+      <x:c r="N28" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0)+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="21" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B29" s="21" t="str">
+        <x:v>flash_decode_partials</x:v>
+      </x:c>
+      <x:c r="C29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$B$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$B$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$B$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0725855481081081</x:v>
+      </x:c>
+      <x:c r="D29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$C$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2904861059459459</x:v>
+      </x:c>
+      <x:c r="E29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$D$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$D$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$D$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1619444237837837</x:v>
+      </x:c>
+      <x:c r="F29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$E$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$E$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$E$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>4.647777695135135</x:v>
+      </x:c>
+      <x:c r="G29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$F$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$F$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$F$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>9.29555539027027</x:v>
       </x:c>
-      <x:c r="L22" s="22" t="n">
-        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,($A$22)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="H29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$G$64)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$G$64)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$5)*('01_Inputs'!$G$64)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,(((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>18.59111078054054</x:v>
+      </x:c>
+      <x:c r="I29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$B$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$B$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$B$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2904861059459459</x:v>
+      </x:c>
+      <x:c r="J29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$C$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$C$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$C$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5809722118918919</x:v>
+      </x:c>
+      <x:c r="K29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$D$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$D$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$D$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1619444237837837</x:v>
+      </x:c>
+      <x:c r="L29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$E$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$E$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$E$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3238888475675674</x:v>
+      </x:c>
+      <x:c r="M29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$F$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$F$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$F$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>4.647777695135135</x:v>
+      </x:c>
+      <x:c r="N29" s="66" t="n">
+        <x:f>(MAX(((1)*((4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))*('01_Inputs'!$C$13)+('01_Inputs'!$C$24)*((('01_Inputs'!$G$65)*('01_Inputs'!$C$14)*('01_Inputs'!$C$10)*('01_Inputs'!$C$11)))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((2*('01_Inputs'!$G$65)*('01_Inputs'!$C$11)*((('01_Inputs'!$C$15)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$18)*('01_Inputs'!$C$23)))+((IF(('01_Inputs'!$C$21)=1,(((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)),0)))+((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$G$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>9.29555539027027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="21" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B30" s="21" t="str">
+        <x:v>flash_decode_reduce</x:v>
+      </x:c>
+      <x:c r="C30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$B$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$C$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00032103783783783783</x:v>
+      </x:c>
+      <x:c r="E30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$D$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011778767567567567</x:v>
+      </x:c>
+      <x:c r="F30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$E$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.004605232432432433</x:v>
+      </x:c>
+      <x:c r="G30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$F$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00917504</x:v>
       </x:c>
-      <x:c r="M22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="H30" s="66" t="n">
+        <x:f>(MAX((((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*(((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))=1,0,('01_Inputs'!$C$5)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(((INT((('01_Inputs'!$G$64)+('01_Inputs'!$C$22)-1)/('01_Inputs'!$C$22))))&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018314655135135135</x:v>
+      </x:c>
+      <x:c r="I30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$B$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028672</x:v>
+      </x:c>
+      <x:c r="J30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$C$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00057344</x:v>
+      </x:c>
+      <x:c r="K30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$D$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00114688</x:v>
+      </x:c>
+      <x:c r="L30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$E$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00229376</x:v>
+      </x:c>
+      <x:c r="M30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$F$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00458752</x:v>
+      </x:c>
+      <x:c r="N30" s="66" t="n">
+        <x:f>(MAX((((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*(((IF(('01_Inputs'!$C$21)=1,0,('01_Inputs'!$G$65)*('01_Inputs'!$C$10)*('01_Inputs'!$C$14)*('01_Inputs'!$C$21)*(('01_Inputs'!$C$13)*('01_Inputs'!$C$19)+('01_Inputs'!$C$20)))))+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((IF(('01_Inputs'!$C$21)&gt;1,1,0)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00917504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="21" t="str">
+        <x:v>attention</x:v>
+      </x:c>
+      <x:c r="B31" s="21" t="str">
+        <x:v>output_projection</x:v>
+      </x:c>
+      <x:c r="C31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.009139615135135136</x:v>
       </x:c>
-      <x:c r="N22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+      <x:c r="E31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+      <x:c r="F31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+      <x:c r="G31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+      <x:c r="H31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+      <x:c r="I31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009070979459459458</x:v>
+      </x:c>
+      <x:c r="J31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009073193513513513</x:v>
+      </x:c>
+      <x:c r="K31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009077621621621621</x:v>
+      </x:c>
+      <x:c r="L31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009086477837837838</x:v>
+      </x:c>
+      <x:c r="M31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009104190270270271</x:v>
+      </x:c>
+      <x:c r="N31" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$16)+((('01_Inputs'!$C$14)*('01_Inputs'!$C$13)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B32" s="21" t="str">
+        <x:v>moe_router</x:v>
+      </x:c>
+      <x:c r="C32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00017715891891891892</x:v>
       </x:c>
-      <x:c r="O22" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+      <x:c r="E32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+      <x:c r="F32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+      <x:c r="G32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+      <x:c r="H32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+      <x:c r="I32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014280756756756757</x:v>
+      </x:c>
+      <x:c r="J32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001439156756756757</x:v>
+      </x:c>
+      <x:c r="K32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014613189189189188</x:v>
+      </x:c>
+      <x:c r="L32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00015056432432432432</x:v>
+      </x:c>
+      <x:c r="M32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00015942918918918918</x:v>
+      </x:c>
+      <x:c r="N32" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$25)+('01_Inputs'!$C$29)*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$25)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$25)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00017715891891891892</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B33" s="21" t="str">
+        <x:v>moe_dispatch</x:v>
+      </x:c>
+      <x:c r="C33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007088432432432432</x:v>
       </x:c>
-      <x:c r="P22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+      <x:c r="E33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+      <x:c r="F33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+      <x:c r="G33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+      <x:c r="H33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+      <x:c r="I33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000002215135135135135</x:v>
+      </x:c>
+      <x:c r="J33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00000443027027027027</x:v>
+      </x:c>
+      <x:c r="K33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00000886054054054054</x:v>
+      </x:c>
+      <x:c r="L33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00001772108108108108</x:v>
+      </x:c>
+      <x:c r="M33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003544216216216216</x:v>
+      </x:c>
+      <x:c r="N33" s="66" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$30)))))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007088432432432432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B34" s="21" t="str">
+        <x:v>expert_up_projection</x:v>
+      </x:c>
+      <x:c r="C34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.5154173189795723</x:v>
       </x:c>
-      <x:c r="Q22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.5154173189795723</x:v>
       </x:c>
-      <x:c r="R22" s="22" t="n">
-        <x:f>(MAX(((1)*((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="E34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="F34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="G34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="H34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="I34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.01814085189189189</x:v>
+      </x:c>
+      <x:c r="J34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.03614000432432432</x:v>
+      </x:c>
+      <x:c r="K34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07171763027027027</x:v>
+      </x:c>
+      <x:c r="L34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14122062214741476</x:v>
+      </x:c>
+      <x:c r="M34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2738541806844355</x:v>
+      </x:c>
+      <x:c r="N34" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B35" s="21" t="str">
+        <x:v>expert_gate_projection</x:v>
+      </x:c>
+      <x:c r="C35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="D35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="E35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="F35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="G35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="H35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="I35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.01814085189189189</x:v>
+      </x:c>
+      <x:c r="J35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.03614000432432432</x:v>
+      </x:c>
+      <x:c r="K35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07171763027027027</x:v>
+      </x:c>
+      <x:c r="L35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14122062214741476</x:v>
+      </x:c>
+      <x:c r="M35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2738541806844355</x:v>
+      </x:c>
+      <x:c r="N35" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B36" s="21" t="str">
+        <x:v>expert_swiglu_activation</x:v>
+      </x:c>
+      <x:c r="C36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.0002125491891891892</x:v>
       </x:c>
-      <x:c r="S22" s="22" t="n">
-        <x:f>(MAX(((1)*((2*((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+      <x:c r="E36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+      <x:c r="F36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+      <x:c r="G36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+      <x:c r="H36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+      <x:c r="I36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000006642162162162162</x:v>
+      </x:c>
+      <x:c r="J36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000013284324324324324</x:v>
+      </x:c>
+      <x:c r="K36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00002656864864864865</x:v>
+      </x:c>
+      <x:c r="L36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000531372972972973</x:v>
+      </x:c>
+      <x:c r="M36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001062745945945946</x:v>
+      </x:c>
+      <x:c r="N36" s="66" t="n">
+        <x:f>(MAX(((1)*((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$35)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((IF(('01_Inputs'!$C$36)=1,0,(2*((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002125491891891892</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="21" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B37" s="21" t="str">
+        <x:v>expert_down_projection</x:v>
+      </x:c>
+      <x:c r="C37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.5154173189795723</x:v>
       </x:c>
-      <x:c r="T22" s="22" t="n">
-        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((($A$22)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+      <x:c r="D37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="E37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="F37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="G37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="H37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+      <x:c r="I37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.01814085189189189</x:v>
+      </x:c>
+      <x:c r="J37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.03614000432432432</x:v>
+      </x:c>
+      <x:c r="K37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07171763027027027</x:v>
+      </x:c>
+      <x:c r="L37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14122062214741476</x:v>
+      </x:c>
+      <x:c r="M37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2738541806844355</x:v>
+      </x:c>
+      <x:c r="N37" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((IF(('01_Inputs'!$C$31)&gt;0,('01_Inputs'!$C$31),('01_Inputs'!$C$25)*(1-POWER(1-1/('01_Inputs'!$C$25),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26))))))*('01_Inputs'!$C$12)*('01_Inputs'!$C$27)*('01_Inputs'!$C$17)*('01_Inputs'!$C$32)))+(IF(('01_Inputs'!$C$36)=1,0,((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$27)*('01_Inputs'!$C$16)))))))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5154173189795723</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="22" t="str">
+        <x:v>moe</x:v>
+      </x:c>
+      <x:c r="B38" s="22" t="str">
+        <x:v>moe_combine</x:v>
+      </x:c>
+      <x:c r="C38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
         <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="D38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="E38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="F38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="G38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="H38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$5)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="I38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000022140540540540544</x:v>
+      </x:c>
+      <x:c r="J38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000004428108108108109</x:v>
+      </x:c>
+      <x:c r="K38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000008856216216216217</x:v>
+      </x:c>
+      <x:c r="L38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000017712432432432435</x:v>
+      </x:c>
+      <x:c r="M38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="N38" s="67" t="n">
+        <x:f>(MAX(((1)*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$26)*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="50" t="str">
+        <x:v>Dependency group</x:v>
+      </x:c>
+      <x:c r="B41" s="51" t="str">
+        <x:v>HOPE stage</x:v>
+      </x:c>
+      <x:c r="C41" s="76" t="n">
+        <x:f>'01_Inputs'!$B$65</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D41" s="76" t="n">
+        <x:f>'01_Inputs'!$C$65</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E41" s="76" t="n">
+        <x:f>'01_Inputs'!$D$65</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F41" s="76" t="n">
+        <x:f>'01_Inputs'!$E$65</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G41" s="76" t="n">
+        <x:f>'01_Inputs'!$F$65</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H41" s="77" t="n">
+        <x:f>'01_Inputs'!$G$65</x:f>
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="20" t="str">
+        <x:v>titans_forward</x:v>
+      </x:c>
+      <x:c r="B42" s="20" t="str">
+        <x:v>static_q_projection</x:v>
+      </x:c>
+      <x:c r="C42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009070979459459458</x:v>
+      </x:c>
+      <x:c r="D42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009073193513513513</x:v>
+      </x:c>
+      <x:c r="E42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009077621621621621</x:v>
+      </x:c>
+      <x:c r="F42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009086477837837838</x:v>
+      </x:c>
+      <x:c r="G42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009104190270270271</x:v>
+      </x:c>
+      <x:c r="H42" s="65" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$12)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$12)*('01_Inputs'!$C$12)*('01_Inputs'!$C$17)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$12)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009139615135135136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="21" t="str">
+        <x:v>titans_forward</x:v>
+      </x:c>
+      <x:c r="B43" s="21" t="str">
+        <x:v>M_mem_forward</x:v>
+      </x:c>
+      <x:c r="C43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018139744864864863</x:v>
+      </x:c>
+      <x:c r="D43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036279489729729726</x:v>
+      </x:c>
+      <x:c r="E43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="F43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="G43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="H43" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B44" s="21" t="str">
+        <x:v>cms_l1_router</x:v>
+      </x:c>
+      <x:c r="C44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$B$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007195783783783785</x:v>
+      </x:c>
+      <x:c r="D44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001439156756756757</x:v>
+      </x:c>
+      <x:c r="E44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$D$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002878313513513514</x:v>
+      </x:c>
+      <x:c r="F44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$E$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005756627027027028</x:v>
+      </x:c>
+      <x:c r="G44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$F$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011513254054054056</x:v>
+      </x:c>
+      <x:c r="H44" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$D$57)+('01_Inputs'!$G$57)*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$G$65),1)))*((('01_Inputs'!$B$57)*('01_Inputs'!$D$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002302650810810811</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B45" s="21" t="str">
+        <x:v>cms_l1_expert_a</x:v>
+      </x:c>
+      <x:c r="C45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007196648648648649</x:v>
+      </x:c>
+      <x:c r="D45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014393297297297299</x:v>
+      </x:c>
+      <x:c r="E45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028786594594594597</x:v>
+      </x:c>
+      <x:c r="F45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757318918918919</x:v>
+      </x:c>
+      <x:c r="G45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514637837837839</x:v>
+      </x:c>
+      <x:c r="H45" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$57)*('01_Inputs'!$C$16)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$M$57)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$B$57)*('01_Inputs'!$E$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0023029275675675678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B46" s="21" t="str">
+        <x:v>cms_l1_expert_b</x:v>
+      </x:c>
+      <x:c r="C46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000719654054054054</x:v>
+      </x:c>
+      <x:c r="D46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001439308108108108</x:v>
+      </x:c>
+      <x:c r="E46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002878616216216216</x:v>
+      </x:c>
+      <x:c r="F46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757232432432432</x:v>
+      </x:c>
+      <x:c r="G46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514464864864865</x:v>
+      </x:c>
+      <x:c r="H46" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)*('01_Inputs'!$E$57)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$57),IF(('01_Inputs'!$K$57)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$57),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$57)))))*((('01_Inputs'!$E$57)*('01_Inputs'!$C$57)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$57)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002302892972972973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B47" s="21" t="str">
+        <x:v>cms_l2_router</x:v>
+      </x:c>
+      <x:c r="C47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$B$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014280756756756757</x:v>
+      </x:c>
+      <x:c r="D47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028561513513513515</x:v>
+      </x:c>
+      <x:c r="E47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$D$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005712302702702703</x:v>
+      </x:c>
+      <x:c r="F47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$E$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011424605405405406</x:v>
+      </x:c>
+      <x:c r="G47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$F$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002284921081081081</x:v>
+      </x:c>
+      <x:c r="H47" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$D$58)+('01_Inputs'!$G$58)*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$G$65),1)))*((('01_Inputs'!$B$58)*('01_Inputs'!$D$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.004569842162162162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B48" s="21" t="str">
+        <x:v>cms_l2_expert_a</x:v>
+      </x:c>
+      <x:c r="C48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007196648648648649</x:v>
+      </x:c>
+      <x:c r="D48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014393297297297299</x:v>
+      </x:c>
+      <x:c r="E48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028786594594594597</x:v>
+      </x:c>
+      <x:c r="F48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757318918918919</x:v>
+      </x:c>
+      <x:c r="G48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514637837837839</x:v>
+      </x:c>
+      <x:c r="H48" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$58)*('01_Inputs'!$C$16)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$M$58)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$B$58)*('01_Inputs'!$E$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0023029275675675678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B49" s="21" t="str">
+        <x:v>cms_l2_expert_b</x:v>
+      </x:c>
+      <x:c r="C49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000719654054054054</x:v>
+      </x:c>
+      <x:c r="D49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001439308108108108</x:v>
+      </x:c>
+      <x:c r="E49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002878616216216216</x:v>
+      </x:c>
+      <x:c r="F49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757232432432432</x:v>
+      </x:c>
+      <x:c r="G49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514464864864865</x:v>
+      </x:c>
+      <x:c r="H49" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)*('01_Inputs'!$E$58)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$58),IF(('01_Inputs'!$K$58)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$58),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$58)))))*((('01_Inputs'!$E$58)*('01_Inputs'!$C$58)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$58)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002302892972972973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B50" s="21" t="str">
+        <x:v>cms_l3_router</x:v>
+      </x:c>
+      <x:c r="C50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$B$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000284507027027027</x:v>
+      </x:c>
+      <x:c r="D50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000569014054054054</x:v>
+      </x:c>
+      <x:c r="E50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$D$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.001138028108108108</x:v>
+      </x:c>
+      <x:c r="F50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$E$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002276056216216216</x:v>
+      </x:c>
+      <x:c r="G50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$F$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.004552112432432432</x:v>
+      </x:c>
+      <x:c r="H50" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$D$59)+('01_Inputs'!$G$59)*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$G$65),1)))*((('01_Inputs'!$B$59)*('01_Inputs'!$D$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009104224864864865</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B51" s="21" t="str">
+        <x:v>cms_l3_expert_a</x:v>
+      </x:c>
+      <x:c r="C51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007196648648648649</x:v>
+      </x:c>
+      <x:c r="D51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014393297297297299</x:v>
+      </x:c>
+      <x:c r="E51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028786594594594597</x:v>
+      </x:c>
+      <x:c r="F51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757318918918919</x:v>
+      </x:c>
+      <x:c r="G51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514637837837839</x:v>
+      </x:c>
+      <x:c r="H51" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$59)*('01_Inputs'!$C$16)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$M$59)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$B$59)*('01_Inputs'!$E$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0023029275675675678</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="21" t="str">
+        <x:v>cms_forward</x:v>
+      </x:c>
+      <x:c r="B52" s="21" t="str">
+        <x:v>cms_l3_expert_b</x:v>
+      </x:c>
+      <x:c r="C52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$B$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000719654054054054</x:v>
+      </x:c>
+      <x:c r="D52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0001439308108108108</x:v>
+      </x:c>
+      <x:c r="E52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$D$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002878616216216216</x:v>
+      </x:c>
+      <x:c r="F52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$E$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005757232432432432</x:v>
+      </x:c>
+      <x:c r="G52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$F$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011514464864864865</x:v>
+      </x:c>
+      <x:c r="H52" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)*('01_Inputs'!$E$59)*('01_Inputs'!$C$16)))+((IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$G$65),1)))*((MIN(('01_Inputs'!$D$59),IF(('01_Inputs'!$K$59)=1,('01_Inputs'!$C$10)*('01_Inputs'!$F$59),((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$F$59)))))*((('01_Inputs'!$E$59)*('01_Inputs'!$C$59)))*('01_Inputs'!$C$37)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$59)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.002302892972972973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B53" s="21" t="str">
+        <x:v>M_k_target_forward</x:v>
+      </x:c>
+      <x:c r="C53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018139744864864863</x:v>
+      </x:c>
+      <x:c r="D53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036279489729729726</x:v>
+      </x:c>
+      <x:c r="E53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="F53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="G53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="H53" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$48)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B54" s="21" t="str">
+        <x:v>M_k_prediction_forward</x:v>
+      </x:c>
+      <x:c r="C54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000581873463372345</x:v>
+      </x:c>
+      <x:c r="D54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000116374692674469</x:v>
+      </x:c>
+      <x:c r="E54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000232749385348938</x:v>
+      </x:c>
+      <x:c r="F54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000465498770697876</x:v>
+      </x:c>
+      <x:c r="G54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000930997541395752</x:v>
+      </x:c>
+      <x:c r="H54" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$48)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.001861995082791504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B55" s="21" t="str">
+        <x:v>M_v_target_forward</x:v>
+      </x:c>
+      <x:c r="C55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018139744864864863</x:v>
+      </x:c>
+      <x:c r="D55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036279489729729726</x:v>
+      </x:c>
+      <x:c r="E55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="F55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="G55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="H55" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$49)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B56" s="21" t="str">
+        <x:v>M_v_prediction_forward</x:v>
+      </x:c>
+      <x:c r="C56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000581873463372345</x:v>
+      </x:c>
+      <x:c r="D56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000116374692674469</x:v>
+      </x:c>
+      <x:c r="E56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000232749385348938</x:v>
+      </x:c>
+      <x:c r="F56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000465498770697876</x:v>
+      </x:c>
+      <x:c r="G56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000930997541395752</x:v>
+      </x:c>
+      <x:c r="H56" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$49)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.001861995082791504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B57" s="21" t="str">
+        <x:v>M_eta_target_forward</x:v>
+      </x:c>
+      <x:c r="C57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009070979594594594</x:v>
+      </x:c>
+      <x:c r="D57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018141959189189188</x:v>
+      </x:c>
+      <x:c r="E57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036283918378378376</x:v>
+      </x:c>
+      <x:c r="F57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07256783675675675</x:v>
+      </x:c>
+      <x:c r="G57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451356735135135</x:v>
+      </x:c>
+      <x:c r="H57" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$50)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.290271347027027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B58" s="21" t="str">
+        <x:v>M_eta_prediction_forward</x:v>
+      </x:c>
+      <x:c r="C58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00002909988751625488</x:v>
+      </x:c>
+      <x:c r="D58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00005819977503250976</x:v>
+      </x:c>
+      <x:c r="E58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00011639955006501952</x:v>
+      </x:c>
+      <x:c r="F58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00023279910013003903</x:v>
+      </x:c>
+      <x:c r="G58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00046559820026007806</x:v>
+      </x:c>
+      <x:c r="H58" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$50)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0009311964005201561</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B59" s="21" t="str">
+        <x:v>M_alpha_target_forward</x:v>
+      </x:c>
+      <x:c r="C59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.009070979594594594</x:v>
+      </x:c>
+      <x:c r="D59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018141959189189188</x:v>
+      </x:c>
+      <x:c r="E59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036283918378378376</x:v>
+      </x:c>
+      <x:c r="F59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07256783675675675</x:v>
+      </x:c>
+      <x:c r="G59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451356735135135</x:v>
+      </x:c>
+      <x:c r="H59" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$51)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.290271347027027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B60" s="21" t="str">
+        <x:v>M_alpha_prediction_forward</x:v>
+      </x:c>
+      <x:c r="C60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00002909988751625488</x:v>
+      </x:c>
+      <x:c r="D60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00005819977503250976</x:v>
+      </x:c>
+      <x:c r="E60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00011639955006501952</x:v>
+      </x:c>
+      <x:c r="F60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00023279910013003903</x:v>
+      </x:c>
+      <x:c r="G60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00046559820026007806</x:v>
+      </x:c>
+      <x:c r="H60" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$51)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0009311964005201561</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B61" s="21" t="str">
+        <x:v>M_mem_target_forward</x:v>
+      </x:c>
+      <x:c r="C61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$B$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.018139744864864863</x:v>
+      </x:c>
+      <x:c r="D61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$C$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.036279489729729726</x:v>
+      </x:c>
+      <x:c r="E61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$D$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="F61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$E$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="G61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$F$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="H61" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+('01_Inputs'!$G$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)*('01_Inputs'!$H$52)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="21" t="str">
+        <x:v>loss</x:v>
+      </x:c>
+      <x:c r="B62" s="21" t="str">
+        <x:v>M_mem_prediction_forward</x:v>
+      </x:c>
+      <x:c r="C62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0000581873463372345</x:v>
+      </x:c>
+      <x:c r="D62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000116374692674469</x:v>
+      </x:c>
+      <x:c r="E62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000232749385348938</x:v>
+      </x:c>
+      <x:c r="F62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000465498770697876</x:v>
+      </x:c>
+      <x:c r="G62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000930997541395752</x:v>
+      </x:c>
+      <x:c r="H62" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$16)))+(0)+((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$D$52)*('01_Inputs'!$C$16))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.001861995082791504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B63" s="21" t="str">
+        <x:v>M_k_weight_backward</x:v>
+      </x:c>
+      <x:c r="C63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255344432432433</x:v>
+      </x:c>
+      <x:c r="D63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14510688864864865</x:v>
+      </x:c>
+      <x:c r="E63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902137772972973</x:v>
+      </x:c>
+      <x:c r="F63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804275545945946</x:v>
+      </x:c>
+      <x:c r="G63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1608551091891892</x:v>
+      </x:c>
+      <x:c r="H63" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$48)+('01_Inputs'!$C$48)+('01_Inputs'!$D$48))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3217102183783784</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B64" s="21" t="str">
+        <x:v>M_k_dgd_extra</x:v>
+      </x:c>
+      <x:c r="C64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$B$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451002464864865</x:v>
+      </x:c>
+      <x:c r="D64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.290200492972973</x:v>
+      </x:c>
+      <x:c r="E64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$D$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.580400985945946</x:v>
+      </x:c>
+      <x:c r="F64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$E$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.160801971891892</x:v>
+      </x:c>
+      <x:c r="G64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$F$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.321603943783784</x:v>
+      </x:c>
+      <x:c r="H64" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$48)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))-(2*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$48)+('01_Inputs'!$C$40)*('01_Inputs'!$D$48))))+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$48)*('01_Inputs'!$D$48))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$G$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>4.643207887567568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B65" s="21" t="str">
+        <x:v>M_k_state_apply</x:v>
+      </x:c>
+      <x:c r="C65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="D65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="E65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014169945945945948</x:v>
+      </x:c>
+      <x:c r="F65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028339891891891896</x:v>
+      </x:c>
+      <x:c r="G65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005667978378378379</x:v>
+      </x:c>
+      <x:c r="H65" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$48)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$48)))*(((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$48))*((('01_Inputs'!$B$48)*('01_Inputs'!$C$48)+('01_Inputs'!$C$48)*('01_Inputs'!$D$48)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$48)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011335956756756758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B66" s="21" t="str">
+        <x:v>M_v_weight_backward</x:v>
+      </x:c>
+      <x:c r="C66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255344432432433</x:v>
+      </x:c>
+      <x:c r="D66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14510688864864865</x:v>
+      </x:c>
+      <x:c r="E66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902137772972973</x:v>
+      </x:c>
+      <x:c r="F66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804275545945946</x:v>
+      </x:c>
+      <x:c r="G66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1608551091891892</x:v>
+      </x:c>
+      <x:c r="H66" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$49)+('01_Inputs'!$C$49)+('01_Inputs'!$D$49))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3217102183783784</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B67" s="21" t="str">
+        <x:v>M_v_dgd_extra</x:v>
+      </x:c>
+      <x:c r="C67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$B$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451002464864865</x:v>
+      </x:c>
+      <x:c r="D67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.290200492972973</x:v>
+      </x:c>
+      <x:c r="E67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$D$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.580400985945946</x:v>
+      </x:c>
+      <x:c r="F67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$E$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.160801971891892</x:v>
+      </x:c>
+      <x:c r="G67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$F$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.321603943783784</x:v>
+      </x:c>
+      <x:c r="H67" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$49)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))-(2*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$49)+('01_Inputs'!$C$40)*('01_Inputs'!$D$49))))+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$49)*('01_Inputs'!$D$49))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$G$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>4.643207887567568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B68" s="21" t="str">
+        <x:v>M_v_state_apply</x:v>
+      </x:c>
+      <x:c r="C68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="D68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="E68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014169945945945948</x:v>
+      </x:c>
+      <x:c r="F68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028339891891891896</x:v>
+      </x:c>
+      <x:c r="G68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005667978378378379</x:v>
+      </x:c>
+      <x:c r="H68" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$49)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$49)))*(((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$49))*((('01_Inputs'!$B$49)*('01_Inputs'!$C$49)+('01_Inputs'!$C$49)*('01_Inputs'!$D$49)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$49)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011335956756756758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B69" s="21" t="str">
+        <x:v>M_eta_weight_backward</x:v>
+      </x:c>
+      <x:c r="C69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.03628170391891892</x:v>
+      </x:c>
+      <x:c r="D69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07256340783783784</x:v>
+      </x:c>
+      <x:c r="E69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14512681567567567</x:v>
+      </x:c>
+      <x:c r="F69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.29025363135135135</x:v>
+      </x:c>
+      <x:c r="G69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5805072627027027</x:v>
+      </x:c>
+      <x:c r="H69" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$50)+('01_Inputs'!$C$50)+('01_Inputs'!$D$50))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1610145254054054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B70" s="21" t="str">
+        <x:v>M_eta_dgd_extra</x:v>
+      </x:c>
+      <x:c r="C70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$B$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="D70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="E70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$D$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="F70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$E$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+      <x:c r="G70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$F$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1609436713513512</x:v>
+      </x:c>
+      <x:c r="H70" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$50)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))-(2*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$50)+('01_Inputs'!$C$40)*('01_Inputs'!$D$50))))+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$50)*('01_Inputs'!$D$50))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$G$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3218873427027025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B71" s="21" t="str">
+        <x:v>M_eta_state_apply</x:v>
+      </x:c>
+      <x:c r="C71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000017714594594594593</x:v>
+      </x:c>
+      <x:c r="D71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000035429189189189186</x:v>
+      </x:c>
+      <x:c r="E71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007085837837837837</x:v>
+      </x:c>
+      <x:c r="F71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014171675675675674</x:v>
+      </x:c>
+      <x:c r="G71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002834335135135135</x:v>
+      </x:c>
+      <x:c r="H71" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$50)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$50)))*(((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$50))*((('01_Inputs'!$B$50)*('01_Inputs'!$C$50)+('01_Inputs'!$C$50)*('01_Inputs'!$D$50)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$50)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000566867027027027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B72" s="21" t="str">
+        <x:v>M_alpha_weight_backward</x:v>
+      </x:c>
+      <x:c r="C72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.03628170391891892</x:v>
+      </x:c>
+      <x:c r="D72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07256340783783784</x:v>
+      </x:c>
+      <x:c r="E72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14512681567567567</x:v>
+      </x:c>
+      <x:c r="F72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.29025363135135135</x:v>
+      </x:c>
+      <x:c r="G72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5805072627027027</x:v>
+      </x:c>
+      <x:c r="H72" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$51)+('01_Inputs'!$C$51)+('01_Inputs'!$D$51))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1610145254054054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B73" s="21" t="str">
+        <x:v>M_alpha_dgd_extra</x:v>
+      </x:c>
+      <x:c r="C73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$B$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255897945945945</x:v>
+      </x:c>
+      <x:c r="D73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451179589189189</x:v>
+      </x:c>
+      <x:c r="E73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$D$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902359178378378</x:v>
+      </x:c>
+      <x:c r="F73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$E$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804718356756756</x:v>
+      </x:c>
+      <x:c r="G73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$F$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1609436713513512</x:v>
+      </x:c>
+      <x:c r="H73" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$51)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))-(2*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$51)+('01_Inputs'!$C$40)*('01_Inputs'!$D$51))))+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$51)*('01_Inputs'!$D$51))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$G$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3218873427027025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B74" s="21" t="str">
+        <x:v>M_alpha_state_apply</x:v>
+      </x:c>
+      <x:c r="C74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000017714594594594593</x:v>
+      </x:c>
+      <x:c r="D74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000035429189189189186</x:v>
+      </x:c>
+      <x:c r="E74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007085837837837837</x:v>
+      </x:c>
+      <x:c r="F74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014171675675675674</x:v>
+      </x:c>
+      <x:c r="G74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0002834335135135135</x:v>
+      </x:c>
+      <x:c r="H74" s="66" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$51)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$51)))*(((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$51))*((('01_Inputs'!$B$51)*('01_Inputs'!$C$51)+('01_Inputs'!$C$51)*('01_Inputs'!$D$51)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$51)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.000566867027027027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B75" s="21" t="str">
+        <x:v>M_mem_weight_backward</x:v>
+      </x:c>
+      <x:c r="C75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.07255344432432433</x:v>
+      </x:c>
+      <x:c r="D75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.14510688864864865</x:v>
+      </x:c>
+      <x:c r="E75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.2902137772972973</x:v>
+      </x:c>
+      <x:c r="F75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.5804275545945946</x:v>
+      </x:c>
+      <x:c r="G75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.1608551091891892</x:v>
+      </x:c>
+      <x:c r="H75" s="66" t="n">
+        <x:f>(MAX(((1)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$B$52)+('01_Inputs'!$C$52)+('01_Inputs'!$D$52))*('01_Inputs'!$C$16)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.3217102183783784</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="21" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B76" s="21" t="str">
+        <x:v>M_mem_dgd_extra</x:v>
+      </x:c>
+      <x:c r="C76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$B$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$B$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$B$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.1451002464864865</x:v>
+      </x:c>
+      <x:c r="D76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$C$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$C$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$C$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.290200492972973</x:v>
+      </x:c>
+      <x:c r="E76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$D$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$D$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$D$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.580400985945946</x:v>
+      </x:c>
+      <x:c r="F76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$E$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$E$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$E$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>1.160801971891892</x:v>
+      </x:c>
+      <x:c r="G76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$F$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$F$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$F$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>2.321603943783784</x:v>
+      </x:c>
+      <x:c r="H76" s="66" t="n">
+        <x:f>(MAX(((1)*((('01_Inputs'!$G$52)*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))-(2*((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))+((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*(('01_Inputs'!$C$39)*('01_Inputs'!$C$52)+('01_Inputs'!$C$40)*('01_Inputs'!$D$52))))+((2*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+4*((('01_Inputs'!$G$65)*('01_Inputs'!$C$10)))*('01_Inputs'!$C$52)*('01_Inputs'!$D$52))))))/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),((1)*(((('01_Inputs'!$G$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38)))+(0)+((('01_Inputs'!$G$65)*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$38))))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+(1)*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>4.643207887567568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="22" t="str">
+        <x:v>backward_update</x:v>
+      </x:c>
+      <x:c r="B77" s="22" t="str">
+        <x:v>M_mem_state_apply</x:v>
+      </x:c>
+      <x:c r="C77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$B$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00003542486486486487</x:v>
+      </x:c>
+      <x:c r="D77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$C$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00007084972972972974</x:v>
+      </x:c>
+      <x:c r="E77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$D$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00014169945945945948</x:v>
+      </x:c>
+      <x:c r="F77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$E$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.00028339891891891896</x:v>
+      </x:c>
+      <x:c r="G77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$F$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0005667978378378379</x:v>
+      </x:c>
+      <x:c r="H77" s="67" t="n">
+        <x:f>(MAX((((1/('01_Inputs'!$E$52)))*(0)/(('01_Inputs'!$C$33)*('02_HW'!$C$6))*('02_HW'!$C$10)),(((1/('01_Inputs'!$E$52)))*(((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+((('01_Inputs'!$G$65)*(1+('01_Inputs'!$F$52))*((('01_Inputs'!$B$52)*('01_Inputs'!$C$52)+('01_Inputs'!$C$52)*('01_Inputs'!$D$52)))*('01_Inputs'!$C$37)))+(0))/(('01_Inputs'!$C$34)*('02_HW'!$C$7))*('02_HW'!$C$10)))+((1/('01_Inputs'!$E$52)))*('02_HW'!$C$9)*('02_HW'!$C$10))</x:f>
+        <x:v>0.0011335956756756758</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:AD1"/>
-    <x:mergeCell ref="A2:AD2"/>
+    <x:mergeCell ref="A1:S1"/>
+    <x:mergeCell ref="A2:S2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e5a78f60bf4491d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf1f4a77fa249e9"/>
 </x:worksheet>
 </file>